--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE236"/>
+  <dimension ref="A1:AE237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 7564-2025</t>
+          <t>A 13567-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45705</v>
+        <v>45736</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1188,1118 +1188,1113 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Klubbsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 62852-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 7564-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45705</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U9" t="n">
         <v>4</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Solvända</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 7564-2025 artfynd.xlsx", "A 7564-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 7564-2025 karta.png", "A 7564-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 7564-2025 georefererad karta.tif", "A 7564-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 7564-2025 FSC-klagomål.docx", "A 7564-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 7564-2025 FSC-klagomål mail.docx", "A 7564-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 7564-2025 tillsynsbegäran.docx", "A 7564-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 7564-2025 tillsynsbegäran mail.docx", "A 7564-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 54444-2021</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44473</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Ängshök</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 41274-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45898</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>2.9</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 41274-2025 artfynd.xlsx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 41274-2025 karta.png", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 41274-2025 georefererad karta.tif", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 41274-2025 FSC-klagomål.docx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 41274-2025 FSC-klagomål mail.docx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 41274-2025 tillsynsbegäran.docx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 41274-2025 tillsynsbegäran mail.docx", "A 41274-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 46156-2025</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>45924</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>3.7</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Tvåblad</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46156-2025 artfynd.xlsx", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46156-2025 karta.png", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46156-2025 georefererad karta.tif", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46156-2025 FSC-klagomål.docx", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46156-2025 FSC-klagomål mail.docx", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46156-2025 tillsynsbegäran.docx", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46156-2025 tillsynsbegäran mail.docx", "A 46156-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 46123-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45924</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>5.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46123-2025 artfynd.xlsx", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46123-2025 karta.png", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46123-2025 georefererad karta.tif", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/knärot/A 46123-2025 karta knärot.png", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46123-2025 FSC-klagomål.docx", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46123-2025 FSC-klagomål mail.docx", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46123-2025 tillsynsbegäran.docx", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46123-2025 tillsynsbegäran mail.docx", "A 46123-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 46522-2025</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45926</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I14" t="n">
         <v>1.2</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Tibast</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 50403-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 22327-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45446</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Springkorn</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 50403-2022 artfynd.xlsx", "A 50403-2022")</f>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 50403-2022 karta.png", "A 50403-2022")</f>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 50403-2022 georefererad karta.tif", "A 50403-2022")</f>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 50403-2022 FSC-klagomål.docx", "A 50403-2022")</f>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 50403-2022 FSC-klagomål mail.docx", "A 50403-2022")</f>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 50403-2022 tillsynsbegäran.docx", "A 50403-2022")</f>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 50403-2022 tillsynsbegäran mail.docx", "A 50403-2022")</f>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 62852-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 51642-2021</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44462</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 51642-2021</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44462</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Vårstarr</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 51642-2021</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>44462</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>2.9</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Vårstarr</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9030-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44615</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 9030-2022 artfynd.xlsx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 9030-2022 karta.png", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 9030-2022 georefererad karta.tif", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 9030-2022 FSC-klagomål.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 9030-2022 FSC-klagomål mail.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 9030-2022 tillsynsbegäran.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 9030-2022 tillsynsbegäran mail.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 45164-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45191</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Skogsduva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32554-2026</t>
+          <t>A 60983-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2313,10 +2308,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46239</v>
+        <v>45261</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2328,19 +2323,14 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2374,35 +2364,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
     </row>
@@ -2426,7 +2416,7 @@
         <v>46239</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2519,7 +2509,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 13567-2025</t>
+          <t>A 32554-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2533,10 +2523,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45736</v>
+        <v>46239</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2548,17 +2538,22 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2573,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2589,42 +2584,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22327-2024</t>
+          <t>A 9030-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2638,10 +2633,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45446</v>
+        <v>44615</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2654,7 +2649,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2663,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2681,7 +2676,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2694,35 +2689,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 9030-2022 artfynd.xlsx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 9030-2022 karta.png", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 9030-2022 georefererad karta.tif", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 9030-2022 FSC-klagomål.docx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 9030-2022 FSC-klagomål mail.docx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 9030-2022 tillsynsbegäran.docx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 9030-2022 tillsynsbegäran mail.docx", "A 9030-2022")</f>
         <v/>
       </c>
     </row>
@@ -2746,7 +2741,7 @@
         <v>46255</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2851,7 +2846,7 @@
         <v>45519</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2939,7 +2934,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60983-2023</t>
+          <t>A 45164-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2953,10 +2948,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45261</v>
+        <v>45191</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2969,7 +2964,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3005,46 +3000,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 53521-2023</t>
+          <t>A 50403-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3058,10 +3053,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45230</v>
+        <v>44866</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3073,14 +3068,19 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3107,255 +3107,255 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
         <v>1</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 50403-2022 artfynd.xlsx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 50403-2022 karta.png", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 50403-2022 georefererad karta.tif", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 50403-2022 FSC-klagomål.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 50403-2022 FSC-klagomål mail.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 50403-2022 tillsynsbegäran.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 50403-2022 tillsynsbegäran mail.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 53521-2023</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45230</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>Skogsduva</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 53521-2023 artfynd.xlsx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 53521-2023 karta.png", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 53521-2023 georefererad karta.tif", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 53521-2023 FSC-klagomål.docx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 53521-2023 FSC-klagomål mail.docx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 53521-2023 tillsynsbegäran.docx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 53521-2023 tillsynsbegäran mail.docx", "A 53521-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 2230-2025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
         <v>45673</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
+      <c r="E27" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>1.6</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 2230-2025 artfynd.xlsx", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 2230-2025 karta.png", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 2230-2025 georefererad karta.tif", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 2230-2025 FSC-klagomål.docx", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 2230-2025 FSC-klagomål mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 2230-2025 tillsynsbegäran.docx", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 2230-2025 tillsynsbegäran mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 54444-2021</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>44473</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Ängshök</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
-    </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44573</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44573</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>44545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44480</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>44692</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>44627</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34431-2022</t>
+          <t>A 50901-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44792</v>
+        <v>45602</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3904,13 +3904,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3953,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12253-2024</t>
+          <t>A 3877-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3967,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45378</v>
+        <v>44951</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3983,7 +3978,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4026,7 +4021,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12254-2024</t>
+          <t>A 14210-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4040,10 +4035,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45378</v>
+        <v>45009</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4056,7 +4051,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4094,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 51475-2023</t>
+          <t>A 36401-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4113,10 +4108,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45221</v>
+        <v>45152</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4128,8 +4123,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17707-2023</t>
+          <t>A 50886-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45037</v>
+        <v>45602</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49566-2021</t>
+          <t>A 16304-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44455</v>
+        <v>45407</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4318,7 +4318,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 53518-2022</t>
+          <t>A 38300-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44879</v>
+        <v>45161</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54442-2021</t>
+          <t>A 43012-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4401,14 +4401,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44473</v>
+        <v>45567</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
         <v>44546</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 72558-2021</t>
+          <t>A 62129-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44546</v>
+        <v>46006</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 66977-2021</t>
+          <t>A 62123-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44522</v>
+        <v>46006</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 65921-2021</t>
+          <t>A 62391-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44517</v>
+        <v>46007</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4712,8 +4712,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4756,7 +4761,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50179-2023</t>
+          <t>A 24499-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4770,10 +4775,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45208</v>
+        <v>45798</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4786,7 +4791,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4829,7 +4834,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 50570-2023</t>
+          <t>A 18740-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4843,10 +4848,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45217</v>
+        <v>45763</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4859,7 +4864,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4902,7 +4907,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39950-2024</t>
+          <t>A 63445-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4916,10 +4921,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45553</v>
+        <v>46013</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4931,13 +4936,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4821-2023</t>
+          <t>A 22328-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44957</v>
+        <v>45446</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10980-2024</t>
+          <t>A 27232-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5063,14 +5063,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45370</v>
+        <v>45812</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28663-2025</t>
+          <t>A 64930-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45819</v>
+        <v>45282</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5199,7 +5199,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 43012-2024</t>
+          <t>A 28663-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5209,14 +5209,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45567</v>
+        <v>45819</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60964-2023</t>
+          <t>A 38299-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45261</v>
+        <v>45161</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5345,7 +5345,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15276-2022</t>
+          <t>A 43026-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44659</v>
+        <v>45909</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5374,13 +5374,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5423,7 +5418,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30468-2025</t>
+          <t>A 43032-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5437,10 +5432,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45827</v>
+        <v>45909</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5453,7 +5448,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5496,7 +5491,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1293-2023</t>
+          <t>A 30468-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5510,10 +5505,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44936</v>
+        <v>45827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5526,7 +5521,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5586,7 +5581,7 @@
         <v>45793</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5642,7 +5637,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31623-2025</t>
+          <t>A 4852-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5656,10 +5651,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45834</v>
+        <v>46048</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5672,7 +5667,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5715,7 +5710,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 64934-2023</t>
+          <t>A 4837-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5729,10 +5724,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45282</v>
+        <v>46048</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5805,7 +5800,7 @@
         <v>45834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5861,7 +5856,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59234-2022</t>
+          <t>A 31623-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5875,10 +5870,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44904</v>
+        <v>45834</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5890,13 +5885,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5939,7 +5929,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 55730-2022</t>
+          <t>A 40667-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5953,10 +5943,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44888</v>
+        <v>45170</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5969,7 +5959,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6012,7 +6002,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50339-2023</t>
+          <t>A 44757-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6026,10 +6016,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45216</v>
+        <v>45917</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6042,7 +6032,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6085,7 +6075,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15491-2024</t>
+          <t>A 44756-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6099,10 +6089,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45401</v>
+        <v>45917</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6114,13 +6104,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6163,7 +6148,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37806-2022</t>
+          <t>A 9125-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6177,10 +6162,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44810</v>
+        <v>44980</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6192,8 +6177,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6236,7 +6226,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 43032-2025</t>
+          <t>A 50339-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6250,10 +6240,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45909</v>
+        <v>45216</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6266,7 +6256,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6309,7 +6299,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 64930-2023</t>
+          <t>A 46164-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6323,10 +6313,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45282</v>
+        <v>45924</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6382,7 +6372,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24866-2023</t>
+          <t>A 46159-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6396,10 +6386,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45085</v>
+        <v>45924</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6412,7 +6402,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6455,7 +6445,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43026-2025</t>
+          <t>A 53518-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6469,10 +6459,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45909</v>
+        <v>44879</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6485,7 +6475,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6528,7 +6518,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37802-2022</t>
+          <t>A 46144-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6542,10 +6532,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44810</v>
+        <v>45924</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6558,7 +6548,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6601,7 +6591,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44756-2025</t>
+          <t>A 46521-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6615,10 +6605,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45917</v>
+        <v>45926</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6630,8 +6620,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6674,7 +6669,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44757-2025</t>
+          <t>A 15783-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6688,10 +6683,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45917</v>
+        <v>44663</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6704,7 +6699,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6747,7 +6742,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3087-2023</t>
+          <t>A 37806-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6761,10 +6756,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44946</v>
+        <v>44810</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6777,7 +6772,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6820,7 +6815,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46164-2025</t>
+          <t>A 50179-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6834,10 +6829,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45924</v>
+        <v>45208</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6850,7 +6845,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6893,7 +6888,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46144-2025</t>
+          <t>A 51475-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6907,10 +6902,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45924</v>
+        <v>45221</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6923,7 +6918,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6966,7 +6961,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 46159-2025</t>
+          <t>A 37802-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6980,10 +6975,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45924</v>
+        <v>44810</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6996,7 +6991,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7039,7 +7034,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58415-2021</t>
+          <t>A 7337-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7053,10 +7048,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44488</v>
+        <v>44971</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7069,7 +7064,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7112,7 +7107,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46521-2025</t>
+          <t>A 11064-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7126,10 +7121,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45926</v>
+        <v>46079</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7141,13 +7136,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7207,7 +7197,7 @@
         <v>45882</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7263,7 +7253,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35447-2023</t>
+          <t>A 51326-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7277,10 +7267,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45146</v>
+        <v>45950</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7293,7 +7283,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7336,7 +7326,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 51630-2021</t>
+          <t>A 51335-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7350,10 +7340,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44462</v>
+        <v>45950</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7366,7 +7356,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7409,7 +7399,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11064-2026</t>
+          <t>A 58412-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7423,10 +7413,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46079</v>
+        <v>45250</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7439,7 +7429,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7499,7 +7489,7 @@
         <v>45273</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7572,7 +7562,7 @@
         <v>45681</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7628,7 +7618,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 36401-2023</t>
+          <t>A 15032-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7642,10 +7632,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45152</v>
+        <v>46104</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7659,11 +7649,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7706,7 +7696,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51335-2025</t>
+          <t>A 14928-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7720,10 +7710,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45950</v>
+        <v>46104</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7733,6 +7723,11 @@
       <c r="G87" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -7779,7 +7774,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 51326-2025</t>
+          <t>A 16110-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7793,10 +7788,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45950</v>
+        <v>46108</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7809,7 +7804,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7852,7 +7847,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14928-2026</t>
+          <t>A 16173-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7866,10 +7861,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7887,7 +7882,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7930,7 +7925,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7337-2023</t>
+          <t>A 2418-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7944,10 +7939,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44971</v>
+        <v>45674</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7960,7 +7955,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8003,7 +7998,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15032-2026</t>
+          <t>A 65921-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8017,10 +8012,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46104</v>
+        <v>44517</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8030,11 +8025,6 @@
       <c r="G91" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -8081,7 +8071,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 44770-2025</t>
+          <t>A 44769-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8098,7 +8088,7 @@
         <v>45917</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8111,7 +8101,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8154,7 +8144,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44769-2025</t>
+          <t>A 17700-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8164,14 +8154,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45917</v>
+        <v>46121</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8184,7 +8174,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8227,7 +8217,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16110-2026</t>
+          <t>A 44770-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8237,14 +8227,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46108</v>
+        <v>45917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8257,7 +8247,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8300,7 +8290,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16173-2026</t>
+          <t>A 17699-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8314,10 +8304,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46111</v>
+        <v>46121</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8329,13 +8319,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8378,7 +8363,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 55939-2025</t>
+          <t>A 54442-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8392,10 +8377,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45973</v>
+        <v>44473</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8408,7 +8393,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8451,7 +8436,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60977-2023</t>
+          <t>A 18517-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8465,10 +8450,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45261</v>
+        <v>46127</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8480,8 +8465,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8524,7 +8514,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17699-2026</t>
+          <t>A 55939-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8538,10 +8528,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46121</v>
+        <v>45973</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8597,7 +8587,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17700-2026</t>
+          <t>A 29580-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8611,10 +8601,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46121</v>
+        <v>45825</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8627,7 +8617,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8687,7 +8677,7 @@
         <v>45979</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8760,7 +8750,7 @@
         <v>45979</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8816,7 +8806,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 57942-2025</t>
+          <t>A 50181-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8830,10 +8820,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45982</v>
+        <v>45208</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8846,7 +8836,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8889,7 +8879,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58321-2025</t>
+          <t>A 57942-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8903,10 +8893,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45985</v>
+        <v>45982</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8919,7 +8909,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8962,7 +8952,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 58756-2025</t>
+          <t>A 58310-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8976,10 +8966,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45986</v>
+        <v>45985</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8992,7 +8982,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9035,7 +9025,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58761-2025</t>
+          <t>A 58321-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9049,10 +9039,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45986</v>
+        <v>45985</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9065,7 +9055,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9108,7 +9098,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 58310-2025</t>
+          <t>A 58756-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9122,10 +9112,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9138,7 +9128,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9181,7 +9171,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 18517-2026</t>
+          <t>A 27251-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9195,10 +9185,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46127</v>
+        <v>45812</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9210,13 +9200,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9259,7 +9244,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59105-2025</t>
+          <t>A 58761-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9273,10 +9258,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45988</v>
+        <v>45986</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9289,7 +9274,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9332,7 +9317,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 60969-2023</t>
+          <t>A 59105-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9346,10 +9331,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45261</v>
+        <v>45988</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9362,7 +9347,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9405,7 +9390,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 38299-2023</t>
+          <t>A 41105-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9419,10 +9404,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45161</v>
+        <v>45898</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9435,7 +9420,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9478,7 +9463,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 39965-2025</t>
+          <t>A 1293-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9492,10 +9477,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45892</v>
+        <v>44936</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9508,7 +9493,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9551,7 +9536,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 27255-2025</t>
+          <t>A 39965-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9565,10 +9550,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45812</v>
+        <v>45892</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9581,7 +9566,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9624,7 +9609,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 27251-2025</t>
+          <t>A 28321-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9638,10 +9623,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45812</v>
+        <v>45818</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9654,7 +9639,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9697,7 +9682,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62129-2025</t>
+          <t>A 27255-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9711,10 +9696,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46006</v>
+        <v>45812</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9727,7 +9712,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9770,7 +9755,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 62123-2025</t>
+          <t>A 41337-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9784,10 +9769,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46006</v>
+        <v>45174</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9800,7 +9785,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9843,7 +9828,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62391-2025</t>
+          <t>A 10984-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9857,10 +9842,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46007</v>
+        <v>45370</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9872,13 +9857,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>8.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9921,7 +9901,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58800-2022</t>
+          <t>A 20357-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9931,14 +9911,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44903</v>
+        <v>46139</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9951,7 +9931,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9994,7 +9974,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 6785-2024</t>
+          <t>A 10980-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10008,10 +9988,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45342</v>
+        <v>45370</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10023,13 +10003,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10072,7 +10047,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 11944-2024</t>
+          <t>A 31010-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10086,10 +10061,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45376</v>
+        <v>44768</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10102,7 +10077,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10145,7 +10120,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 41105-2025</t>
+          <t>A 11944-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10159,10 +10134,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45898</v>
+        <v>45376</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10175,7 +10150,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10218,7 +10193,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 29580-2025</t>
+          <t>A 62447-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10232,10 +10207,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45825</v>
+        <v>46007</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10247,8 +10222,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10291,7 +10271,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 63445-2025</t>
+          <t>A 3681-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10305,10 +10285,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46013</v>
+        <v>45681</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10321,7 +10301,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10364,7 +10344,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59411-2022</t>
+          <t>A 59234-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10374,14 +10354,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44907</v>
+        <v>44904</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10399,7 +10379,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10442,7 +10422,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58412-2023</t>
+          <t>A 2715-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10456,10 +10436,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45250</v>
+        <v>44580</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10472,7 +10452,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10515,7 +10495,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59410-2022</t>
+          <t>A 961-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10525,14 +10505,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44907</v>
+        <v>45301</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10544,13 +10524,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10593,7 +10568,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 45918-2024</t>
+          <t>A 21518-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10607,10 +10582,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45580</v>
+        <v>46148</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10623,7 +10598,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10666,7 +10641,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 31010-2022</t>
+          <t>A 1013-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10680,10 +10655,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44768</v>
+        <v>45666</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10696,7 +10671,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10739,7 +10714,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 20357-2026</t>
+          <t>A 32581-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10753,10 +10728,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46139</v>
+        <v>45838</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10769,7 +10744,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10829,7 +10804,7 @@
         <v>45269</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10885,7 +10860,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 4837-2026</t>
+          <t>A 2073-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10899,10 +10874,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46048</v>
+        <v>46036</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10915,7 +10890,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10958,7 +10933,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 4852-2026</t>
+          <t>A 50883-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10972,10 +10947,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46048</v>
+        <v>45602</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10988,7 +10963,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11031,7 +11006,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62447-2025</t>
+          <t>A 50896-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11045,10 +11020,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46007</v>
+        <v>45602</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11060,13 +11035,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11109,7 +11079,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 28321-2025</t>
+          <t>A 1011-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11123,10 +11093,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45818</v>
+        <v>45666</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11139,7 +11109,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11182,7 +11152,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 14210-2023</t>
+          <t>A 24139-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11196,10 +11166,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45009</v>
+        <v>46168</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11211,8 +11181,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11255,7 +11230,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35404-2023</t>
+          <t>A 24457-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11269,10 +11244,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45146</v>
+        <v>46170</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11284,8 +11259,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11328,7 +11308,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21518-2026</t>
+          <t>A 25031-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11342,10 +11322,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46148</v>
+        <v>46174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11357,8 +11337,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11401,7 +11386,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 68095-2021</t>
+          <t>A 24786-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11415,10 +11400,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44526</v>
+        <v>46171</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11430,8 +11415,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11474,7 +11464,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 49915-2024</t>
+          <t>A 24900-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11488,10 +11478,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45597</v>
+        <v>46174</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11503,8 +11493,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11547,7 +11542,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32581-2025</t>
+          <t>A 24894-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11561,10 +11556,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45838</v>
+        <v>46174</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11576,8 +11571,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11620,7 +11620,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 37631-2023</t>
+          <t>A 24888-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11634,10 +11634,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45159</v>
+        <v>46174</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11649,8 +11649,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11693,7 +11698,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 2073-2026</t>
+          <t>A 24896-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11707,10 +11712,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46036</v>
+        <v>46174</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11722,8 +11727,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11766,7 +11776,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 11270-2022</t>
+          <t>A 24903-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11776,14 +11786,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44629</v>
+        <v>46174</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11795,8 +11805,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11839,7 +11854,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 41337-2023</t>
+          <t>A 25503-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11853,10 +11868,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45174</v>
+        <v>46177</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11868,8 +11883,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11912,7 +11932,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 2800-2025</t>
+          <t>A 27126-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11922,14 +11942,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45677</v>
+        <v>46188</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11941,8 +11961,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11985,7 +12010,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 8658-2022</t>
+          <t>A 27137-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11999,10 +12024,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44613</v>
+        <v>46188</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12014,8 +12039,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12058,7 +12088,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 2418-2025</t>
+          <t>A 32558-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12072,10 +12102,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45674</v>
+        <v>46239</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12087,8 +12117,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12131,7 +12166,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 2231-2025</t>
+          <t>A 32317-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12145,10 +12180,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45673</v>
+        <v>46237</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12161,7 +12196,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12204,7 +12239,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 24139-2026</t>
+          <t>A 32574-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12218,10 +12253,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46168</v>
+        <v>46239</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12282,7 +12317,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 1011-2025</t>
+          <t>A 32564-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12296,10 +12331,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45666</v>
+        <v>46239</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12311,8 +12346,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12355,7 +12395,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24786-2026</t>
+          <t>A 28652-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12369,10 +12409,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46171</v>
+        <v>46198</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12390,7 +12430,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12433,7 +12473,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24457-2026</t>
+          <t>A 3087-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12447,10 +12487,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46170</v>
+        <v>44946</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12462,13 +12502,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12511,7 +12546,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 24903-2026</t>
+          <t>A 28525-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12521,14 +12556,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46174</v>
+        <v>46197</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12546,7 +12581,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12589,7 +12624,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 24894-2026</t>
+          <t>A 33010-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12603,10 +12638,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46174</v>
+        <v>46244</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12618,13 +12653,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12667,7 +12697,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 25031-2026</t>
+          <t>A 4314-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12677,14 +12707,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46174</v>
+        <v>45324</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12698,11 +12728,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12745,7 +12775,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24888-2026</t>
+          <t>A 12769-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12759,10 +12789,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46174</v>
+        <v>45384</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12774,13 +12804,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12823,7 +12848,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24896-2026</t>
+          <t>A 34172-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12837,10 +12862,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46174</v>
+        <v>46253</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12858,7 +12883,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12901,7 +12926,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 24900-2026</t>
+          <t>A 49915-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12915,10 +12940,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46174</v>
+        <v>45597</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12930,13 +12955,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12979,7 +12999,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 25503-2026</t>
+          <t>A 44753-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12993,10 +13013,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46177</v>
+        <v>45917</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13008,13 +13028,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13057,7 +13072,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 11478-2024</t>
+          <t>A 31161-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13071,10 +13086,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45372</v>
+        <v>46216</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13087,7 +13102,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13130,7 +13145,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27126-2026</t>
+          <t>A 34794-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13144,10 +13159,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46188</v>
+        <v>46258</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13165,7 +13180,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13208,7 +13223,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 27137-2026</t>
+          <t>A 34730-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13222,10 +13237,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46188</v>
+        <v>46258</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13243,7 +13258,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13286,7 +13301,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 50181-2023</t>
+          <t>A 34748-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13300,10 +13315,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45208</v>
+        <v>46258</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13315,8 +13330,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13359,7 +13379,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 53520-2022</t>
+          <t>A 31193-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13373,10 +13393,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44879</v>
+        <v>46217</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13389,7 +13409,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13432,7 +13452,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 32317-2026</t>
+          <t>A 31192-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13446,10 +13466,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46237</v>
+        <v>46217</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13462,7 +13482,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13505,7 +13525,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 52655-2023</t>
+          <t>A 41819-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13515,14 +13535,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45225</v>
+        <v>45176</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13535,7 +13555,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13578,7 +13598,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 32564-2026</t>
+          <t>A 58415-2021</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13592,10 +13612,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46239</v>
+        <v>44488</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13607,13 +13627,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13656,7 +13671,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22307-2024</t>
+          <t>A 60917-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13670,10 +13685,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45446</v>
+        <v>44908</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13686,7 +13701,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13729,7 +13744,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 32558-2026</t>
+          <t>A 22307-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13743,10 +13758,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46239</v>
+        <v>45446</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13758,13 +13773,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13807,7 +13817,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 3877-2023</t>
+          <t>A 36206-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13821,10 +13831,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44951</v>
+        <v>46267</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13837,7 +13847,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13880,7 +13890,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 28525-2026</t>
+          <t>A 36209-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13894,10 +13904,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46197</v>
+        <v>46267</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13909,13 +13919,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13958,7 +13963,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 61012-2023</t>
+          <t>A 34167-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13972,10 +13977,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45259</v>
+        <v>46253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13987,8 +13992,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14031,7 +14041,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 15783-2022</t>
+          <t>A 34431-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14045,10 +14055,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44663</v>
+        <v>44792</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14060,8 +14070,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14104,7 +14119,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 34521-2024</t>
+          <t>A 34162-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14118,10 +14133,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45525</v>
+        <v>46253</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14133,8 +14148,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14177,7 +14197,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 32574-2026</t>
+          <t>A 34834-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14191,10 +14211,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46239</v>
+        <v>46258</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14206,13 +14226,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14255,7 +14270,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 1013-2025</t>
+          <t>A 37226-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14269,10 +14284,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45666</v>
+        <v>46274</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14284,8 +14299,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14328,7 +14348,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 33010-2026</t>
+          <t>A 37355-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14342,10 +14362,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46244</v>
+        <v>46275</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14358,7 +14378,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14401,7 +14421,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28652-2026</t>
+          <t>A 37174-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14415,10 +14435,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46198</v>
+        <v>46274</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14432,11 +14452,11 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14479,7 +14499,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 2715-2022</t>
+          <t>A 37364-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14493,10 +14513,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44580</v>
+        <v>46275</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14509,7 +14529,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14552,7 +14572,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 44753-2025</t>
+          <t>A 60969-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14566,10 +14586,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45917</v>
+        <v>45261</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14582,7 +14602,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14625,7 +14645,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 4314-2024</t>
+          <t>A 31928-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14635,14 +14655,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45324</v>
+        <v>46232</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14654,13 +14674,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14703,7 +14718,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34172-2026</t>
+          <t>A 37353-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14717,10 +14732,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14732,13 +14747,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14781,7 +14791,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34730-2026</t>
+          <t>A 37367-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14795,10 +14805,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46258</v>
+        <v>46275</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14810,13 +14820,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14859,7 +14864,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 3681-2025</t>
+          <t>A 31929-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14873,10 +14878,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45681</v>
+        <v>46232</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14889,7 +14894,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14932,7 +14937,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 34748-2026</t>
+          <t>A 31930-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14946,10 +14951,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46258</v>
+        <v>46232</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14961,13 +14966,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15010,7 +15010,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34794-2026</t>
+          <t>A 60964-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15020,14 +15020,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46258</v>
+        <v>45261</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15039,13 +15039,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15088,7 +15083,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 41819-2023</t>
+          <t>A 37888-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15102,10 +15097,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45176</v>
+        <v>46279</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15117,8 +15112,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15161,7 +15161,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 50883-2024</t>
+          <t>A 28131-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15175,10 +15175,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45602</v>
+        <v>46195</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15234,7 +15234,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 50896-2024</t>
+          <t>A 42042-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15248,10 +15248,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45602</v>
+        <v>45177</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15307,7 +15307,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 31161-2026</t>
+          <t>A 64934-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15321,10 +15321,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46216</v>
+        <v>45282</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15380,7 +15380,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 10984-2024</t>
+          <t>A 37631-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15394,10 +15394,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45370</v>
+        <v>45159</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15453,7 +15453,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 31192-2026</t>
+          <t>A 2231-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15467,10 +15467,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46217</v>
+        <v>45673</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15526,7 +15526,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 31193-2026</t>
+          <t>A 59410-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15536,14 +15536,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46217</v>
+        <v>44907</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15555,8 +15555,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15599,7 +15604,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 15467-2023</t>
+          <t>A 59411-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15609,14 +15614,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45020</v>
+        <v>44907</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15628,8 +15633,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15672,7 +15682,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 60917-2022</t>
+          <t>A 2800-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15686,10 +15696,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44908</v>
+        <v>45677</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15702,7 +15712,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15745,7 +15755,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 40667-2023</t>
+          <t>A 34521-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15759,10 +15769,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45170</v>
+        <v>45525</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15775,7 +15785,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15818,7 +15828,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 42042-2023</t>
+          <t>A 8658-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15832,10 +15842,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45177</v>
+        <v>44613</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15848,7 +15858,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15891,7 +15901,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 36209-2026</t>
+          <t>A 50570-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15905,10 +15915,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46267</v>
+        <v>45217</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15964,7 +15974,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 50886-2024</t>
+          <t>A 60977-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15978,10 +15988,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45602</v>
+        <v>45261</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15994,7 +16004,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16037,7 +16047,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 50901-2024</t>
+          <t>A 12253-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16051,10 +16061,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45602</v>
+        <v>45378</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16067,7 +16077,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16110,7 +16120,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 36206-2026</t>
+          <t>A 12254-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16124,10 +16134,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46267</v>
+        <v>45378</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16140,7 +16150,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16183,7 +16193,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 12769-2024</t>
+          <t>A 52655-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16193,14 +16203,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45384</v>
+        <v>45225</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16256,7 +16266,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 50906-2024</t>
+          <t>A 24866-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16270,10 +16280,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45602</v>
+        <v>45085</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16286,7 +16296,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16329,7 +16339,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 34167-2026</t>
+          <t>A 39950-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16343,10 +16353,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46253</v>
+        <v>45553</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16360,11 +16370,11 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16407,7 +16417,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 9125-2023</t>
+          <t>A 11270-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16421,10 +16431,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44980</v>
+        <v>44629</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16436,13 +16446,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16485,7 +16490,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 34162-2026</t>
+          <t>A 68095-2021</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16499,10 +16504,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46253</v>
+        <v>44526</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16514,13 +16519,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16563,7 +16563,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 16304-2024</t>
+          <t>A 58800-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16573,14 +16573,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45407</v>
+        <v>44903</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16636,7 +16636,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37226-2026</t>
+          <t>A 4821-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16650,10 +16650,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46274</v>
+        <v>44957</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16665,13 +16665,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16714,7 +16709,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 37174-2026</t>
+          <t>A 11478-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16728,10 +16723,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46274</v>
+        <v>45372</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16743,13 +16738,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16792,7 +16782,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 34834-2026</t>
+          <t>A 51630-2021</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16806,10 +16796,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46258</v>
+        <v>44462</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16822,7 +16812,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16865,7 +16855,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 22328-2024</t>
+          <t>A 15491-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16879,10 +16869,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45446</v>
+        <v>45401</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16894,8 +16884,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16938,7 +16933,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 31929-2026</t>
+          <t>A 45918-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16952,10 +16947,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46232</v>
+        <v>45580</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16968,7 +16963,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17011,7 +17006,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37367-2026</t>
+          <t>A 50906-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17025,10 +17020,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46275</v>
+        <v>45602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17041,7 +17036,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17084,7 +17079,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 28131-2026</t>
+          <t>A 6785-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17098,10 +17093,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46195</v>
+        <v>45342</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17113,8 +17108,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17157,7 +17157,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 37364-2026</t>
+          <t>A 55730-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46275</v>
+        <v>44888</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17230,7 +17230,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 37353-2026</t>
+          <t>A 53520-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17244,10 +17244,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46275</v>
+        <v>44879</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17303,7 +17303,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 37355-2026</t>
+          <t>A 35404-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17317,10 +17317,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46275</v>
+        <v>45146</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17376,7 +17376,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 79-2024</t>
+          <t>A 61012-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17386,14 +17386,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45293</v>
+        <v>45259</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17449,7 +17449,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 31928-2026</t>
+          <t>A 15467-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17463,10 +17463,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46232</v>
+        <v>45020</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17522,7 +17522,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 961-2024</t>
+          <t>A 72558-2021</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17536,10 +17536,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45301</v>
+        <v>44546</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 31930-2026</t>
+          <t>A 35447-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17609,10 +17609,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46232</v>
+        <v>45146</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 38300-2023</t>
+          <t>A 79-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17678,14 +17678,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45161</v>
+        <v>45293</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17741,7 +17741,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 46248-2024</t>
+          <t>A 66977-2021</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17755,10 +17755,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45581</v>
+        <v>44522</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17814,7 +17814,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 61575-2023</t>
+          <t>A 49566-2021</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17828,10 +17828,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45261</v>
+        <v>44455</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17887,7 +17887,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 49971-2023</t>
+          <t>A 15276-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17901,10 +17901,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45215</v>
+        <v>44659</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17916,8 +17916,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17960,7 +17965,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 38278-2024</t>
+          <t>A 17707-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17970,14 +17975,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45545</v>
+        <v>45037</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17990,7 +17995,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18033,7 +18038,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 12675-2024</t>
+          <t>A 46248-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18047,10 +18052,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45384</v>
+        <v>45581</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18063,7 +18068,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18106,7 +18111,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 37083-2024</t>
+          <t>A 61575-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18120,10 +18125,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45539</v>
+        <v>45261</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18136,7 +18141,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18179,7 +18184,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 13560-2025</t>
+          <t>A 34664-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18193,10 +18198,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45736</v>
+        <v>45526</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18209,7 +18214,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18252,7 +18257,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 34664-2024</t>
+          <t>A 37083-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18266,10 +18271,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45526</v>
+        <v>45539</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18282,7 +18287,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18325,7 +18330,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 23114-2025</t>
+          <t>A 12675-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18339,10 +18344,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45791</v>
+        <v>45384</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18355,7 +18360,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18398,7 +18403,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 2749-2024</t>
+          <t>A 49971-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18412,10 +18417,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45314</v>
+        <v>45215</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18428,7 +18433,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18471,7 +18476,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 57284-2024</t>
+          <t>A 13560-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18485,10 +18490,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45629</v>
+        <v>45736</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18501,7 +18506,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18544,7 +18549,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 24499-2025</t>
+          <t>A 38278-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18554,14 +18559,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45798</v>
+        <v>45545</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18574,7 +18579,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18617,7 +18622,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 18740-2025</t>
+          <t>A 23114-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18631,10 +18636,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45763</v>
+        <v>45791</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18647,7 +18652,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18690,7 +18695,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 27232-2025</t>
+          <t>A 57284-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18700,14 +18705,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45812</v>
+        <v>45629</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18720,7 +18725,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18760,83 +18765,156 @@
       </c>
       <c r="V235" s="2" t="inlineStr"/>
     </row>
-    <row r="236">
+    <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
+          <t>A 2749-2024</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D236" s="1" t="n">
+        <v>45314</v>
+      </c>
+      <c r="E236" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>0</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" t="n">
+        <v>0</v>
+      </c>
+      <c r="T236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="n">
+        <v>0</v>
+      </c>
+      <c r="V236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
           <t>S 1827-2026</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C237" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D236" s="1" t="n">
+      <c r="D237" s="1" t="n">
         <v>46197</v>
       </c>
-      <c r="E236" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
+      <c r="E237" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I236" t="n">
+      <c r="I237" t="n">
         <v>3.8</v>
       </c>
-      <c r="J236" t="n">
-        <v>0</v>
-      </c>
-      <c r="K236" t="n">
-        <v>0</v>
-      </c>
-      <c r="L236" t="n">
-        <v>0</v>
-      </c>
-      <c r="M236" t="n">
-        <v>0</v>
-      </c>
-      <c r="N236" t="n">
-        <v>0</v>
-      </c>
-      <c r="O236" t="n">
-        <v>0</v>
-      </c>
-      <c r="P236" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
-      <c r="R236" t="n">
-        <v>0</v>
-      </c>
-      <c r="S236" t="n">
-        <v>0</v>
-      </c>
-      <c r="T236" t="n">
-        <v>0</v>
-      </c>
-      <c r="U236" t="n">
-        <v>0</v>
-      </c>
-      <c r="V236" s="2" t="inlineStr"/>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" t="n">
+        <v>0</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>0</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0</v>
+      </c>
+      <c r="S237" t="n">
+        <v>0</v>
+      </c>
+      <c r="T237" t="n">
+        <v>0</v>
+      </c>
+      <c r="U237" t="n">
+        <v>0</v>
+      </c>
+      <c r="V237" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13567-2025</t>
+          <t>A 45164-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45736</v>
+        <v>45191</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1191,1215 +1191,1220 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 7564-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45705</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 7564-2025 artfynd.xlsx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 7564-2025 karta.png", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 7564-2025 georefererad karta.tif", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 7564-2025 FSC-klagomål.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 7564-2025 FSC-klagomål mail.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 7564-2025 tillsynsbegäran.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 7564-2025 tillsynsbegäran mail.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 41274-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45898</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 41274-2025 artfynd.xlsx", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 41274-2025 karta.png", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 41274-2025 georefererad karta.tif", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 41274-2025 FSC-klagomål.docx", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 41274-2025 FSC-klagomål mail.docx", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 41274-2025 tillsynsbegäran.docx", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 41274-2025 tillsynsbegäran mail.docx", "A 41274-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 46156-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45924</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46156-2025 artfynd.xlsx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46156-2025 karta.png", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46156-2025 georefererad karta.tif", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46156-2025 FSC-klagomål.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46156-2025 FSC-klagomål mail.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46156-2025 tillsynsbegäran.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46156-2025 tillsynsbegäran mail.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 46123-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45924</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46123-2025 artfynd.xlsx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46123-2025 karta.png", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46123-2025 georefererad karta.tif", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/knärot/A 46123-2025 karta knärot.png", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46123-2025 FSC-klagomål.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46123-2025 FSC-klagomål mail.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46123-2025 tillsynsbegäran.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46123-2025 tillsynsbegäran mail.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 46522-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45926</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 51642-2021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44462</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 51642-2021</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44462</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 62852-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 50403-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 50403-2022 artfynd.xlsx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 50403-2022 karta.png", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 50403-2022 georefererad karta.tif", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 50403-2022 FSC-klagomål.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 50403-2022 FSC-klagomål mail.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 50403-2022 tillsynsbegäran.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 50403-2022 tillsynsbegäran mail.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 13567-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 62852-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 22327-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45446</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 7564-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45705</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Solvända</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 7564-2025 artfynd.xlsx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 7564-2025 karta.png", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 7564-2025 georefererad karta.tif", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 7564-2025 FSC-klagomål.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 7564-2025 FSC-klagomål mail.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 7564-2025 tillsynsbegäran.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 7564-2025 tillsynsbegäran mail.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 54444-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44473</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ängshök</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 41274-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45898</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 41274-2025 artfynd.xlsx", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 41274-2025 karta.png", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 41274-2025 georefererad karta.tif", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 41274-2025 FSC-klagomål.docx", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 41274-2025 FSC-klagomål mail.docx", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 41274-2025 tillsynsbegäran.docx", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 41274-2025 tillsynsbegäran mail.docx", "A 41274-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 46156-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45924</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46156-2025 artfynd.xlsx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46156-2025 karta.png", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46156-2025 georefererad karta.tif", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46156-2025 FSC-klagomål.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46156-2025 FSC-klagomål mail.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46156-2025 tillsynsbegäran.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46156-2025 tillsynsbegäran mail.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 46123-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45924</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46123-2025 artfynd.xlsx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46123-2025 karta.png", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46123-2025 georefererad karta.tif", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/knärot/A 46123-2025 karta knärot.png", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46123-2025 FSC-klagomål.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46123-2025 FSC-klagomål mail.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46123-2025 tillsynsbegäran.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46123-2025 tillsynsbegäran mail.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 46522-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45926</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 22327-2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45446</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Svinrot</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 51642-2021</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44462</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Vårstarr</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 51642-2021</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44462</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Vårstarr</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 60983-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32573-2026</t>
+          <t>A 32554-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2416,7 +2421,7 @@
         <v>46239</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2434,16 +2439,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2458,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2474,148 +2479,148 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 32573-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>Lunglav</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32573-2026 artfynd.xlsx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32573-2026 karta.png", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32573-2026 georefererad karta.tif", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32573-2026 FSC-klagomål.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32573-2026 FSC-klagomål mail.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32573-2026 tillsynsbegäran.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32573-2026 tillsynsbegäran mail.docx", "A 32573-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 32554-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Purpurknipprot</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
@@ -2636,7 +2641,7 @@
         <v>44615</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2741,7 +2746,7 @@
         <v>46255</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2846,7 +2851,7 @@
         <v>45519</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2934,7 +2939,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45164-2023</t>
+          <t>A 60983-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2948,10 +2953,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45191</v>
+        <v>45261</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2964,7 +2969,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3000,46 +3005,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 50403-2022</t>
+          <t>A 53521-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3053,10 +3058,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44866</v>
+        <v>45230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3068,19 +3073,14 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3107,49 +3107,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 50403-2022 artfynd.xlsx", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 53521-2023 artfynd.xlsx", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 50403-2022 karta.png", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 53521-2023 karta.png", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 50403-2022 georefererad karta.tif", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 53521-2023 georefererad karta.tif", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 50403-2022 FSC-klagomål.docx", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 53521-2023 FSC-klagomål.docx", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 50403-2022 FSC-klagomål mail.docx", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 53521-2023 FSC-klagomål mail.docx", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 50403-2022 tillsynsbegäran.docx", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 53521-2023 tillsynsbegäran.docx", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 50403-2022 tillsynsbegäran mail.docx", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 53521-2023 tillsynsbegäran mail.docx", "A 53521-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53521-2023</t>
+          <t>A 2230-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45230</v>
+        <v>45673</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3219,42 +3219,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 53521-2023 artfynd.xlsx", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 2230-2025 artfynd.xlsx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 53521-2023 karta.png", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 2230-2025 karta.png", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 53521-2023 georefererad karta.tif", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 2230-2025 georefererad karta.tif", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 53521-2023 FSC-klagomål.docx", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 2230-2025 FSC-klagomål.docx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 53521-2023 FSC-klagomål mail.docx", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 2230-2025 FSC-klagomål mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 53521-2023 tillsynsbegäran.docx", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 2230-2025 tillsynsbegäran.docx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 53521-2023 tillsynsbegäran mail.docx", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 2230-2025 tillsynsbegäran mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2230-2025</t>
+          <t>A 54444-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45673</v>
+        <v>44473</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3320,39 +3320,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängshök</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 2230-2025 artfynd.xlsx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 2230-2025 karta.png", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 2230-2025 georefererad karta.tif", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 2230-2025 FSC-klagomål.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 2230-2025 FSC-klagomål mail.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 2230-2025 tillsynsbegäran.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 2230-2025 tillsynsbegäran mail.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
         <v/>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
         <v>44573</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44573</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>44545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 56458-2021</t>
+          <t>A 51475-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44480</v>
+        <v>45221</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19352-2022</t>
+          <t>A 12253-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44692</v>
+        <v>45378</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10950-2022</t>
+          <t>A 12254-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44627</v>
+        <v>45378</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3875,7 +3875,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50901-2024</t>
+          <t>A 56458-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45602</v>
+        <v>44480</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3877-2023</t>
+          <t>A 17707-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44951</v>
+        <v>45037</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14210-2023</t>
+          <t>A 49566-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45009</v>
+        <v>44455</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 36401-2023</t>
+          <t>A 53518-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45152</v>
+        <v>44879</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4123,13 +4123,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4172,7 +4167,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50886-2024</t>
+          <t>A 19352-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4186,10 +4181,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45602</v>
+        <v>44692</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4202,7 +4197,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4245,7 +4240,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16304-2024</t>
+          <t>A 10950-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4259,10 +4254,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45407</v>
+        <v>44627</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4275,7 +4270,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4318,7 +4313,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38300-2023</t>
+          <t>A 38199-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4332,10 +4327,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45161</v>
+        <v>45882</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4348,7 +4343,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4391,7 +4386,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 43012-2024</t>
+          <t>A 34431-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4401,14 +4396,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45567</v>
+        <v>44792</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4420,8 +4415,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 72563-2021</t>
+          <t>A 54442-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44546</v>
+        <v>44473</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62129-2025</t>
+          <t>A 11478-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46006</v>
+        <v>45372</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62123-2025</t>
+          <t>A 72563-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46006</v>
+        <v>44546</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62391-2025</t>
+          <t>A 11064-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46007</v>
+        <v>46079</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4712,13 +4712,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>8.300000000000001</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4761,7 +4756,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 24499-2025</t>
+          <t>A 72558-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4775,10 +4770,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45798</v>
+        <v>44546</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4791,7 +4786,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4834,7 +4829,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18740-2025</t>
+          <t>A 66977-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4848,10 +4843,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45763</v>
+        <v>44522</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4864,7 +4859,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4907,7 +4902,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 63445-2025</t>
+          <t>A 14928-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4921,10 +4916,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46013</v>
+        <v>46104</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4936,8 +4931,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22328-2024</t>
+          <t>A 43032-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45446</v>
+        <v>45909</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27232-2025</t>
+          <t>A 43026-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5063,14 +5063,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45812</v>
+        <v>45909</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 64930-2023</t>
+          <t>A 15032-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45282</v>
+        <v>46104</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5155,8 +5155,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5199,7 +5204,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28663-2025</t>
+          <t>A 65921-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5213,10 +5218,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45819</v>
+        <v>44517</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5229,7 +5234,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5272,7 +5277,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38299-2023</t>
+          <t>A 16110-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5286,10 +5291,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45161</v>
+        <v>46108</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5302,7 +5307,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5345,7 +5350,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43026-2025</t>
+          <t>A 44756-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5359,10 +5364,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45909</v>
+        <v>45917</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5375,7 +5380,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5418,7 +5423,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43032-2025</t>
+          <t>A 50179-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5432,10 +5437,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45909</v>
+        <v>45208</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5448,7 +5453,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5491,7 +5496,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30468-2025</t>
+          <t>A 44757-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5505,10 +5510,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45827</v>
+        <v>45917</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5521,7 +5526,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5564,7 +5569,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23781-2025</t>
+          <t>A 50570-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5578,10 +5583,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45793</v>
+        <v>45217</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5594,7 +5599,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5637,7 +5642,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4852-2026</t>
+          <t>A 16173-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5651,10 +5656,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46048</v>
+        <v>46111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5666,8 +5671,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5710,7 +5720,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4837-2026</t>
+          <t>A 50181-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5724,10 +5734,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46048</v>
+        <v>45208</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5783,7 +5793,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31624-2025</t>
+          <t>A 39950-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5797,10 +5807,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45834</v>
+        <v>45553</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5812,8 +5822,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5856,7 +5871,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31623-2025</t>
+          <t>A 53520-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5870,10 +5885,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45834</v>
+        <v>44879</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5886,7 +5901,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5929,7 +5944,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 40667-2023</t>
+          <t>A 4821-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5943,10 +5958,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45170</v>
+        <v>44957</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5959,7 +5974,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6002,7 +6017,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44757-2025</t>
+          <t>A 46164-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6016,10 +6031,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6032,7 +6047,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6075,7 +6090,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44756-2025</t>
+          <t>A 10980-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6089,10 +6104,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45917</v>
+        <v>45370</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6105,7 +6120,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6148,7 +6163,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9125-2023</t>
+          <t>A 17699-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6162,10 +6177,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44980</v>
+        <v>46121</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6177,13 +6192,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6226,7 +6236,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 50339-2023</t>
+          <t>A 17700-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6240,10 +6250,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45216</v>
+        <v>46121</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6256,7 +6266,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6299,7 +6309,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 46164-2025</t>
+          <t>A 46144-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6316,7 +6326,7 @@
         <v>45924</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6329,7 +6339,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6372,7 +6382,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46159-2025</t>
+          <t>A 43012-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6382,14 +6392,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45924</v>
+        <v>45567</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6402,7 +6412,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6445,7 +6455,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53518-2022</t>
+          <t>A 46159-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6459,10 +6469,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44879</v>
+        <v>45924</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6475,7 +6485,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6518,7 +6528,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 46144-2025</t>
+          <t>A 60964-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6532,10 +6542,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45924</v>
+        <v>45261</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6548,7 +6558,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6591,7 +6601,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 46521-2025</t>
+          <t>A 52655-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6601,14 +6611,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45926</v>
+        <v>45225</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6620,13 +6630,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6669,7 +6674,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15783-2022</t>
+          <t>A 15276-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6683,10 +6688,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44663</v>
+        <v>44659</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6698,8 +6703,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6742,7 +6752,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37806-2022</t>
+          <t>A 46521-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6756,10 +6766,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44810</v>
+        <v>45926</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6771,8 +6781,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6815,7 +6830,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50179-2023</t>
+          <t>A 22307-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6829,10 +6844,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45208</v>
+        <v>45446</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6845,7 +6860,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6888,7 +6903,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51475-2023</t>
+          <t>A 3877-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6902,10 +6917,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45221</v>
+        <v>44951</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6918,7 +6933,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6961,7 +6976,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37802-2022</t>
+          <t>A 18517-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6975,10 +6990,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44810</v>
+        <v>46127</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6990,8 +7005,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7034,7 +7054,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7337-2023</t>
+          <t>A 1293-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7048,10 +7068,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44971</v>
+        <v>44936</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7064,7 +7084,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7107,7 +7127,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11064-2026</t>
+          <t>A 61012-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7121,10 +7141,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46079</v>
+        <v>45259</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7137,7 +7157,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7180,7 +7200,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38199-2025</t>
+          <t>A 15783-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7194,10 +7214,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45882</v>
+        <v>44663</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7210,7 +7230,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7253,7 +7273,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 51326-2025</t>
+          <t>A 34521-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7267,10 +7287,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45950</v>
+        <v>45525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7283,7 +7303,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7326,7 +7346,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 51335-2025</t>
+          <t>A 64934-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7340,10 +7360,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45950</v>
+        <v>45282</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7356,7 +7376,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7399,7 +7419,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58412-2023</t>
+          <t>A 39965-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7413,10 +7433,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45250</v>
+        <v>45892</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7429,7 +7449,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7472,7 +7492,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 63449-2023</t>
+          <t>A 59234-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7482,14 +7502,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45273</v>
+        <v>44904</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7501,8 +7521,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7545,7 +7570,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3678-2025</t>
+          <t>A 27255-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7559,10 +7584,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45681</v>
+        <v>45812</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7575,7 +7600,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7618,7 +7643,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15032-2026</t>
+          <t>A 27251-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7632,10 +7657,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46104</v>
+        <v>45812</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7647,13 +7672,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7696,7 +7716,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14928-2026</t>
+          <t>A 51335-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7710,10 +7730,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46104</v>
+        <v>45950</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7723,11 +7743,6 @@
       <c r="G87" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -7774,7 +7789,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16110-2026</t>
+          <t>A 55730-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7788,10 +7803,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46108</v>
+        <v>44888</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7804,7 +7819,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7847,7 +7862,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 16173-2026</t>
+          <t>A 51326-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7861,10 +7876,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46111</v>
+        <v>45950</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7876,13 +7891,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7925,7 +7935,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2418-2025</t>
+          <t>A 41105-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7939,10 +7949,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45674</v>
+        <v>45898</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +8008,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 65921-2021</t>
+          <t>A 1013-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8012,10 +8022,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44517</v>
+        <v>45666</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8028,7 +8038,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8071,7 +8081,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 44769-2025</t>
+          <t>A 29580-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8081,14 +8091,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45917</v>
+        <v>45825</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8101,7 +8111,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8144,7 +8154,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17700-2026</t>
+          <t>A 15491-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8158,10 +8168,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46121</v>
+        <v>45401</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8171,6 +8181,11 @@
       <c r="G93" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -8217,7 +8232,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44770-2025</t>
+          <t>A 64930-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8227,14 +8242,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45917</v>
+        <v>45282</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8247,7 +8262,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8290,7 +8305,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17699-2026</t>
+          <t>A 24866-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8304,10 +8319,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46121</v>
+        <v>45085</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8320,7 +8335,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8363,7 +8378,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 54442-2021</t>
+          <t>A 31010-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8377,10 +8392,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44473</v>
+        <v>44768</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8393,7 +8408,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8436,7 +8451,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 18517-2026</t>
+          <t>A 20357-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8450,10 +8465,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46127</v>
+        <v>46139</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8465,13 +8480,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8514,7 +8524,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 55939-2025</t>
+          <t>A 44770-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8524,14 +8534,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45973</v>
+        <v>45917</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8587,7 +8597,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 29580-2025</t>
+          <t>A 44769-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8597,14 +8607,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45825</v>
+        <v>45917</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8617,7 +8627,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8660,7 +8670,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 57181-2025</t>
+          <t>A 3087-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8674,10 +8684,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45979</v>
+        <v>44946</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8690,7 +8700,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8733,7 +8743,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 57194-2025</t>
+          <t>A 58415-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8747,10 +8757,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45979</v>
+        <v>44488</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8763,7 +8773,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8806,7 +8816,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 50181-2023</t>
+          <t>A 35447-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8820,10 +8830,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45208</v>
+        <v>45146</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8836,7 +8846,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8879,7 +8889,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 57942-2025</t>
+          <t>A 55939-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8893,10 +8903,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45982</v>
+        <v>45973</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8909,7 +8919,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8952,7 +8962,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 58310-2025</t>
+          <t>A 62447-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8966,10 +8976,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45985</v>
+        <v>46007</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8981,8 +8991,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9025,7 +9040,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58321-2025</t>
+          <t>A 51630-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9039,10 +9054,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45985</v>
+        <v>44462</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9055,7 +9070,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9098,7 +9113,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 58756-2025</t>
+          <t>A 28321-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9112,10 +9127,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45986</v>
+        <v>45818</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9171,7 +9186,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 27251-2025</t>
+          <t>A 57181-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9185,10 +9200,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45812</v>
+        <v>45979</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9201,7 +9216,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9244,7 +9259,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 58761-2025</t>
+          <t>A 57194-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9258,10 +9273,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45986</v>
+        <v>45979</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9274,7 +9289,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9317,7 +9332,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 59105-2025</t>
+          <t>A 57942-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9331,10 +9346,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45988</v>
+        <v>45982</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9347,7 +9362,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9390,7 +9405,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 41105-2025</t>
+          <t>A 58321-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9404,10 +9419,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45898</v>
+        <v>45985</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9420,7 +9435,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9463,7 +9478,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 1293-2023</t>
+          <t>A 58756-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9477,10 +9492,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44936</v>
+        <v>45986</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9493,7 +9508,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9536,7 +9551,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 39965-2025</t>
+          <t>A 58761-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9550,10 +9565,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45892</v>
+        <v>45986</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9566,7 +9581,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9609,7 +9624,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 28321-2025</t>
+          <t>A 58310-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9623,10 +9638,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45818</v>
+        <v>45985</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9639,7 +9654,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9682,7 +9697,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27255-2025</t>
+          <t>A 63449-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9692,14 +9707,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45812</v>
+        <v>45273</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9712,7 +9727,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9755,7 +9770,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 41337-2023</t>
+          <t>A 59105-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9769,10 +9784,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45174</v>
+        <v>45988</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9785,7 +9800,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9828,7 +9843,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 10984-2024</t>
+          <t>A 3678-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9842,10 +9857,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45370</v>
+        <v>45681</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9858,7 +9873,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9901,7 +9916,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20357-2026</t>
+          <t>A 36401-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9915,10 +9930,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46139</v>
+        <v>45152</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9930,8 +9945,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9974,7 +9994,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 10980-2024</t>
+          <t>A 2715-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9988,10 +10008,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45370</v>
+        <v>44580</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10004,7 +10024,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10047,7 +10067,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 31010-2022</t>
+          <t>A 21518-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10061,10 +10081,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44768</v>
+        <v>46148</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10077,7 +10097,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10120,7 +10140,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 11944-2024</t>
+          <t>A 7337-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10134,10 +10154,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45376</v>
+        <v>44971</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10193,7 +10213,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 62447-2025</t>
+          <t>A 32581-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10207,10 +10227,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46007</v>
+        <v>45838</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10222,13 +10242,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10271,7 +10286,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 3681-2025</t>
+          <t>A 62129-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10285,10 +10300,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45681</v>
+        <v>46006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10301,7 +10316,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10344,7 +10359,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59234-2022</t>
+          <t>A 62123-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10358,10 +10373,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44904</v>
+        <v>46006</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10373,13 +10388,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10422,7 +10432,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2715-2022</t>
+          <t>A 62391-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10436,10 +10446,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44580</v>
+        <v>46007</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10451,8 +10461,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>5.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10495,7 +10510,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 961-2024</t>
+          <t>A 2073-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10509,10 +10524,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45301</v>
+        <v>46036</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10525,7 +10540,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10568,7 +10583,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 21518-2026</t>
+          <t>A 63445-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10582,10 +10597,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46148</v>
+        <v>46013</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10598,7 +10613,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10641,7 +10656,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 1013-2025</t>
+          <t>A 60977-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10655,10 +10670,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45666</v>
+        <v>45261</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10671,7 +10686,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10714,7 +10729,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32581-2025</t>
+          <t>A 24139-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10728,10 +10743,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45838</v>
+        <v>46168</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10743,8 +10758,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10787,7 +10807,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62570-2023</t>
+          <t>A 1011-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10801,10 +10821,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45269</v>
+        <v>45666</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10817,7 +10837,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10860,7 +10880,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 2073-2026</t>
+          <t>A 60969-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10874,10 +10894,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46036</v>
+        <v>45261</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10890,7 +10910,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10933,7 +10953,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 50883-2024</t>
+          <t>A 24786-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10947,10 +10967,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45602</v>
+        <v>46171</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10962,8 +10982,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11006,7 +11031,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 50896-2024</t>
+          <t>A 24457-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11020,10 +11045,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45602</v>
+        <v>46170</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11035,8 +11060,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11079,7 +11109,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 1011-2025</t>
+          <t>A 24903-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11089,14 +11119,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45666</v>
+        <v>46174</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11108,8 +11138,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11152,7 +11187,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 24139-2026</t>
+          <t>A 38299-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11166,10 +11201,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46168</v>
+        <v>45161</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11181,13 +11216,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11230,7 +11260,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 24457-2026</t>
+          <t>A 24894-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11244,10 +11274,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11265,7 +11295,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11325,7 +11355,7 @@
         <v>46174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11386,7 +11416,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24786-2026</t>
+          <t>A 4837-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11400,10 +11430,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46171</v>
+        <v>46048</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11415,13 +11445,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11464,7 +11489,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 24900-2026</t>
+          <t>A 4852-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11478,10 +11503,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46174</v>
+        <v>46048</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11493,13 +11518,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11542,7 +11562,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 24894-2026</t>
+          <t>A 24888-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11559,7 +11579,7 @@
         <v>46174</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11577,7 +11597,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11620,7 +11640,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 24888-2026</t>
+          <t>A 24896-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11637,7 +11657,7 @@
         <v>46174</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11655,7 +11675,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.6</v>
+        <v>0.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11698,7 +11718,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 24896-2026</t>
+          <t>A 24900-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11715,7 +11735,7 @@
         <v>46174</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11733,7 +11753,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11776,7 +11796,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 24903-2026</t>
+          <t>A 58800-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11786,14 +11806,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46174</v>
+        <v>44903</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11805,13 +11825,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11854,7 +11869,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 25503-2026</t>
+          <t>A 6785-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11868,10 +11883,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46177</v>
+        <v>45342</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11885,11 +11900,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11932,7 +11947,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 27126-2026</t>
+          <t>A 25503-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11942,14 +11957,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46188</v>
+        <v>46177</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11967,7 +11982,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12010,7 +12025,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 27137-2026</t>
+          <t>A 11944-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12024,10 +12039,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46188</v>
+        <v>45376</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12039,13 +12054,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12088,7 +12098,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 32558-2026</t>
+          <t>A 59411-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12098,14 +12108,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46239</v>
+        <v>44907</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12166,7 +12176,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 32317-2026</t>
+          <t>A 58412-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12180,10 +12190,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46237</v>
+        <v>45250</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12196,7 +12206,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12239,7 +12249,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32574-2026</t>
+          <t>A 59410-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12249,14 +12259,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46239</v>
+        <v>44907</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12274,7 +12284,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12317,7 +12327,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 32564-2026</t>
+          <t>A 45918-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12331,10 +12341,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46239</v>
+        <v>45580</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12346,13 +12356,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12395,7 +12400,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 28652-2026</t>
+          <t>A 27126-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12405,14 +12410,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46198</v>
+        <v>46188</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12473,7 +12478,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3087-2023</t>
+          <t>A 27137-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12487,10 +12492,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44946</v>
+        <v>46188</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12502,8 +12507,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12546,7 +12556,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 28525-2026</t>
+          <t>A 62570-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12560,10 +12570,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46197</v>
+        <v>45269</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12575,13 +12585,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12624,7 +12629,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 33010-2026</t>
+          <t>A 4314-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12634,14 +12639,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46244</v>
+        <v>45324</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12653,8 +12658,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12697,7 +12707,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4314-2024</t>
+          <t>A 3681-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12707,14 +12717,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45324</v>
+        <v>45681</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12726,13 +12736,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12775,7 +12780,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 12769-2024</t>
+          <t>A 32564-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12789,10 +12794,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45384</v>
+        <v>46239</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12804,8 +12809,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12848,7 +12858,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 34172-2026</t>
+          <t>A 32558-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12862,10 +12872,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46253</v>
+        <v>46239</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12883,7 +12893,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12926,7 +12936,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 49915-2024</t>
+          <t>A 28525-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12940,10 +12950,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45597</v>
+        <v>46197</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12955,8 +12965,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12999,7 +13014,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 44753-2025</t>
+          <t>A 41819-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13013,10 +13028,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45917</v>
+        <v>45176</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13029,7 +13044,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13072,7 +13087,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 31161-2026</t>
+          <t>A 32574-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13086,10 +13101,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46216</v>
+        <v>46239</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13101,8 +13116,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13145,7 +13165,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34794-2026</t>
+          <t>A 50883-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13155,14 +13175,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46258</v>
+        <v>45602</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13172,11 +13192,6 @@
       <c r="G160" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I160" t="n">
@@ -13223,7 +13238,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 34730-2026</t>
+          <t>A 50896-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13237,10 +13252,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46258</v>
+        <v>45602</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13252,13 +13267,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13301,7 +13311,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 34748-2026</t>
+          <t>A 10984-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13315,10 +13325,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46258</v>
+        <v>45370</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13330,13 +13340,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13379,7 +13384,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 31193-2026</t>
+          <t>A 33010-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13393,10 +13398,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46217</v>
+        <v>46244</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13409,7 +13414,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13452,7 +13457,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 31192-2026</t>
+          <t>A 28652-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13466,10 +13471,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46217</v>
+        <v>46198</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13481,8 +13486,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13525,7 +13535,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 41819-2023</t>
+          <t>A 14210-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13539,10 +13549,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45176</v>
+        <v>45009</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13555,7 +13565,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13598,7 +13608,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 58415-2021</t>
+          <t>A 15467-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13612,10 +13622,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44488</v>
+        <v>45020</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13628,7 +13638,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13671,7 +13681,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 60917-2022</t>
+          <t>A 35404-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13685,10 +13695,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44908</v>
+        <v>45146</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13701,7 +13711,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13744,7 +13754,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 22307-2024</t>
+          <t>A 68095-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13758,10 +13768,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45446</v>
+        <v>44526</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13774,7 +13784,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13817,7 +13827,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 36206-2026</t>
+          <t>A 49915-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13831,10 +13841,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46267</v>
+        <v>45597</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13847,7 +13857,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13890,7 +13900,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 36209-2026</t>
+          <t>A 40667-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13904,10 +13914,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46267</v>
+        <v>45170</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13920,7 +13930,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13963,7 +13973,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 34167-2026</t>
+          <t>A 37631-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13977,10 +13987,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46253</v>
+        <v>45159</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13992,13 +14002,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14041,7 +14046,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 34431-2022</t>
+          <t>A 44753-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14055,10 +14060,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44792</v>
+        <v>45917</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14070,13 +14075,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14119,7 +14119,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 34162-2026</t>
+          <t>A 11270-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14133,10 +14133,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46253</v>
+        <v>44629</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14148,13 +14148,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14197,7 +14192,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 34834-2026</t>
+          <t>A 41337-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14211,10 +14206,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46258</v>
+        <v>45174</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14227,7 +14222,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14270,7 +14265,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 37226-2026</t>
+          <t>A 2800-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14284,10 +14279,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46274</v>
+        <v>45677</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14299,13 +14294,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14348,7 +14338,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 37355-2026</t>
+          <t>A 34172-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14362,10 +14352,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46275</v>
+        <v>46253</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14375,6 +14365,11 @@
       <c r="G176" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -14421,7 +14416,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37174-2026</t>
+          <t>A 8658-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14435,10 +14430,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46274</v>
+        <v>44613</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14450,13 +14445,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14499,7 +14489,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 37364-2026</t>
+          <t>A 34730-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14513,10 +14503,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46275</v>
+        <v>46258</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14528,8 +14518,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14572,7 +14567,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 60969-2023</t>
+          <t>A 2418-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14586,10 +14581,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45261</v>
+        <v>45674</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14602,7 +14597,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14645,7 +14640,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 31928-2026</t>
+          <t>A 2231-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14659,10 +14654,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46232</v>
+        <v>45673</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14675,7 +14670,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14718,7 +14713,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37353-2026</t>
+          <t>A 34748-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14732,10 +14727,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46275</v>
+        <v>46258</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14747,8 +14742,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14791,7 +14791,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 37367-2026</t>
+          <t>A 34794-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14801,14 +14801,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46275</v>
+        <v>46258</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14820,8 +14820,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14864,7 +14869,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31929-2026</t>
+          <t>A 42042-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14878,10 +14883,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46232</v>
+        <v>45177</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14937,7 +14942,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31930-2026</t>
+          <t>A 31161-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14951,10 +14956,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46232</v>
+        <v>46216</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14967,7 +14972,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15010,7 +15015,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 60964-2023</t>
+          <t>A 31192-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15024,10 +15029,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45261</v>
+        <v>46217</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15040,7 +15045,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15083,7 +15088,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 37888-2026</t>
+          <t>A 31193-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15097,10 +15102,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46279</v>
+        <v>46217</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15112,13 +15117,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15161,7 +15161,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 28131-2026</t>
+          <t>A 50886-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15175,10 +15175,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46195</v>
+        <v>45602</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15234,7 +15234,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 42042-2023</t>
+          <t>A 50901-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15248,10 +15248,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45177</v>
+        <v>45602</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15307,7 +15307,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 64934-2023</t>
+          <t>A 60917-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15321,10 +15321,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45282</v>
+        <v>44908</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15380,7 +15380,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 37631-2023</t>
+          <t>A 12769-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15394,10 +15394,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45159</v>
+        <v>45384</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15453,7 +15453,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 2231-2025</t>
+          <t>A 50906-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15467,10 +15467,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45673</v>
+        <v>45602</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15526,7 +15526,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 59410-2022</t>
+          <t>A 36209-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15536,14 +15536,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44907</v>
+        <v>46267</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15555,13 +15555,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15604,7 +15599,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 59411-2022</t>
+          <t>A 9125-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15614,14 +15609,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44907</v>
+        <v>44980</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15635,11 +15630,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15682,7 +15677,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 2800-2025</t>
+          <t>A 16304-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15696,10 +15691,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45677</v>
+        <v>45407</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15712,7 +15707,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15755,7 +15750,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 34521-2024</t>
+          <t>A 36206-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15769,10 +15764,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45525</v>
+        <v>46267</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15785,7 +15780,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15828,7 +15823,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 8658-2022</t>
+          <t>A 34167-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15842,10 +15837,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44613</v>
+        <v>46253</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15857,8 +15852,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15901,7 +15901,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 50570-2023</t>
+          <t>A 34162-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15915,10 +15915,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45217</v>
+        <v>46253</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15930,8 +15930,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15974,7 +15979,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 60977-2023</t>
+          <t>A 22328-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15988,10 +15993,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45261</v>
+        <v>45446</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16004,7 +16009,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16047,7 +16052,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 12253-2024</t>
+          <t>A 37226-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16061,10 +16066,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45378</v>
+        <v>46274</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16076,8 +16081,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16120,7 +16130,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 12254-2024</t>
+          <t>A 37174-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16134,10 +16144,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45378</v>
+        <v>46274</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16149,8 +16159,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16193,7 +16208,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 52655-2023</t>
+          <t>A 34834-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16203,14 +16218,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45225</v>
+        <v>46258</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16223,7 +16238,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16266,7 +16281,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 24866-2023</t>
+          <t>A 31929-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16280,10 +16295,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45085</v>
+        <v>46232</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16296,7 +16311,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16339,7 +16354,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 39950-2024</t>
+          <t>A 37367-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16353,10 +16368,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45553</v>
+        <v>46275</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16368,13 +16383,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16417,7 +16427,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 11270-2022</t>
+          <t>A 28131-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16431,10 +16441,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44629</v>
+        <v>46195</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16447,7 +16457,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16490,7 +16500,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 68095-2021</t>
+          <t>A 37364-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16504,10 +16514,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44526</v>
+        <v>46275</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16520,7 +16530,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16563,7 +16573,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 58800-2022</t>
+          <t>A 37353-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16573,14 +16583,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44903</v>
+        <v>46275</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16593,7 +16603,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16636,7 +16646,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 4821-2023</t>
+          <t>A 37355-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16650,10 +16660,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44957</v>
+        <v>46275</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16666,7 +16676,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16709,7 +16719,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 11478-2024</t>
+          <t>A 79-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16719,14 +16729,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45372</v>
+        <v>45293</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16739,7 +16749,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16782,7 +16792,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 51630-2021</t>
+          <t>A 31928-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16796,10 +16806,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44462</v>
+        <v>46232</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16812,7 +16822,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16855,7 +16865,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 15491-2024</t>
+          <t>A 961-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16869,10 +16879,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45401</v>
+        <v>45301</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16884,13 +16894,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16933,7 +16938,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 45918-2024</t>
+          <t>A 31930-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16947,10 +16952,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45580</v>
+        <v>46232</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16963,7 +16968,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17006,7 +17011,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 50906-2024</t>
+          <t>A 38300-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17020,10 +17025,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45602</v>
+        <v>45161</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17079,7 +17084,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 6785-2024</t>
+          <t>A 46248-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17093,10 +17098,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45342</v>
+        <v>45581</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17108,13 +17113,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17157,7 +17157,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 55730-2022</t>
+          <t>A 37888-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17171,10 +17171,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44888</v>
+        <v>46279</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17186,8 +17186,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17230,7 +17235,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 53520-2022</t>
+          <t>A 32317-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17244,10 +17249,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44879</v>
+        <v>46237</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17260,7 +17265,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17303,7 +17308,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 35404-2023</t>
+          <t>A 61575-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17317,10 +17322,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45146</v>
+        <v>45261</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17333,7 +17338,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17376,7 +17381,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 61012-2023</t>
+          <t>A 49971-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17390,10 +17395,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45259</v>
+        <v>45215</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17406,7 +17411,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17449,7 +17454,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 15467-2023</t>
+          <t>A 38278-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17459,14 +17464,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45020</v>
+        <v>45545</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17479,7 +17484,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17522,7 +17527,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 72558-2021</t>
+          <t>A 12675-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17536,10 +17541,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44546</v>
+        <v>45384</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17552,7 +17557,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17595,7 +17600,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 35447-2023</t>
+          <t>A 37083-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17609,10 +17614,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45146</v>
+        <v>45539</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17625,7 +17630,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17668,7 +17673,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 79-2024</t>
+          <t>A 13560-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17678,14 +17683,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45293</v>
+        <v>45736</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17741,7 +17746,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 66977-2021</t>
+          <t>A 34664-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17755,10 +17760,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44522</v>
+        <v>45526</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17771,7 +17776,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17814,7 +17819,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 49566-2021</t>
+          <t>A 23114-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17828,10 +17833,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44455</v>
+        <v>45791</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17844,7 +17849,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17887,7 +17892,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 15276-2022</t>
+          <t>A 2749-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17901,10 +17906,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44659</v>
+        <v>45314</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17916,13 +17921,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17965,7 +17965,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 17707-2023</t>
+          <t>A 57284-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17979,10 +17979,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45037</v>
+        <v>45629</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18038,7 +18038,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 46248-2024</t>
+          <t>A 24499-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18052,10 +18052,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45581</v>
+        <v>45798</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18111,7 +18111,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 61575-2023</t>
+          <t>A 18740-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18125,10 +18125,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45261</v>
+        <v>45763</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18184,7 +18184,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 34664-2024</t>
+          <t>A 27232-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18194,14 +18194,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45526</v>
+        <v>45812</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18257,7 +18257,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 37083-2024</t>
+          <t>A 28663-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18271,10 +18271,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45539</v>
+        <v>45819</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18330,7 +18330,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 12675-2024</t>
+          <t>A 30468-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18344,10 +18344,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45384</v>
+        <v>45827</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18403,7 +18403,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 49971-2023</t>
+          <t>A 23781-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18417,10 +18417,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45215</v>
+        <v>45793</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18476,7 +18476,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 13560-2025</t>
+          <t>A 31623-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18490,10 +18490,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45736</v>
+        <v>45834</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18549,7 +18549,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 38278-2024</t>
+          <t>A 31624-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18559,14 +18559,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45545</v>
+        <v>45834</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18622,7 +18622,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 23114-2025</t>
+          <t>A 50339-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18636,10 +18636,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45791</v>
+        <v>45216</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18695,7 +18695,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 57284-2024</t>
+          <t>A 37806-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18709,10 +18709,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45629</v>
+        <v>44810</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18768,7 +18768,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 2749-2024</t>
+          <t>A 37802-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18782,10 +18782,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45314</v>
+        <v>44810</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18858,7 +18858,7 @@
         <v>46197</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>

--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE237"/>
+  <dimension ref="A1:AE236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 45164-2023</t>
+          <t>A 13567-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45191</v>
+        <v>45736</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1155,17 +1155,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1191,39 +1191,39 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
         <v/>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
         <v>45705</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 41274-2025</t>
+          <t>A 54444-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45898</v>
+        <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1405,471 +1405,471 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Ängshök</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 41274-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45898</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 41274-2025 artfynd.xlsx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 41274-2025 karta.png", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 41274-2025 georefererad karta.tif", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 41274-2025 FSC-klagomål.docx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 41274-2025 FSC-klagomål mail.docx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 41274-2025 tillsynsbegäran.docx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 41274-2025 tillsynsbegäran mail.docx", "A 41274-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 46156-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45924</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>3.7</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tvåblad</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46156-2025 artfynd.xlsx", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46156-2025 karta.png", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46156-2025 georefererad karta.tif", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46156-2025 FSC-klagomål.docx", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46156-2025 FSC-klagomål mail.docx", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46156-2025 tillsynsbegäran.docx", "A 46156-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46156-2025 tillsynsbegäran mail.docx", "A 46156-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 46123-2025</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>45924</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>5.6</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46123-2025 artfynd.xlsx", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46123-2025 karta.png", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46123-2025 georefererad karta.tif", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/knärot/A 46123-2025 karta knärot.png", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46123-2025 FSC-klagomål.docx", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46123-2025 FSC-klagomål mail.docx", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46123-2025 tillsynsbegäran.docx", "A 46123-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46123-2025 tillsynsbegäran mail.docx", "A 46123-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 46522-2025</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45926</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>1.2</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tibast</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 51642-2021</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44462</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Vårstarr</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 51642-2021</t>
+          <t>A 22327-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44462</v>
+        <v>45446</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1939,35 +1939,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
         <v>46008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50403-2022</t>
+          <t>A 60983-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44866</v>
+        <v>45261</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2113,19 +2113,14 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2152,895 +2147,895 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 9030-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44615</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 9030-2022 artfynd.xlsx", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 9030-2022 karta.png", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 9030-2022 georefererad karta.tif", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 9030-2022 FSC-klagomål.docx", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 9030-2022 FSC-klagomål mail.docx", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 9030-2022 tillsynsbegäran.docx", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 9030-2022 tillsynsbegäran mail.docx", "A 9030-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 33532-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45519</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 51642-2021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44462</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 51642-2021</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44462</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 45164-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45191</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 50403-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U22" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Springkorn</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 50403-2022 artfynd.xlsx", "A 50403-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 50403-2022 karta.png", "A 50403-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 50403-2022 georefererad karta.tif", "A 50403-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 50403-2022 FSC-klagomål.docx", "A 50403-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 50403-2022 FSC-klagomål mail.docx", "A 50403-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 50403-2022 tillsynsbegäran.docx", "A 50403-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 50403-2022 tillsynsbegäran mail.docx", "A 50403-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 13567-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45736</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 34869-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="n">
+      <c r="R23" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Klubbsprötad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 34869-2026 artfynd.xlsx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 34869-2026 karta.png", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 34869-2026 georefererad karta.tif", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 34869-2026 FSC-klagomål.docx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 34869-2026 FSC-klagomål mail.docx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 34869-2026 tillsynsbegäran.docx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 34869-2026 tillsynsbegäran mail.docx", "A 34869-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 22327-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45446</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 32573-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T24" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 32554-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Purpurknipprot</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 32573-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Lunglav</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32573-2026 artfynd.xlsx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32573-2026 karta.png", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32573-2026 georefererad karta.tif", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32573-2026 FSC-klagomål.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32573-2026 FSC-klagomål mail.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32573-2026 tillsynsbegäran.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32573-2026 tillsynsbegäran mail.docx", "A 32573-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 9030-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44615</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 9030-2022 artfynd.xlsx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 9030-2022 karta.png", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 9030-2022 georefererad karta.tif", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 9030-2022 FSC-klagomål.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 9030-2022 FSC-klagomål mail.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 9030-2022 tillsynsbegäran.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 9030-2022 tillsynsbegäran mail.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 34869-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Backsippa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 34869-2026 artfynd.xlsx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 34869-2026 karta.png", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 34869-2026 georefererad karta.tif", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 34869-2026 FSC-klagomål.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 34869-2026 FSC-klagomål mail.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 34869-2026 tillsynsbegäran.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 34869-2026 tillsynsbegäran mail.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 33532-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45519</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Backsippa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 60983-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
@@ -3061,7 +3056,7 @@
         <v>45230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3166,7 +3161,7 @@
         <v>45673</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3254,7 +3249,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54444-2021</t>
+          <t>A 32554-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3268,10 +3263,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44473</v>
+        <v>46239</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3283,14 +3278,19 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3320,39 +3320,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ängshök</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
         <v/>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
         <v>44573</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44573</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>44545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 51475-2023</t>
+          <t>A 56458-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45221</v>
+        <v>44480</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12253-2024</t>
+          <t>A 19352-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45378</v>
+        <v>44692</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12254-2024</t>
+          <t>A 10950-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45378</v>
+        <v>44627</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3875,7 +3875,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 56458-2021</t>
+          <t>A 50901-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44480</v>
+        <v>45602</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17707-2023</t>
+          <t>A 36401-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45037</v>
+        <v>45152</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3977,8 +3977,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.6</v>
+        <v>6.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4021,7 +4026,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 49566-2021</t>
+          <t>A 14210-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4035,10 +4040,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44455</v>
+        <v>45009</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4051,7 +4056,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4094,7 +4099,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 53518-2022</t>
+          <t>A 50886-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4108,10 +4113,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44879</v>
+        <v>45602</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4124,7 +4129,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4167,7 +4172,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19352-2022</t>
+          <t>A 16304-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4181,10 +4186,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44692</v>
+        <v>45407</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4197,7 +4202,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4240,7 +4245,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10950-2022</t>
+          <t>A 38300-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4254,10 +4259,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44627</v>
+        <v>45161</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4270,7 +4275,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4313,7 +4318,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38199-2025</t>
+          <t>A 43012-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4323,14 +4328,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45882</v>
+        <v>45567</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4343,7 +4348,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4386,7 +4391,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34431-2022</t>
+          <t>A 3877-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4400,10 +4405,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44792</v>
+        <v>44951</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4415,13 +4420,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54442-2021</t>
+          <t>A 72563-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44473</v>
+        <v>44546</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11478-2024</t>
+          <t>A 64930-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45372</v>
+        <v>45282</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 72563-2021</t>
+          <t>A 22328-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44546</v>
+        <v>45446</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11064-2026</t>
+          <t>A 24499-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46079</v>
+        <v>45798</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 72558-2021</t>
+          <t>A 18740-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44546</v>
+        <v>45763</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 66977-2021</t>
+          <t>A 38299-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44522</v>
+        <v>45161</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14928-2026</t>
+          <t>A 27232-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4912,14 +4912,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46104</v>
+        <v>45812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4931,13 +4931,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4980,7 +4975,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43032-2025</t>
+          <t>A 40667-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4994,10 +4989,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45909</v>
+        <v>45170</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5010,7 +5005,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5053,7 +5048,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 43026-2025</t>
+          <t>A 28663-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5067,10 +5062,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45909</v>
+        <v>45819</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5083,7 +5078,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5126,7 +5121,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15032-2026</t>
+          <t>A 9125-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5140,10 +5135,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46104</v>
+        <v>44980</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5157,11 +5152,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5204,7 +5199,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 65921-2021</t>
+          <t>A 53518-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5218,10 +5213,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44517</v>
+        <v>44879</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5234,7 +5229,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5277,7 +5272,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 16110-2026</t>
+          <t>A 30468-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5291,10 +5286,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46108</v>
+        <v>45827</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5307,7 +5302,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5350,7 +5345,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 44756-2025</t>
+          <t>A 23781-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5364,10 +5359,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45917</v>
+        <v>45793</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5380,7 +5375,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5423,7 +5418,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 50179-2023</t>
+          <t>A 15783-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5437,10 +5432,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45208</v>
+        <v>44663</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5453,7 +5448,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.6</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5496,7 +5491,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 44757-2025</t>
+          <t>A 43026-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5510,10 +5505,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45917</v>
+        <v>45909</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5526,7 +5521,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5569,7 +5564,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50570-2023</t>
+          <t>A 43032-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5583,10 +5578,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45217</v>
+        <v>45909</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5599,7 +5594,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5642,7 +5637,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16173-2026</t>
+          <t>A 31624-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5656,10 +5651,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46111</v>
+        <v>45834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5671,13 +5666,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5720,7 +5710,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50181-2023</t>
+          <t>A 31623-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5734,10 +5724,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45208</v>
+        <v>45834</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5750,7 +5740,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5793,7 +5783,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39950-2024</t>
+          <t>A 50179-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5807,10 +5797,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45553</v>
+        <v>45208</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5822,13 +5812,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5871,7 +5856,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 53520-2022</t>
+          <t>A 51475-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5885,10 +5870,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44879</v>
+        <v>45221</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5901,7 +5886,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5944,7 +5929,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4821-2023</t>
+          <t>A 44757-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5958,10 +5943,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44957</v>
+        <v>45917</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5974,7 +5959,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6017,7 +6002,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 46164-2025</t>
+          <t>A 7337-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6031,10 +6016,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45924</v>
+        <v>44971</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6047,7 +6032,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6090,7 +6075,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10980-2024</t>
+          <t>A 44756-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6104,10 +6089,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45370</v>
+        <v>45917</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6120,7 +6105,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6163,7 +6148,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17699-2026</t>
+          <t>A 50339-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6177,10 +6162,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46121</v>
+        <v>45216</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6193,7 +6178,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6236,7 +6221,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17700-2026</t>
+          <t>A 46164-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6250,10 +6235,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46121</v>
+        <v>45924</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6266,7 +6251,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6309,7 +6294,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 46144-2025</t>
+          <t>A 46159-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6326,7 +6311,7 @@
         <v>45924</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6339,7 +6324,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6382,7 +6367,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 43012-2024</t>
+          <t>A 46144-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6392,14 +6377,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45567</v>
+        <v>45924</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6412,7 +6397,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6455,7 +6440,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 46159-2025</t>
+          <t>A 37806-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6469,10 +6454,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45924</v>
+        <v>44810</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6485,7 +6470,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6528,7 +6513,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60964-2023</t>
+          <t>A 46521-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6542,10 +6527,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45261</v>
+        <v>45926</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6557,8 +6542,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6601,7 +6591,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52655-2023</t>
+          <t>A 58412-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6611,14 +6601,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45225</v>
+        <v>45250</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6631,7 +6621,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6674,7 +6664,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15276-2022</t>
+          <t>A 63449-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6684,14 +6674,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44659</v>
+        <v>45273</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6703,13 +6693,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6752,7 +6737,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 46521-2025</t>
+          <t>A 37802-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6766,10 +6751,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45926</v>
+        <v>44810</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6781,13 +6766,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6830,7 +6810,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22307-2024</t>
+          <t>A 4852-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6844,10 +6824,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45446</v>
+        <v>46048</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6860,7 +6840,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6903,7 +6883,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3877-2023</t>
+          <t>A 3678-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6917,10 +6897,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44951</v>
+        <v>45681</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6933,7 +6913,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6976,7 +6956,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18517-2026</t>
+          <t>A 51326-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6990,10 +6970,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46127</v>
+        <v>45950</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7005,13 +6985,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7054,7 +7029,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1293-2023</t>
+          <t>A 4837-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7068,10 +7043,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44936</v>
+        <v>46048</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7084,7 +7059,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7127,7 +7102,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61012-2023</t>
+          <t>A 38199-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7141,10 +7116,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45259</v>
+        <v>45882</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7200,7 +7175,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15783-2022</t>
+          <t>A 51335-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7214,10 +7189,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44663</v>
+        <v>45950</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7230,7 +7205,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7273,7 +7248,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 34521-2024</t>
+          <t>A 2418-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7287,10 +7262,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45525</v>
+        <v>45674</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7303,7 +7278,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7346,7 +7321,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 64934-2023</t>
+          <t>A 65921-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7360,10 +7335,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45282</v>
+        <v>44517</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7376,7 +7351,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7419,7 +7394,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 39965-2025</t>
+          <t>A 44769-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7429,14 +7404,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45892</v>
+        <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7449,7 +7424,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7492,7 +7467,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59234-2022</t>
+          <t>A 54442-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7506,10 +7481,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44904</v>
+        <v>44473</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7521,13 +7496,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7570,7 +7540,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 27255-2025</t>
+          <t>A 44770-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7580,14 +7550,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45812</v>
+        <v>45917</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7600,7 +7570,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7643,7 +7613,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 27251-2025</t>
+          <t>A 55939-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7657,10 +7627,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45812</v>
+        <v>45973</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7673,7 +7643,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7716,7 +7686,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51335-2025</t>
+          <t>A 50181-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7730,10 +7700,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45950</v>
+        <v>45208</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7746,7 +7716,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7789,7 +7759,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 55730-2022</t>
+          <t>A 57181-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7803,10 +7773,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44888</v>
+        <v>45979</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7819,7 +7789,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7862,7 +7832,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 51326-2025</t>
+          <t>A 57194-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7876,10 +7846,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45950</v>
+        <v>45979</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7892,7 +7862,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7935,7 +7905,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41105-2025</t>
+          <t>A 57942-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7949,10 +7919,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45898</v>
+        <v>45982</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7965,7 +7935,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8008,7 +7978,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1013-2025</t>
+          <t>A 1293-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8022,10 +7992,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45666</v>
+        <v>44936</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8038,7 +8008,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8081,7 +8051,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 29580-2025</t>
+          <t>A 58310-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8095,10 +8065,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45825</v>
+        <v>45985</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8111,7 +8081,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8154,7 +8124,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15491-2024</t>
+          <t>A 58321-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8168,10 +8138,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45401</v>
+        <v>45985</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8183,13 +8153,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8232,7 +8197,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 64930-2023</t>
+          <t>A 58756-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8246,10 +8211,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45282</v>
+        <v>45986</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8262,7 +8227,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8305,7 +8270,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24866-2023</t>
+          <t>A 58761-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8319,10 +8284,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45085</v>
+        <v>45986</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8335,7 +8300,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8378,7 +8343,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31010-2022</t>
+          <t>A 59105-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8392,10 +8357,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44768</v>
+        <v>45988</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8408,7 +8373,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8451,7 +8416,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 20357-2026</t>
+          <t>A 11064-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8465,10 +8430,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8481,7 +8446,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8524,7 +8489,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 44770-2025</t>
+          <t>A 41337-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8534,14 +8499,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45917</v>
+        <v>45174</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8554,7 +8519,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8597,7 +8562,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 44769-2025</t>
+          <t>A 10984-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8607,14 +8572,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45917</v>
+        <v>45370</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8627,7 +8592,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8670,7 +8635,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 3087-2023</t>
+          <t>A 10980-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8684,10 +8649,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44946</v>
+        <v>45370</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8700,7 +8665,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8743,7 +8708,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 58415-2021</t>
+          <t>A 62129-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8757,10 +8722,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44488</v>
+        <v>46006</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8773,7 +8738,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8816,7 +8781,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 35447-2023</t>
+          <t>A 62123-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8830,10 +8795,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45146</v>
+        <v>46006</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8846,7 +8811,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8889,7 +8854,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 55939-2025</t>
+          <t>A 62391-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8903,10 +8868,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45973</v>
+        <v>46007</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8918,8 +8883,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8962,7 +8932,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 62447-2025</t>
+          <t>A 11944-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8976,10 +8946,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46007</v>
+        <v>45376</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8991,13 +8961,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9040,7 +9005,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 51630-2021</t>
+          <t>A 63445-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9054,10 +9019,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44462</v>
+        <v>46013</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9070,7 +9035,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9113,7 +9078,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 28321-2025</t>
+          <t>A 3681-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9127,10 +9092,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45818</v>
+        <v>45681</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9143,7 +9108,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9186,7 +9151,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57181-2025</t>
+          <t>A 59234-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9200,10 +9165,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45979</v>
+        <v>44904</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9215,8 +9180,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9259,7 +9229,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 57194-2025</t>
+          <t>A 15032-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9273,10 +9243,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45979</v>
+        <v>46104</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9288,8 +9258,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9332,7 +9307,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57942-2025</t>
+          <t>A 14928-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9346,10 +9321,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45982</v>
+        <v>46104</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9359,6 +9334,11 @@
       <c r="G109" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -9405,7 +9385,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 58321-2025</t>
+          <t>A 2715-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9419,10 +9399,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45985</v>
+        <v>44580</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9435,7 +9415,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9478,7 +9458,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58756-2025</t>
+          <t>A 961-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9492,10 +9472,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45986</v>
+        <v>45301</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9508,7 +9488,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9551,7 +9531,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 58761-2025</t>
+          <t>A 1013-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9565,10 +9545,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45986</v>
+        <v>45666</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9581,7 +9561,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9624,7 +9604,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 58310-2025</t>
+          <t>A 62570-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9638,10 +9618,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45985</v>
+        <v>45269</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9697,7 +9677,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 63449-2023</t>
+          <t>A 16110-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9707,14 +9687,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45273</v>
+        <v>46108</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9727,7 +9707,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9770,7 +9750,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 59105-2025</t>
+          <t>A 16173-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9784,10 +9764,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45988</v>
+        <v>46111</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9799,8 +9779,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9843,7 +9828,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3678-2025</t>
+          <t>A 50883-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9857,10 +9842,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45681</v>
+        <v>45602</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9873,7 +9858,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9916,7 +9901,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 36401-2023</t>
+          <t>A 50896-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9930,10 +9915,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45152</v>
+        <v>45602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9945,13 +9930,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>6.3</v>
+        <v>3.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9994,7 +9974,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 2715-2022</t>
+          <t>A 17700-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10008,10 +9988,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44580</v>
+        <v>46121</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10024,7 +10004,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10067,7 +10047,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 21518-2026</t>
+          <t>A 17699-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10081,10 +10061,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46148</v>
+        <v>46121</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10097,7 +10077,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10140,7 +10120,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 7337-2023</t>
+          <t>A 18517-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10154,10 +10134,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44971</v>
+        <v>46127</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10169,8 +10149,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10213,7 +10198,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32581-2025</t>
+          <t>A 3087-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10227,10 +10212,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45838</v>
+        <v>44946</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10243,7 +10228,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10286,7 +10271,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 62129-2025</t>
+          <t>A 29580-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10300,10 +10285,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46006</v>
+        <v>45825</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10316,7 +10301,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10359,7 +10344,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 62123-2025</t>
+          <t>A 4314-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10369,14 +10354,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46006</v>
+        <v>45324</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10388,8 +10373,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10432,7 +10422,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 62391-2025</t>
+          <t>A 12769-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10446,10 +10436,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46007</v>
+        <v>45384</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10461,13 +10451,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>8.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10510,7 +10495,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 2073-2026</t>
+          <t>A 49915-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10524,10 +10509,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46036</v>
+        <v>45597</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10540,7 +10525,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10583,7 +10568,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 63445-2025</t>
+          <t>A 27251-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10597,10 +10582,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46013</v>
+        <v>45812</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10613,7 +10598,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10656,7 +10641,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 60977-2023</t>
+          <t>A 41819-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10670,10 +10655,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45261</v>
+        <v>45176</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10686,7 +10671,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10729,7 +10714,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 24139-2026</t>
+          <t>A 58415-2021</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10743,10 +10728,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46168</v>
+        <v>44488</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10758,13 +10743,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10807,7 +10787,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 1011-2025</t>
+          <t>A 41105-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10821,10 +10801,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45666</v>
+        <v>45898</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10837,7 +10817,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10880,7 +10860,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 60969-2023</t>
+          <t>A 39965-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10894,10 +10874,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45261</v>
+        <v>45892</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10910,7 +10890,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10953,7 +10933,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 24786-2026</t>
+          <t>A 22307-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10967,10 +10947,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46171</v>
+        <v>45446</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10982,13 +10962,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11031,7 +11006,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24457-2026</t>
+          <t>A 28321-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11045,10 +11020,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46170</v>
+        <v>45818</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11060,13 +11035,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11109,7 +11079,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 24903-2026</t>
+          <t>A 27255-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11119,14 +11089,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46174</v>
+        <v>45812</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11138,13 +11108,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11187,7 +11152,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 38299-2023</t>
+          <t>A 34431-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11201,10 +11166,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45161</v>
+        <v>44792</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11216,8 +11181,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11260,7 +11230,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 24894-2026</t>
+          <t>A 20357-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11274,10 +11244,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46174</v>
+        <v>46139</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11289,13 +11259,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11338,7 +11303,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 25031-2026</t>
+          <t>A 31010-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11352,10 +11317,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46174</v>
+        <v>44768</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11367,13 +11332,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11416,7 +11376,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 4837-2026</t>
+          <t>A 60969-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11430,10 +11390,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46048</v>
+        <v>45261</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11446,7 +11406,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11489,7 +11449,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 4852-2026</t>
+          <t>A 62447-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11503,10 +11463,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46048</v>
+        <v>46007</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11518,8 +11478,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11562,7 +11527,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 24888-2026</t>
+          <t>A 60964-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11576,10 +11541,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46174</v>
+        <v>45261</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11591,13 +11556,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11640,7 +11600,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 24896-2026</t>
+          <t>A 21518-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11654,10 +11614,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46174</v>
+        <v>46148</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11669,13 +11629,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11718,7 +11673,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 24900-2026</t>
+          <t>A 32581-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11732,10 +11687,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46174</v>
+        <v>45838</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11747,13 +11702,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11796,7 +11746,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 58800-2022</t>
+          <t>A 2073-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11806,14 +11756,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44903</v>
+        <v>46036</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11826,7 +11776,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11869,7 +11819,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 6785-2024</t>
+          <t>A 42042-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11883,10 +11833,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45342</v>
+        <v>45177</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11898,13 +11848,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11947,7 +11892,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 25503-2026</t>
+          <t>A 64934-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11961,10 +11906,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46177</v>
+        <v>45282</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11976,13 +11921,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12025,7 +11965,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 11944-2024</t>
+          <t>A 37631-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12039,10 +11979,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45376</v>
+        <v>45159</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12055,7 +11995,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12098,7 +12038,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 59411-2022</t>
+          <t>A 1011-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12108,14 +12048,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44907</v>
+        <v>45666</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12127,13 +12067,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12176,7 +12111,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 58412-2023</t>
+          <t>A 2231-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12190,10 +12125,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45250</v>
+        <v>45673</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12206,7 +12141,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12249,7 +12184,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 59410-2022</t>
+          <t>A 24139-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12259,14 +12194,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44907</v>
+        <v>46168</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12284,7 +12219,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12327,7 +12262,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 45918-2024</t>
+          <t>A 59410-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12337,14 +12272,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45580</v>
+        <v>44907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12356,8 +12291,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12400,7 +12340,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 27126-2026</t>
+          <t>A 59411-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12414,10 +12354,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46188</v>
+        <v>44907</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12435,7 +12375,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12478,7 +12418,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27137-2026</t>
+          <t>A 24457-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12492,10 +12432,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46188</v>
+        <v>46170</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12556,7 +12496,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 62570-2023</t>
+          <t>A 2800-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12570,10 +12510,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45269</v>
+        <v>45677</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12586,7 +12526,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12629,7 +12569,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 4314-2024</t>
+          <t>A 25031-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12639,14 +12579,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45324</v>
+        <v>46174</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12660,11 +12600,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12707,7 +12647,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 3681-2025</t>
+          <t>A 24786-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12721,10 +12661,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45681</v>
+        <v>46171</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12736,8 +12676,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12780,7 +12725,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 32564-2026</t>
+          <t>A 24900-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12794,10 +12739,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46239</v>
+        <v>46174</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12815,7 +12760,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12858,7 +12803,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 32558-2026</t>
+          <t>A 24894-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12872,10 +12817,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46239</v>
+        <v>46174</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12893,7 +12838,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12936,7 +12881,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 28525-2026</t>
+          <t>A 24888-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12950,10 +12895,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46197</v>
+        <v>46174</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12971,7 +12916,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13014,7 +12959,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 41819-2023</t>
+          <t>A 24896-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13028,10 +12973,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45176</v>
+        <v>46174</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13043,8 +12988,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13087,7 +13037,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 32574-2026</t>
+          <t>A 24903-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13097,14 +13047,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46239</v>
+        <v>46174</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13122,7 +13072,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13165,7 +13115,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 50883-2024</t>
+          <t>A 34521-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13179,10 +13129,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45602</v>
+        <v>45525</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13195,7 +13145,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13238,7 +13188,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 50896-2024</t>
+          <t>A 8658-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13252,10 +13202,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45602</v>
+        <v>44613</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13268,7 +13218,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13311,7 +13261,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 10984-2024</t>
+          <t>A 50570-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13325,10 +13275,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45370</v>
+        <v>45217</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13341,7 +13291,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13384,7 +13334,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 33010-2026</t>
+          <t>A 25503-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13398,10 +13348,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46244</v>
+        <v>46177</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13413,8 +13363,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13457,7 +13412,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 28652-2026</t>
+          <t>A 60977-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13471,10 +13426,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46198</v>
+        <v>45261</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13486,13 +13441,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13535,7 +13485,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 14210-2023</t>
+          <t>A 12253-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13549,10 +13499,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45009</v>
+        <v>45378</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13565,7 +13515,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13608,7 +13558,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 15467-2023</t>
+          <t>A 12254-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13622,10 +13572,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45020</v>
+        <v>45378</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13638,7 +13588,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13681,7 +13631,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 35404-2023</t>
+          <t>A 27126-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13691,14 +13641,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45146</v>
+        <v>46188</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13710,8 +13660,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13754,7 +13709,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 68095-2021</t>
+          <t>A 27137-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13768,10 +13723,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44526</v>
+        <v>46188</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13783,8 +13738,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13827,7 +13787,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 49915-2024</t>
+          <t>A 52655-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13837,14 +13797,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45597</v>
+        <v>45225</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13857,7 +13817,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13900,7 +13860,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 40667-2023</t>
+          <t>A 24866-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13914,10 +13874,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45170</v>
+        <v>45085</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13930,7 +13890,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13973,7 +13933,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37631-2023</t>
+          <t>A 39950-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13987,10 +13947,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45159</v>
+        <v>45553</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14002,8 +13962,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14046,7 +14011,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 44753-2025</t>
+          <t>A 11270-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14060,10 +14025,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45917</v>
+        <v>44629</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14076,7 +14041,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14119,7 +14084,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 11270-2022</t>
+          <t>A 28652-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14133,10 +14098,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44629</v>
+        <v>46198</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14148,8 +14113,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14192,7 +14162,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 41337-2023</t>
+          <t>A 68095-2021</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14206,10 +14176,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45174</v>
+        <v>44526</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14222,7 +14192,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14265,7 +14235,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 2800-2025</t>
+          <t>A 28525-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14279,10 +14249,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45677</v>
+        <v>46197</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14294,8 +14264,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14338,7 +14313,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 34172-2026</t>
+          <t>A 58800-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14348,14 +14323,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46253</v>
+        <v>44903</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14367,13 +14342,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14416,7 +14386,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 8658-2022</t>
+          <t>A 33010-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14430,10 +14400,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44613</v>
+        <v>46244</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14446,7 +14416,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14489,7 +14459,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 34730-2026</t>
+          <t>A 4821-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14503,10 +14473,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46258</v>
+        <v>44957</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14518,13 +14488,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14567,7 +14532,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 2418-2025</t>
+          <t>A 11478-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14581,10 +14546,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45674</v>
+        <v>45372</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14597,7 +14562,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14640,7 +14605,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 2231-2025</t>
+          <t>A 51630-2021</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14654,10 +14619,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45673</v>
+        <v>44462</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14670,7 +14635,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14713,7 +14678,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34748-2026</t>
+          <t>A 15491-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14727,10 +14692,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46258</v>
+        <v>45401</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14744,11 +14709,11 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14791,7 +14756,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34794-2026</t>
+          <t>A 45918-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14801,14 +14766,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46258</v>
+        <v>45580</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14820,13 +14785,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14869,7 +14829,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 42042-2023</t>
+          <t>A 34172-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14883,10 +14843,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45177</v>
+        <v>46253</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14896,6 +14856,11 @@
       <c r="G183" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I183" t="n">
@@ -14942,7 +14907,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31161-2026</t>
+          <t>A 50906-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14956,10 +14921,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46216</v>
+        <v>45602</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14972,7 +14937,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15015,7 +14980,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 31192-2026</t>
+          <t>A 44753-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15029,10 +14994,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46217</v>
+        <v>45917</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15088,7 +15053,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 31193-2026</t>
+          <t>A 6785-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15102,10 +15067,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46217</v>
+        <v>45342</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15117,8 +15082,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15161,7 +15131,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 50886-2024</t>
+          <t>A 55730-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15175,10 +15145,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45602</v>
+        <v>44888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15191,7 +15161,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15234,7 +15204,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 50901-2024</t>
+          <t>A 31161-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15248,10 +15218,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45602</v>
+        <v>46216</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15264,7 +15234,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15307,7 +15277,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 60917-2022</t>
+          <t>A 53520-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15321,10 +15291,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44908</v>
+        <v>44879</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15337,7 +15307,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15380,7 +15350,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 12769-2024</t>
+          <t>A 34794-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15390,14 +15360,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45384</v>
+        <v>46258</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15409,8 +15379,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15453,7 +15428,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 50906-2024</t>
+          <t>A 34730-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15467,10 +15442,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45602</v>
+        <v>46258</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15482,8 +15457,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15526,7 +15506,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 36209-2026</t>
+          <t>A 35404-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15540,10 +15520,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46267</v>
+        <v>45146</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15556,7 +15536,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15599,7 +15579,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 9125-2023</t>
+          <t>A 34748-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15613,10 +15593,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44980</v>
+        <v>46258</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15630,11 +15610,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15677,7 +15657,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 16304-2024</t>
+          <t>A 31193-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15691,10 +15671,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45407</v>
+        <v>46217</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15707,7 +15687,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15750,7 +15730,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 36206-2026</t>
+          <t>A 31192-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15764,10 +15744,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46267</v>
+        <v>46217</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15780,7 +15760,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15823,7 +15803,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 34167-2026</t>
+          <t>A 61012-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15837,10 +15817,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46253</v>
+        <v>45259</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15852,13 +15832,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15901,7 +15876,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 34162-2026</t>
+          <t>A 60917-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15915,10 +15890,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46253</v>
+        <v>44908</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15930,13 +15905,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15979,7 +15949,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 22328-2024</t>
+          <t>A 36206-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15993,10 +15963,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45446</v>
+        <v>46267</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16009,7 +15979,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16052,7 +16022,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 37226-2026</t>
+          <t>A 15467-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16066,10 +16036,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46274</v>
+        <v>45020</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16081,13 +16051,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16130,7 +16095,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 37174-2026</t>
+          <t>A 72558-2021</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16144,10 +16109,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46274</v>
+        <v>44546</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16159,13 +16124,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16208,7 +16168,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 34834-2026</t>
+          <t>A 36209-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16222,10 +16182,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46258</v>
+        <v>46267</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16238,7 +16198,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16281,7 +16241,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 31929-2026</t>
+          <t>A 35447-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16295,10 +16255,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46232</v>
+        <v>45146</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16311,7 +16271,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16354,7 +16314,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37367-2026</t>
+          <t>A 34167-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16368,10 +16328,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46275</v>
+        <v>46253</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16383,8 +16343,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16427,7 +16392,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 28131-2026</t>
+          <t>A 79-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16437,14 +16402,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46195</v>
+        <v>45293</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16500,7 +16465,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37364-2026</t>
+          <t>A 34162-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16514,10 +16479,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46275</v>
+        <v>46253</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16529,8 +16494,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>8.5</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16573,7 +16543,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 37353-2026</t>
+          <t>A 34834-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16587,10 +16557,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46275</v>
+        <v>46258</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16603,7 +16573,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16646,7 +16616,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37355-2026</t>
+          <t>A 37226-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16660,10 +16630,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16675,8 +16645,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16719,7 +16694,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 79-2024</t>
+          <t>A 37355-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16729,14 +16704,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45293</v>
+        <v>46275</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16749,7 +16724,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16792,7 +16767,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31928-2026</t>
+          <t>A 37174-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16806,10 +16781,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46232</v>
+        <v>46274</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16821,8 +16796,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16865,7 +16845,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 961-2024</t>
+          <t>A 37364-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16879,10 +16859,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45301</v>
+        <v>46275</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16895,7 +16875,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16938,7 +16918,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 31930-2026</t>
+          <t>A 31928-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16955,7 +16935,7 @@
         <v>46232</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16968,7 +16948,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17011,7 +16991,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 38300-2023</t>
+          <t>A 37353-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17025,10 +17005,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45161</v>
+        <v>46275</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17041,7 +17021,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17084,7 +17064,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 46248-2024</t>
+          <t>A 37367-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17098,10 +17078,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45581</v>
+        <v>46275</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17114,7 +17094,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17157,7 +17137,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 37888-2026</t>
+          <t>A 66977-2021</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17171,10 +17151,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46279</v>
+        <v>44522</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17186,13 +17166,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17235,7 +17210,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 32317-2026</t>
+          <t>A 31929-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17249,10 +17224,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46237</v>
+        <v>46232</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17265,7 +17240,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17308,7 +17283,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 61575-2023</t>
+          <t>A 31930-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17322,10 +17297,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45261</v>
+        <v>46232</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17338,7 +17313,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17381,7 +17356,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 49971-2023</t>
+          <t>A 37888-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17395,10 +17370,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45215</v>
+        <v>46279</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17410,8 +17385,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17454,7 +17434,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 38278-2024</t>
+          <t>A 28131-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17464,14 +17444,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45545</v>
+        <v>46195</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17484,7 +17464,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17527,7 +17507,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 12675-2024</t>
+          <t>A 15276-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17541,10 +17521,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45384</v>
+        <v>44659</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17556,8 +17536,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17600,7 +17585,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 37083-2024</t>
+          <t>A 17707-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17614,10 +17599,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45539</v>
+        <v>45037</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17630,7 +17615,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17673,7 +17658,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 13560-2025</t>
+          <t>A 46248-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17687,10 +17672,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45736</v>
+        <v>45581</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17703,7 +17688,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17746,7 +17731,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 34664-2024</t>
+          <t>A 32574-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17760,10 +17745,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45526</v>
+        <v>46239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17775,8 +17760,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17819,7 +17809,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 23114-2025</t>
+          <t>A 61575-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17833,10 +17823,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45791</v>
+        <v>45261</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17849,7 +17839,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17892,7 +17882,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 2749-2024</t>
+          <t>A 32558-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17906,10 +17896,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45314</v>
+        <v>46239</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17921,8 +17911,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17965,7 +17960,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 57284-2024</t>
+          <t>A 32564-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17979,10 +17974,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45629</v>
+        <v>46239</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17994,8 +17989,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18038,7 +18038,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 24499-2025</t>
+          <t>A 34664-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18052,10 +18052,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45798</v>
+        <v>45526</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18111,7 +18111,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 18740-2025</t>
+          <t>A 32317-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18125,10 +18125,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45763</v>
+        <v>46237</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18184,7 +18184,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 27232-2025</t>
+          <t>A 37083-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18194,14 +18194,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45812</v>
+        <v>45539</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18257,7 +18257,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 28663-2025</t>
+          <t>A 12675-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18271,10 +18271,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45819</v>
+        <v>45384</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18330,7 +18330,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 30468-2025</t>
+          <t>A 49971-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18344,10 +18344,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45827</v>
+        <v>45215</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 23781-2025</t>
+          <t>A 13560-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18417,10 +18417,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45793</v>
+        <v>45736</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 31623-2025</t>
+          <t>A 38278-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18486,14 +18486,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45834</v>
+        <v>45545</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18549,7 +18549,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 31624-2025</t>
+          <t>A 23114-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18563,10 +18563,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45834</v>
+        <v>45791</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18622,7 +18622,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 50339-2023</t>
+          <t>A 57284-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18636,10 +18636,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45216</v>
+        <v>45629</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18695,7 +18695,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 37806-2022</t>
+          <t>A 2749-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18709,10 +18709,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44810</v>
+        <v>45314</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18765,27 +18765,27 @@
       </c>
       <c r="V235" s="2" t="inlineStr"/>
     </row>
-    <row r="236" ht="15" customHeight="1">
+    <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 37802-2022</t>
+          <t>S 1827-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44810</v>
+        <v>46197</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18797,8 +18797,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18837,84 +18842,6 @@
         <v>0</v>
       </c>
       <c r="V236" s="2" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>S 1827-2026</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D237" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="E237" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I237" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J237" t="n">
-        <v>0</v>
-      </c>
-      <c r="K237" t="n">
-        <v>0</v>
-      </c>
-      <c r="L237" t="n">
-        <v>0</v>
-      </c>
-      <c r="M237" t="n">
-        <v>0</v>
-      </c>
-      <c r="N237" t="n">
-        <v>0</v>
-      </c>
-      <c r="O237" t="n">
-        <v>0</v>
-      </c>
-      <c r="P237" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
-      <c r="R237" t="n">
-        <v>0</v>
-      </c>
-      <c r="S237" t="n">
-        <v>0</v>
-      </c>
-      <c r="T237" t="n">
-        <v>0</v>
-      </c>
-      <c r="U237" t="n">
-        <v>0</v>
-      </c>
-      <c r="V237" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13567-2025</t>
+          <t>A 7564-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45736</v>
+        <v>45705</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1188,49 +1188,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 7564-2025 artfynd.xlsx", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 7564-2025 karta.png", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 7564-2025 georefererad karta.tif", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 7564-2025 FSC-klagomål.docx", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 7564-2025 FSC-klagomål mail.docx", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 7564-2025 tillsynsbegäran.docx", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 7564-2025 tillsynsbegäran mail.docx", "A 7564-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 7564-2025</t>
+          <t>A 41274-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45705</v>
+        <v>45898</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1269,10 +1269,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1287,55 +1287,55 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 7564-2025 artfynd.xlsx", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 41274-2025 artfynd.xlsx", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 7564-2025 karta.png", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 41274-2025 karta.png", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 7564-2025 georefererad karta.tif", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 41274-2025 georefererad karta.tif", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 7564-2025 FSC-klagomål.docx", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 41274-2025 FSC-klagomål.docx", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 7564-2025 FSC-klagomål mail.docx", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 41274-2025 FSC-klagomål mail.docx", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 7564-2025 tillsynsbegäran.docx", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 41274-2025 tillsynsbegäran.docx", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 7564-2025 tillsynsbegäran mail.docx", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 41274-2025 tillsynsbegäran mail.docx", "A 41274-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 54444-2021</t>
+          <t>A 51642-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44473</v>
+        <v>44462</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1392,7 +1392,7 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1401,46 +1401,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Ängshök</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 41274-2025</t>
+          <t>A 51642-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45898</v>
+        <v>44462</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1506,39 +1506,39 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 41274-2025 artfynd.xlsx", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 41274-2025 karta.png", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 41274-2025 georefererad karta.tif", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 41274-2025 FSC-klagomål.docx", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 41274-2025 FSC-klagomål mail.docx", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 41274-2025 tillsynsbegäran.docx", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 41274-2025 tillsynsbegäran mail.docx", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
         <v>45924</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>45924</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45926</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 22327-2024</t>
+          <t>A 50403-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45446</v>
+        <v>44866</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1898,17 +1898,22 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1923,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1932,1110 +1937,1110 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 50403-2022 artfynd.xlsx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 50403-2022 karta.png", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 50403-2022 georefererad karta.tif", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 50403-2022 FSC-klagomål.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 50403-2022 FSC-klagomål mail.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 50403-2022 tillsynsbegäran.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 50403-2022 tillsynsbegäran mail.docx", "A 50403-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9030-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44615</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 9030-2022 artfynd.xlsx", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 9030-2022 karta.png", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 9030-2022 georefererad karta.tif", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 9030-2022 FSC-klagomål.docx", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 9030-2022 FSC-klagomål mail.docx", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 9030-2022 tillsynsbegäran.docx", "A 9030-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 9030-2022 tillsynsbegäran mail.docx", "A 9030-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 45164-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45191</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 34869-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 34869-2026 artfynd.xlsx", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 34869-2026 karta.png", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 34869-2026 georefererad karta.tif", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 34869-2026 FSC-klagomål.docx", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 34869-2026 FSC-klagomål mail.docx", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 34869-2026 tillsynsbegäran.docx", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 34869-2026 tillsynsbegäran mail.docx", "A 34869-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 62852-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 32573-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32573-2026 artfynd.xlsx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32573-2026 karta.png", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32573-2026 georefererad karta.tif", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32573-2026 FSC-klagomål.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32573-2026 FSC-klagomål mail.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32573-2026 tillsynsbegäran.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32573-2026 tillsynsbegäran mail.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 32554-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 13567-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Klubbsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 22327-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45446</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>Svinrot</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 62852-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 33532-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45519</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 60983-2023</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>45261</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>3.8</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T24" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9030-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44615</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 9030-2022 artfynd.xlsx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 9030-2022 karta.png", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 9030-2022 georefererad karta.tif", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 9030-2022 FSC-klagomål.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 9030-2022 FSC-klagomål mail.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 9030-2022 tillsynsbegäran.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 9030-2022 tillsynsbegäran mail.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 33532-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45519</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Backsippa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 51642-2021</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44462</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Vårstarr</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 51642-2021</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>44462</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Vårstarr</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 45164-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45191</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Skogsduva</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 50403-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Springkorn</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 50403-2022 artfynd.xlsx", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 50403-2022 karta.png", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 50403-2022 georefererad karta.tif", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 50403-2022 FSC-klagomål.docx", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 50403-2022 FSC-klagomål mail.docx", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 50403-2022 tillsynsbegäran.docx", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 50403-2022 tillsynsbegäran mail.docx", "A 50403-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 34869-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Backsippa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 34869-2026 artfynd.xlsx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 34869-2026 karta.png", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 34869-2026 georefererad karta.tif", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 34869-2026 FSC-klagomål.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 34869-2026 FSC-klagomål mail.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 34869-2026 tillsynsbegäran.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 34869-2026 tillsynsbegäran mail.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 32573-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32573-2026 artfynd.xlsx", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32573-2026 karta.png", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32573-2026 georefererad karta.tif", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32573-2026 FSC-klagomål.docx", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32573-2026 FSC-klagomål mail.docx", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32573-2026 tillsynsbegäran.docx", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32573-2026 tillsynsbegäran mail.docx", "A 32573-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
@@ -3056,7 +3061,7 @@
         <v>45230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3161,7 +3166,7 @@
         <v>45673</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3249,7 +3254,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32554-2026</t>
+          <t>A 54444-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3263,10 +3268,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46239</v>
+        <v>44473</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3278,29 +3283,24 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3320,39 +3320,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Ängshök</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
         <v/>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
         <v>44573</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44573</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>44545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44480</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>44692</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>44627</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50901-2024</t>
+          <t>A 34431-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45602</v>
+        <v>44792</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3904,8 +3904,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3948,7 +3953,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36401-2023</t>
+          <t>A 12253-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3967,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45152</v>
+        <v>45378</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3977,13 +3982,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4026,7 +4026,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14210-2023</t>
+          <t>A 12254-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45009</v>
+        <v>45378</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50886-2024</t>
+          <t>A 51475-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45602</v>
+        <v>45221</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16304-2024</t>
+          <t>A 53518-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45407</v>
+        <v>44879</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38300-2023</t>
+          <t>A 17707-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45161</v>
+        <v>45037</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4318,7 +4318,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 43012-2024</t>
+          <t>A 54442-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4328,14 +4328,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45567</v>
+        <v>44473</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3877-2023</t>
+          <t>A 72563-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44951</v>
+        <v>44546</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 72563-2021</t>
+          <t>A 72558-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4481,7 +4481,7 @@
         <v>44546</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64930-2023</t>
+          <t>A 66977-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45282</v>
+        <v>44522</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22328-2024</t>
+          <t>A 65921-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45446</v>
+        <v>44517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24499-2025</t>
+          <t>A 50179-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45798</v>
+        <v>45208</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18740-2025</t>
+          <t>A 39950-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45763</v>
+        <v>45553</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4785,8 +4785,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4829,7 +4834,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38299-2023</t>
+          <t>A 50570-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4843,10 +4848,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45161</v>
+        <v>45217</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4859,7 +4864,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4902,7 +4907,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27232-2025</t>
+          <t>A 10980-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4912,14 +4917,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45812</v>
+        <v>45370</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4932,7 +4937,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4975,7 +4980,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 40667-2023</t>
+          <t>A 4821-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4989,10 +4994,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45170</v>
+        <v>44957</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5005,7 +5010,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5048,7 +5053,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28663-2025</t>
+          <t>A 43012-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5058,14 +5063,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45819</v>
+        <v>45567</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5078,7 +5083,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5121,7 +5126,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9125-2023</t>
+          <t>A 28663-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5135,10 +5140,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44980</v>
+        <v>45819</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5150,13 +5155,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5199,7 +5199,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53518-2022</t>
+          <t>A 60964-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44879</v>
+        <v>45261</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30468-2025</t>
+          <t>A 15276-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45827</v>
+        <v>44659</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5301,8 +5301,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5345,7 +5350,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23781-2025</t>
+          <t>A 30468-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5359,10 +5364,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45793</v>
+        <v>45827</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5375,7 +5380,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5418,7 +5423,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15783-2022</t>
+          <t>A 1293-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5432,10 +5437,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44663</v>
+        <v>44936</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5448,7 +5453,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5491,7 +5496,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 43026-2025</t>
+          <t>A 64934-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5505,10 +5510,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45909</v>
+        <v>45282</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5521,7 +5526,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5564,7 +5569,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43032-2025</t>
+          <t>A 23781-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5578,10 +5583,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45909</v>
+        <v>45793</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5594,7 +5599,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5637,7 +5642,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31624-2025</t>
+          <t>A 31623-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5654,7 +5659,7 @@
         <v>45834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5667,7 +5672,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5710,7 +5715,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31623-2025</t>
+          <t>A 59234-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5724,10 +5729,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45834</v>
+        <v>44904</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5739,8 +5744,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5783,7 +5793,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50179-2023</t>
+          <t>A 31624-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5797,10 +5807,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45208</v>
+        <v>45834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5813,7 +5823,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5856,7 +5866,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51475-2023</t>
+          <t>A 11064-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5870,10 +5880,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45221</v>
+        <v>46079</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5886,7 +5896,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5929,7 +5939,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44757-2025</t>
+          <t>A 55730-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5943,10 +5953,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45917</v>
+        <v>44888</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5959,7 +5969,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6002,7 +6012,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7337-2023</t>
+          <t>A 15491-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6016,10 +6026,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44971</v>
+        <v>45401</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6031,8 +6041,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6075,7 +6090,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44756-2025</t>
+          <t>A 50339-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6089,10 +6104,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45917</v>
+        <v>45216</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6105,7 +6120,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6148,7 +6163,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50339-2023</t>
+          <t>A 64930-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6162,10 +6177,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45216</v>
+        <v>45282</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6178,7 +6193,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6221,7 +6236,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 46164-2025</t>
+          <t>A 24866-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6235,10 +6250,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45924</v>
+        <v>45085</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6251,7 +6266,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6294,7 +6309,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 46159-2025</t>
+          <t>A 37806-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6308,10 +6323,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45924</v>
+        <v>44810</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6324,7 +6339,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6367,7 +6382,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46144-2025</t>
+          <t>A 14928-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6381,10 +6396,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45924</v>
+        <v>46104</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6396,8 +6411,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6440,7 +6460,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37806-2022</t>
+          <t>A 15032-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6454,10 +6474,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44810</v>
+        <v>46104</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6469,8 +6489,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6513,7 +6538,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 46521-2025</t>
+          <t>A 3087-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6527,10 +6552,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45926</v>
+        <v>44946</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6542,13 +6567,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6591,7 +6611,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58412-2023</t>
+          <t>A 37802-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6605,10 +6625,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45250</v>
+        <v>44810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6621,7 +6641,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6664,7 +6684,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 63449-2023</t>
+          <t>A 16110-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6674,14 +6694,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45273</v>
+        <v>46108</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6694,7 +6714,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6737,7 +6757,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37802-2022</t>
+          <t>A 58415-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6751,10 +6771,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44810</v>
+        <v>44488</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6767,7 +6787,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6810,7 +6830,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4852-2026</t>
+          <t>A 16173-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6824,10 +6844,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46048</v>
+        <v>46111</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6839,8 +6859,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6883,7 +6908,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3678-2025</t>
+          <t>A 35447-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6897,10 +6922,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45681</v>
+        <v>45146</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6913,7 +6938,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6956,7 +6981,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 51326-2025</t>
+          <t>A 51630-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6970,10 +6995,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45950</v>
+        <v>44462</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6986,7 +7011,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7029,7 +7054,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4837-2026</t>
+          <t>A 17699-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7043,10 +7068,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46048</v>
+        <v>46121</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7059,7 +7084,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7102,7 +7127,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38199-2025</t>
+          <t>A 17700-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7116,10 +7141,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45882</v>
+        <v>46121</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7132,7 +7157,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7175,7 +7200,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 51335-2025</t>
+          <t>A 38199-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7189,10 +7214,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45950</v>
+        <v>45882</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7205,7 +7230,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7248,7 +7273,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2418-2025</t>
+          <t>A 18517-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7262,10 +7287,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45674</v>
+        <v>46127</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7277,8 +7302,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7321,7 +7351,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 65921-2021</t>
+          <t>A 63449-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7331,14 +7361,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44517</v>
+        <v>45273</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7351,7 +7381,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7394,7 +7424,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44769-2025</t>
+          <t>A 3678-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7404,14 +7434,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45917</v>
+        <v>45681</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7424,7 +7454,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7467,7 +7497,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54442-2021</t>
+          <t>A 36401-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7481,10 +7511,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44473</v>
+        <v>45152</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7496,8 +7526,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7540,7 +7575,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44770-2025</t>
+          <t>A 39965-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7550,14 +7585,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45917</v>
+        <v>45892</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7570,7 +7605,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7613,7 +7648,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 55939-2025</t>
+          <t>A 27255-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7627,10 +7662,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45973</v>
+        <v>45812</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7643,7 +7678,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7686,7 +7721,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 50181-2023</t>
+          <t>A 27251-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7700,10 +7735,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45208</v>
+        <v>45812</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7716,7 +7751,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7759,7 +7794,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 57181-2025</t>
+          <t>A 43032-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7773,10 +7808,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45979</v>
+        <v>45909</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7832,7 +7867,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 57194-2025</t>
+          <t>A 43026-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7846,10 +7881,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45979</v>
+        <v>45909</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7905,7 +7940,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 57942-2025</t>
+          <t>A 41105-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7919,10 +7954,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45982</v>
+        <v>45898</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7935,7 +7970,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7978,7 +8013,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1293-2023</t>
+          <t>A 29580-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7992,10 +8027,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44936</v>
+        <v>45825</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8051,7 +8086,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58310-2025</t>
+          <t>A 44756-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8065,10 +8100,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45985</v>
+        <v>45917</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8081,7 +8116,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8124,7 +8159,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 58321-2025</t>
+          <t>A 7337-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8138,10 +8173,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45985</v>
+        <v>44971</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8154,7 +8189,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8197,7 +8232,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 58756-2025</t>
+          <t>A 44757-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8211,10 +8246,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45986</v>
+        <v>45917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8227,7 +8262,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8270,7 +8305,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58761-2025</t>
+          <t>A 46164-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8284,10 +8319,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45986</v>
+        <v>45924</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8300,7 +8335,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8343,7 +8378,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 59105-2025</t>
+          <t>A 46144-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8357,10 +8392,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45988</v>
+        <v>45924</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8373,7 +8408,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8416,7 +8451,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11064-2026</t>
+          <t>A 31010-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8430,10 +8465,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46079</v>
+        <v>44768</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8446,7 +8481,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8489,7 +8524,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 41337-2023</t>
+          <t>A 20357-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8503,10 +8538,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45174</v>
+        <v>46139</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8519,7 +8554,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8562,7 +8597,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10984-2024</t>
+          <t>A 46159-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8576,10 +8611,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45370</v>
+        <v>45924</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8592,7 +8627,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8635,7 +8670,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 10980-2024</t>
+          <t>A 60977-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8649,10 +8684,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45370</v>
+        <v>45261</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8665,7 +8700,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8708,7 +8743,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62129-2025</t>
+          <t>A 46521-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8722,10 +8757,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46006</v>
+        <v>45926</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8737,8 +8772,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8781,7 +8821,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62123-2025</t>
+          <t>A 62447-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8795,10 +8835,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8810,8 +8850,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8854,7 +8899,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 62391-2025</t>
+          <t>A 28321-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8868,10 +8913,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46007</v>
+        <v>45818</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8883,13 +8928,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>8.300000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8932,7 +8972,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 11944-2024</t>
+          <t>A 60969-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8946,10 +8986,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45376</v>
+        <v>45261</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8962,7 +9002,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9005,7 +9045,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 63445-2025</t>
+          <t>A 38299-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9019,10 +9059,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46013</v>
+        <v>45161</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9035,7 +9075,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9078,7 +9118,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3681-2025</t>
+          <t>A 21518-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9092,10 +9132,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45681</v>
+        <v>46148</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9108,7 +9148,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9151,7 +9191,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 59234-2022</t>
+          <t>A 58800-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9161,14 +9201,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44904</v>
+        <v>44903</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9180,13 +9220,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9229,7 +9264,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 15032-2026</t>
+          <t>A 6785-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9243,10 +9278,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46104</v>
+        <v>45342</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9260,11 +9295,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9307,7 +9342,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 14928-2026</t>
+          <t>A 11944-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9321,10 +9356,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46104</v>
+        <v>45376</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9336,13 +9371,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9385,7 +9415,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 2715-2022</t>
+          <t>A 32581-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9399,10 +9429,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44580</v>
+        <v>45838</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9415,7 +9445,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9458,7 +9488,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 961-2024</t>
+          <t>A 59411-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9468,14 +9498,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45301</v>
+        <v>44907</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9487,8 +9517,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9531,7 +9566,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1013-2025</t>
+          <t>A 2073-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9545,10 +9580,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45666</v>
+        <v>46036</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9561,7 +9596,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9604,7 +9639,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 62570-2023</t>
+          <t>A 58412-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9618,10 +9653,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45269</v>
+        <v>45250</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9634,7 +9669,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9677,7 +9712,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 16110-2026</t>
+          <t>A 59410-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9687,14 +9722,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46108</v>
+        <v>44907</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9706,8 +9741,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9750,7 +9790,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 16173-2026</t>
+          <t>A 45918-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9764,10 +9804,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46111</v>
+        <v>45580</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9779,13 +9819,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9828,7 +9863,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 50883-2024</t>
+          <t>A 24139-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9842,10 +9877,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45602</v>
+        <v>46168</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9857,8 +9892,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9901,7 +9941,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 50896-2024</t>
+          <t>A 62570-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9915,10 +9955,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45602</v>
+        <v>45269</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9931,7 +9971,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9974,7 +10014,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 17700-2026</t>
+          <t>A 1011-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9988,10 +10028,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46121</v>
+        <v>45666</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10047,7 +10087,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 17699-2026</t>
+          <t>A 24786-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10061,10 +10101,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46121</v>
+        <v>46171</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10076,8 +10116,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10120,7 +10165,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 18517-2026</t>
+          <t>A 24457-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10134,10 +10179,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46127</v>
+        <v>46170</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10155,7 +10200,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10198,7 +10243,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 3087-2023</t>
+          <t>A 24903-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10208,14 +10253,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44946</v>
+        <v>46174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10227,8 +10272,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10271,7 +10321,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 29580-2025</t>
+          <t>A 24894-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10285,10 +10335,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45825</v>
+        <v>46174</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10300,8 +10350,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10344,7 +10399,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 4314-2024</t>
+          <t>A 25031-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10354,14 +10409,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45324</v>
+        <v>46174</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10375,11 +10430,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10422,7 +10477,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 12769-2024</t>
+          <t>A 51335-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10436,10 +10491,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45384</v>
+        <v>45950</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10452,7 +10507,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10495,7 +10550,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 49915-2024</t>
+          <t>A 24888-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10509,10 +10564,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45597</v>
+        <v>46174</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10524,8 +10579,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10568,7 +10628,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 27251-2025</t>
+          <t>A 24896-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10582,10 +10642,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45812</v>
+        <v>46174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10597,8 +10657,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10641,7 +10706,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 41819-2023</t>
+          <t>A 24900-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10655,10 +10720,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45176</v>
+        <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10670,8 +10735,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10714,7 +10784,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 58415-2021</t>
+          <t>A 51326-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10728,10 +10798,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44488</v>
+        <v>45950</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10744,7 +10814,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10787,7 +10857,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 41105-2025</t>
+          <t>A 14210-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10801,10 +10871,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45898</v>
+        <v>45009</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10817,7 +10887,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10860,7 +10930,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 39965-2025</t>
+          <t>A 25503-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10874,10 +10944,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45892</v>
+        <v>46177</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10889,8 +10959,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10933,7 +11008,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22307-2024</t>
+          <t>A 35404-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10947,10 +11022,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45446</v>
+        <v>45146</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10963,7 +11038,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11006,7 +11081,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 28321-2025</t>
+          <t>A 68095-2021</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11020,10 +11095,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45818</v>
+        <v>44526</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11036,7 +11111,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11079,7 +11154,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 27255-2025</t>
+          <t>A 27126-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11089,14 +11164,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45812</v>
+        <v>46188</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11108,8 +11183,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11152,7 +11232,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 34431-2022</t>
+          <t>A 27137-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11166,10 +11246,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44792</v>
+        <v>46188</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11183,11 +11263,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11230,7 +11310,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 20357-2026</t>
+          <t>A 49915-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11244,10 +11324,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46139</v>
+        <v>45597</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11260,7 +11340,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11303,7 +11383,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 31010-2022</t>
+          <t>A 44770-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11313,14 +11393,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44768</v>
+        <v>45917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11333,7 +11413,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11376,7 +11456,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 60969-2023</t>
+          <t>A 44769-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11386,14 +11466,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45261</v>
+        <v>45917</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11406,7 +11486,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11449,7 +11529,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 62447-2025</t>
+          <t>A 37631-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11463,10 +11543,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46007</v>
+        <v>45159</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11478,13 +11558,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11527,7 +11602,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 60964-2023</t>
+          <t>A 28525-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11541,10 +11616,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45261</v>
+        <v>46197</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11556,8 +11631,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11600,7 +11680,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 21518-2026</t>
+          <t>A 11270-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11614,10 +11694,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46148</v>
+        <v>44629</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11630,7 +11710,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11673,7 +11753,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 32581-2025</t>
+          <t>A 41337-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11687,10 +11767,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45838</v>
+        <v>45174</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11703,7 +11783,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11746,7 +11826,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 2073-2026</t>
+          <t>A 2800-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11760,10 +11840,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46036</v>
+        <v>45677</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11776,7 +11856,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11819,7 +11899,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 42042-2023</t>
+          <t>A 8658-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11833,10 +11913,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45177</v>
+        <v>44613</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11849,7 +11929,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11892,7 +11972,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 64934-2023</t>
+          <t>A 55939-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11906,10 +11986,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45282</v>
+        <v>45973</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11922,7 +12002,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11965,7 +12045,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 37631-2023</t>
+          <t>A 2418-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11979,10 +12059,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45159</v>
+        <v>45674</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11995,7 +12075,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12038,7 +12118,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 1011-2025</t>
+          <t>A 33010-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12052,10 +12132,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45666</v>
+        <v>46244</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12068,7 +12148,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12111,7 +12191,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 2231-2025</t>
+          <t>A 28652-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12125,10 +12205,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45673</v>
+        <v>46198</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12140,8 +12220,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12184,7 +12269,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 24139-2026</t>
+          <t>A 2231-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12198,10 +12283,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46168</v>
+        <v>45673</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12213,13 +12298,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12262,7 +12342,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 59410-2022</t>
+          <t>A 57181-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12272,14 +12352,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44907</v>
+        <v>45979</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12291,13 +12371,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12340,7 +12415,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 59411-2022</t>
+          <t>A 57194-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12350,14 +12425,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44907</v>
+        <v>45979</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12369,13 +12444,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12418,7 +12488,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24457-2026</t>
+          <t>A 57942-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12432,10 +12502,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46170</v>
+        <v>45982</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12447,13 +12517,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12496,7 +12561,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 2800-2025</t>
+          <t>A 58321-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12510,10 +12575,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45677</v>
+        <v>45985</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12526,7 +12591,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12569,7 +12634,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 25031-2026</t>
+          <t>A 58756-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12583,10 +12648,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46174</v>
+        <v>45986</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12598,13 +12663,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12647,7 +12707,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 24786-2026</t>
+          <t>A 58761-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12661,10 +12721,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46171</v>
+        <v>45986</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12676,13 +12736,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12725,7 +12780,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24900-2026</t>
+          <t>A 58310-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12739,10 +12794,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46174</v>
+        <v>45985</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12754,13 +12809,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12803,7 +12853,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24894-2026</t>
+          <t>A 44753-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12817,10 +12867,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46174</v>
+        <v>45917</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12832,13 +12882,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12881,7 +12926,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 24888-2026</t>
+          <t>A 59105-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12895,10 +12940,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46174</v>
+        <v>45988</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12910,13 +12955,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12959,7 +12999,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 24896-2026</t>
+          <t>A 34172-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12973,10 +13013,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46174</v>
+        <v>46253</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12994,7 +13034,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13037,7 +13077,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 24903-2026</t>
+          <t>A 34730-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13047,14 +13087,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46174</v>
+        <v>46258</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13072,7 +13112,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13115,7 +13155,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34521-2024</t>
+          <t>A 34748-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13129,10 +13169,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45525</v>
+        <v>46258</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13144,8 +13184,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13188,7 +13233,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 8658-2022</t>
+          <t>A 34794-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13198,14 +13243,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44613</v>
+        <v>46258</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13217,8 +13262,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13261,7 +13311,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 50570-2023</t>
+          <t>A 31161-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13275,10 +13325,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45217</v>
+        <v>46216</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13291,7 +13341,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13334,7 +13384,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 25503-2026</t>
+          <t>A 31192-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13348,10 +13398,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46177</v>
+        <v>46217</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13363,13 +13413,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13412,7 +13457,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 60977-2023</t>
+          <t>A 31193-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13426,10 +13471,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45261</v>
+        <v>46217</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13442,7 +13487,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13485,7 +13530,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 12253-2024</t>
+          <t>A 60917-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13499,10 +13544,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45378</v>
+        <v>44908</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13515,7 +13560,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13558,7 +13603,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 12254-2024</t>
+          <t>A 11478-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13572,10 +13617,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45378</v>
+        <v>45372</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13588,7 +13633,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13631,7 +13676,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 27126-2026</t>
+          <t>A 36209-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13641,14 +13686,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46188</v>
+        <v>46267</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13660,13 +13705,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13709,7 +13749,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 27137-2026</t>
+          <t>A 62129-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13723,10 +13763,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46188</v>
+        <v>46006</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13738,13 +13778,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13787,7 +13822,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 52655-2023</t>
+          <t>A 62123-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13797,14 +13832,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45225</v>
+        <v>46006</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13817,7 +13852,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13860,7 +13895,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24866-2023</t>
+          <t>A 36206-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13874,10 +13909,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45085</v>
+        <v>46267</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13890,7 +13925,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13933,7 +13968,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 39950-2024</t>
+          <t>A 34167-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13947,10 +13982,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45553</v>
+        <v>46253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13964,11 +13999,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14011,7 +14046,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 11270-2022</t>
+          <t>A 62391-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14025,10 +14060,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44629</v>
+        <v>46007</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14040,8 +14075,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14084,7 +14124,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 28652-2026</t>
+          <t>A 50181-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14098,10 +14138,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46198</v>
+        <v>45208</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14111,11 +14151,6 @@
       <c r="G173" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I173" t="n">
@@ -14162,7 +14197,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 68095-2021</t>
+          <t>A 34162-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14176,10 +14211,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44526</v>
+        <v>46253</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14191,8 +14226,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14235,7 +14275,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28525-2026</t>
+          <t>A 53520-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14249,10 +14289,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46197</v>
+        <v>44879</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14264,13 +14304,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14313,7 +14348,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 58800-2022</t>
+          <t>A 37226-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14323,14 +14358,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44903</v>
+        <v>46274</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14342,8 +14377,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14386,7 +14426,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 33010-2026</t>
+          <t>A 52655-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14396,14 +14436,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46244</v>
+        <v>45225</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14416,7 +14456,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14459,7 +14499,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 4821-2023</t>
+          <t>A 37174-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14473,10 +14513,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44957</v>
+        <v>46274</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14488,8 +14528,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14532,7 +14577,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 11478-2024</t>
+          <t>A 22307-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14546,10 +14591,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45372</v>
+        <v>45446</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14562,7 +14607,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14605,7 +14650,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 51630-2021</t>
+          <t>A 3877-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14619,10 +14664,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44462</v>
+        <v>44951</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14635,7 +14680,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14678,7 +14723,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 15491-2024</t>
+          <t>A 34834-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14692,10 +14737,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45401</v>
+        <v>46258</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14707,13 +14752,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14756,7 +14796,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 45918-2024</t>
+          <t>A 63445-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14770,10 +14810,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45580</v>
+        <v>46013</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14786,7 +14826,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14829,7 +14869,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 34172-2026</t>
+          <t>A 61012-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14843,10 +14883,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46253</v>
+        <v>45259</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14858,13 +14898,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14907,7 +14942,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 50906-2024</t>
+          <t>A 15783-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14921,10 +14956,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45602</v>
+        <v>44663</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14937,7 +14972,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14980,7 +15015,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 44753-2025</t>
+          <t>A 34521-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14994,10 +15029,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45917</v>
+        <v>45525</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15010,7 +15045,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15053,7 +15088,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 6785-2024</t>
+          <t>A 31929-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15067,10 +15102,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45342</v>
+        <v>46232</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15082,13 +15117,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15131,7 +15161,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 55730-2022</t>
+          <t>A 37367-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15145,10 +15175,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44888</v>
+        <v>46275</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15161,7 +15191,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15204,7 +15234,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 31161-2026</t>
+          <t>A 28131-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15218,10 +15248,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46216</v>
+        <v>46195</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15234,7 +15264,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15277,7 +15307,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 53520-2022</t>
+          <t>A 37364-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15291,10 +15321,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44879</v>
+        <v>46275</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15307,7 +15337,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15350,7 +15380,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 34794-2026</t>
+          <t>A 37353-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15360,14 +15390,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46258</v>
+        <v>46275</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15379,13 +15409,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15428,7 +15453,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 34730-2026</t>
+          <t>A 37355-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15442,10 +15467,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46258</v>
+        <v>46275</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15457,13 +15482,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15506,7 +15526,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 35404-2023</t>
+          <t>A 1013-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15520,10 +15540,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45146</v>
+        <v>45666</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15536,7 +15556,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15579,7 +15599,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 34748-2026</t>
+          <t>A 31928-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15593,10 +15613,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46258</v>
+        <v>46232</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15608,13 +15628,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15657,7 +15672,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31193-2026</t>
+          <t>A 31930-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15671,10 +15686,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46217</v>
+        <v>46232</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15687,7 +15702,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15730,7 +15745,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 31192-2026</t>
+          <t>A 37888-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15744,10 +15759,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46217</v>
+        <v>46279</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15759,8 +15774,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15803,7 +15823,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 61012-2023</t>
+          <t>A 32317-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15817,10 +15837,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45259</v>
+        <v>46237</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15833,7 +15853,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15876,7 +15896,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 60917-2022</t>
+          <t>A 32558-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15890,10 +15910,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44908</v>
+        <v>46239</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15905,8 +15925,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15949,7 +15974,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 36206-2026</t>
+          <t>A 32574-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15963,10 +15988,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46267</v>
+        <v>46239</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15978,8 +16003,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16022,7 +16052,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 15467-2023</t>
+          <t>A 32564-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16036,10 +16066,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45020</v>
+        <v>46239</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16051,8 +16081,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16095,7 +16130,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 72558-2021</t>
+          <t>A 2715-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16109,10 +16144,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44546</v>
+        <v>44580</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16125,7 +16160,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16168,7 +16203,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 36209-2026</t>
+          <t>A 4837-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16182,10 +16217,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46267</v>
+        <v>46048</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16198,7 +16233,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16241,7 +16276,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 35447-2023</t>
+          <t>A 4852-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16255,10 +16290,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45146</v>
+        <v>46048</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16271,7 +16306,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16314,7 +16349,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 34167-2026</t>
+          <t>A 4314-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16324,14 +16359,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46253</v>
+        <v>45324</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16345,11 +16380,11 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16392,7 +16427,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 79-2024</t>
+          <t>A 3681-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16402,14 +16437,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45293</v>
+        <v>45681</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16422,7 +16457,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16465,7 +16500,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 34162-2026</t>
+          <t>A 41819-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16479,10 +16514,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46253</v>
+        <v>45176</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16494,13 +16529,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16543,7 +16573,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 34834-2026</t>
+          <t>A 50883-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16557,10 +16587,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46258</v>
+        <v>45602</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16573,7 +16603,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16616,7 +16646,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37226-2026</t>
+          <t>A 50896-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16630,10 +16660,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46274</v>
+        <v>45602</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16645,13 +16675,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16694,7 +16719,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 37355-2026</t>
+          <t>A 10984-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16708,10 +16733,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46275</v>
+        <v>45370</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16724,7 +16749,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16767,7 +16792,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 37174-2026</t>
+          <t>A 15467-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16781,10 +16806,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46274</v>
+        <v>45020</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16796,13 +16821,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16845,7 +16865,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37364-2026</t>
+          <t>A 40667-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16859,10 +16879,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46275</v>
+        <v>45170</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16875,7 +16895,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16918,7 +16938,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 31928-2026</t>
+          <t>A 42042-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16932,10 +16952,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46232</v>
+        <v>45177</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16948,7 +16968,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16991,7 +17011,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37353-2026</t>
+          <t>A 50886-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17005,10 +17025,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46275</v>
+        <v>45602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17021,7 +17041,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17064,7 +17084,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 37367-2026</t>
+          <t>A 50901-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17078,10 +17098,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46275</v>
+        <v>45602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17094,7 +17114,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17137,7 +17157,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 66977-2021</t>
+          <t>A 12769-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17151,10 +17171,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44522</v>
+        <v>45384</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17167,7 +17187,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17210,7 +17230,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31929-2026</t>
+          <t>A 50906-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17224,10 +17244,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46232</v>
+        <v>45602</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17240,7 +17260,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17283,7 +17303,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 31930-2026</t>
+          <t>A 9125-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17297,10 +17317,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46232</v>
+        <v>44980</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17312,8 +17332,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17356,7 +17381,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 37888-2026</t>
+          <t>A 16304-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17370,10 +17395,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46279</v>
+        <v>45407</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17385,13 +17410,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17434,7 +17454,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 28131-2026</t>
+          <t>A 22328-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17448,10 +17468,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46195</v>
+        <v>45446</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17464,7 +17484,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17507,7 +17527,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 15276-2022</t>
+          <t>A 79-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17517,14 +17537,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44659</v>
+        <v>45293</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17536,13 +17556,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17585,7 +17600,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 17707-2023</t>
+          <t>A 961-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17599,10 +17614,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45037</v>
+        <v>45301</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17615,7 +17630,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17658,7 +17673,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 46248-2024</t>
+          <t>A 38300-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17672,10 +17687,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45581</v>
+        <v>45161</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17688,7 +17703,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17731,7 +17746,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 32574-2026</t>
+          <t>A 46248-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17745,10 +17760,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46239</v>
+        <v>45581</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17760,13 +17775,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17826,7 +17836,7 @@
         <v>45261</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17882,7 +17892,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 32558-2026</t>
+          <t>A 49971-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17896,10 +17906,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46239</v>
+        <v>45215</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17911,13 +17921,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17960,7 +17965,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 32564-2026</t>
+          <t>A 38278-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17970,14 +17975,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46239</v>
+        <v>45545</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17989,13 +17994,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18038,7 +18038,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 34664-2024</t>
+          <t>A 12675-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18052,10 +18052,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45526</v>
+        <v>45384</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18111,7 +18111,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 32317-2026</t>
+          <t>A 37083-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18125,10 +18125,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46237</v>
+        <v>45539</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18184,7 +18184,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 37083-2024</t>
+          <t>A 13560-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45539</v>
+        <v>45736</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18257,7 +18257,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 12675-2024</t>
+          <t>A 34664-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18271,10 +18271,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45384</v>
+        <v>45526</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18330,7 +18330,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 49971-2023</t>
+          <t>A 23114-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18344,10 +18344,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45215</v>
+        <v>45791</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18403,7 +18403,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 13560-2025</t>
+          <t>A 2749-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18417,10 +18417,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45736</v>
+        <v>45314</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18476,7 +18476,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 38278-2024</t>
+          <t>A 57284-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18486,14 +18486,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45545</v>
+        <v>45629</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18549,7 +18549,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 23114-2025</t>
+          <t>A 24499-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18563,10 +18563,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45791</v>
+        <v>45798</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18622,7 +18622,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 57284-2024</t>
+          <t>A 18740-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18636,10 +18636,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45629</v>
+        <v>45763</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18695,7 +18695,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 2749-2024</t>
+          <t>A 27232-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18705,14 +18705,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45314</v>
+        <v>45812</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18785,7 +18785,7 @@
         <v>46197</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>

--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>45736</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>45446</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>45898</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44462</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44462</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45261</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45924</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45924</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45926</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44615</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45519</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>46008</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>45191</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>44866</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>46255</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45673</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>46239</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44473</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44573</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44573</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>44545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44480</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>44692</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>44627</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>44951</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>45009</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>45152</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>45602</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45602</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>45161</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>45567</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45407</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>44546</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>45446</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45282</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45161</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>45170</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>44980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>44879</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>44663</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>45208</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>45221</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>44971</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45250</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>45273</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45681</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>45674</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>44517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>44473</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>45208</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>45812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>45898</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>44936</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>45892</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45818</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>45174</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45812</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>45370</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45370</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>46139</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44768</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>45909</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45909</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>46007</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>45376</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>45917</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>45917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>45681</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>45924</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>45924</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>45924</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44904</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>45926</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>44580</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45301</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45666</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45269</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45602</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45602</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>46148</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>45950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45950</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44946</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45838</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>45324</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>46036</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45384</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45917</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45917</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>45597</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45973</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>45176</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>44488</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>45979</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45979</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45446</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>45982</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45985</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45985</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44792</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>45986</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45986</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>45988</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>45261</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45261</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>46006</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>46006</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>46007</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>45666</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>46013</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>46168</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>45177</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>46170</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>46174</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>46171</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>46174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>46174</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>46174</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>46174</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>45282</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45159</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>45673</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>46048</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>46048</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44907</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44907</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>45677</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>46177</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45525</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44613</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45217</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>46079</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45261</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45378</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45378</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>46188</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>46188</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45225</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45085</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45553</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44629</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>46104</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>46104</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>46198</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>44526</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>46108</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>46197</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>46111</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44903</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>46244</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44957</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45372</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>46121</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>44462</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>46121</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>46127</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45401</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45580</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45825</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45602</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>45342</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44888</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44879</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45146</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>46253</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45259</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45020</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44546</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45917</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>46216</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45146</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45293</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>46258</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>46258</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>46258</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>46217</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>46217</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44522</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>44908</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>46267</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>46267</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>46253</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>44659</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45037</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>45581</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>46253</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45261</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>46258</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>46274</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>46275</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>46274</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>46275</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>46232</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>45526</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>46275</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>46275</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>46232</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>46232</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>46279</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>46195</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45539</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45384</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45215</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45736</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45545</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45791</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45629</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45314</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>46237</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>46239</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>46239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>46239</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45798</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45763</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>45812</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>45819</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>45827</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>45793</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>45834</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45834</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45216</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>44810</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44810</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45882</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>46197</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>

--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>45736</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>45446</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 41274-2025</t>
+          <t>A 7564-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45898</v>
+        <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1374,10 +1374,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1392,160 +1392,160 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 7564-2025 artfynd.xlsx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 7564-2025 karta.png", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 7564-2025 georefererad karta.tif", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 7564-2025 FSC-klagomål.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 7564-2025 FSC-klagomål mail.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 7564-2025 tillsynsbegäran.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 7564-2025 tillsynsbegäran mail.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 41274-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45898</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 41274-2025 artfynd.xlsx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 41274-2025 karta.png", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 41274-2025 georefererad karta.tif", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 41274-2025 FSC-klagomål.docx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 41274-2025 FSC-klagomål mail.docx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 41274-2025 tillsynsbegäran.docx", "A 41274-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 41274-2025 tillsynsbegäran mail.docx", "A 41274-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 7564-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45705</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Solvända</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 7564-2025 artfynd.xlsx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 7564-2025 karta.png", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 7564-2025 georefererad karta.tif", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 7564-2025 FSC-klagomål.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 7564-2025 FSC-klagomål mail.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 7564-2025 tillsynsbegäran.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 7564-2025 tillsynsbegäran mail.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 51642-2021</t>
+          <t>A 46156-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44462</v>
+        <v>45924</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1575,16 +1575,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1615,572 +1615,572 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46156-2025 artfynd.xlsx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46156-2025 karta.png", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46156-2025 georefererad karta.tif", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46156-2025 FSC-klagomål.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46156-2025 FSC-klagomål mail.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46156-2025 tillsynsbegäran.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46156-2025 tillsynsbegäran mail.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 46123-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45924</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46123-2025 artfynd.xlsx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46123-2025 karta.png", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46123-2025 georefererad karta.tif", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/knärot/A 46123-2025 karta knärot.png", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46123-2025 FSC-klagomål.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46123-2025 FSC-klagomål mail.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46123-2025 tillsynsbegäran.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46123-2025 tillsynsbegäran mail.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 46522-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45926</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 51642-2021</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44462</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Vårstarr</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 51642-2021</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>44462</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>2.9</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Vårstarr</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 60983-2023</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>45261</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>3.8</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 46156-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45924</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46156-2025 artfynd.xlsx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46156-2025 karta.png", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46156-2025 georefererad karta.tif", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46156-2025 FSC-klagomål.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46156-2025 FSC-klagomål mail.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46156-2025 tillsynsbegäran.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46156-2025 tillsynsbegäran mail.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 46123-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45924</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46123-2025 artfynd.xlsx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46123-2025 karta.png", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46123-2025 georefererad karta.tif", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="Z15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/knärot/A 46123-2025 karta knärot.png", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46123-2025 FSC-klagomål.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46123-2025 FSC-klagomål mail.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46123-2025 tillsynsbegäran.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46123-2025 tillsynsbegäran mail.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 46522-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45926</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44615</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33532-2024</t>
+          <t>A 62852-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45519</v>
+        <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2318,20 +2318,25 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2343,10 +2348,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2359,148 +2364,143 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 33532-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45519</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>Backsippa</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 62852-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>45191</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>44866</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>46255</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 53521-2023</t>
+          <t>A 32573-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45230</v>
+        <v>46239</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2853,18 +2853,23 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -2878,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2894,363 +2899,358 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32573-2026 artfynd.xlsx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32573-2026 karta.png", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32573-2026 georefererad karta.tif", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32573-2026 FSC-klagomål.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32573-2026 FSC-klagomål mail.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32573-2026 tillsynsbegäran.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32573-2026 tillsynsbegäran mail.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 32554-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 53521-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45230</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>Skogsduva</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 53521-2023 artfynd.xlsx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 53521-2023 karta.png", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 53521-2023 georefererad karta.tif", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 53521-2023 FSC-klagomål.docx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 53521-2023 FSC-klagomål mail.docx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 53521-2023 tillsynsbegäran.docx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 53521-2023 tillsynsbegäran mail.docx", "A 53521-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 2230-2025</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>45673</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>1.6</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 2230-2025 artfynd.xlsx", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 2230-2025 karta.png", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 2230-2025 georefererad karta.tif", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 2230-2025 FSC-klagomål.docx", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 2230-2025 FSC-klagomål mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 2230-2025 tillsynsbegäran.docx", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 2230-2025 tillsynsbegäran mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 32573-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32573-2026 artfynd.xlsx", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32573-2026 karta.png", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32573-2026 georefererad karta.tif", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32573-2026 FSC-klagomål.docx", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32573-2026 FSC-klagomål mail.docx", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32573-2026 tillsynsbegäran.docx", "A 32573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32573-2026 tillsynsbegäran mail.docx", "A 32573-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 32554-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Purpurknipprot</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44473</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44573</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44573</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>44545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44480</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>44692</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>44627</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3877-2023</t>
+          <t>A 50901-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44951</v>
+        <v>45602</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 14210-2023</t>
+          <t>A 36401-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45009</v>
+        <v>45152</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3977,8 +3977,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4021,7 +4026,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 36401-2023</t>
+          <t>A 14210-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4035,10 +4040,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45152</v>
+        <v>45009</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4050,13 +4055,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
         <v>45602</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50901-2024</t>
+          <t>A 38300-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45602</v>
+        <v>45161</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38300-2023</t>
+          <t>A 43012-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4255,14 +4255,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45161</v>
+        <v>45567</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4318,7 +4318,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 43012-2024</t>
+          <t>A 16304-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4328,14 +4328,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45567</v>
+        <v>45407</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16304-2024</t>
+          <t>A 72563-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45407</v>
+        <v>44546</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 72563-2021</t>
+          <t>A 3877-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44546</v>
+        <v>44951</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4554,7 +4554,7 @@
         <v>45446</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45282</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38299-2023</t>
+          <t>A 40667-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45161</v>
+        <v>45170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40667-2023</t>
+          <t>A 9125-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45170</v>
+        <v>44980</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4785,8 +4785,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4829,7 +4834,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9125-2023</t>
+          <t>A 53518-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4843,10 +4848,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44980</v>
+        <v>44879</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4858,13 +4863,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53518-2022</t>
+          <t>A 15783-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44879</v>
+        <v>44663</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15783-2022</t>
+          <t>A 50179-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44663</v>
+        <v>45208</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 50179-2023</t>
+          <t>A 51475-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45208</v>
+        <v>45221</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 51475-2023</t>
+          <t>A 38299-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45221</v>
+        <v>45161</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5216,7 +5216,7 @@
         <v>44971</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45250</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>45273</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45681</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2418-2025</t>
+          <t>A 29580-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45674</v>
+        <v>45825</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5564,7 +5564,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 65921-2021</t>
+          <t>A 2418-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44517</v>
+        <v>45674</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5637,7 +5637,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54442-2021</t>
+          <t>A 65921-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44473</v>
+        <v>44517</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50181-2023</t>
+          <t>A 38199-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45208</v>
+        <v>45882</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27251-2025</t>
+          <t>A 54442-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45812</v>
+        <v>44473</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5856,7 +5856,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41105-2025</t>
+          <t>A 27251-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45898</v>
+        <v>45812</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5929,7 +5929,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1293-2023</t>
+          <t>A 41105-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5943,10 +5943,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44936</v>
+        <v>45898</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39965-2025</t>
+          <t>A 50181-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45892</v>
+        <v>45208</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28321-2025</t>
+          <t>A 39965-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45818</v>
+        <v>45892</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6148,7 +6148,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 41337-2023</t>
+          <t>A 28321-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45174</v>
+        <v>45818</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6221,7 +6221,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 27255-2025</t>
+          <t>A 43026-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6235,10 +6235,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45812</v>
+        <v>45909</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10984-2024</t>
+          <t>A 43032-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6308,10 +6308,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45370</v>
+        <v>45909</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6367,7 +6367,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10980-2024</t>
+          <t>A 27255-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45370</v>
+        <v>45812</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6440,7 +6440,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20357-2026</t>
+          <t>A 44757-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46139</v>
+        <v>45917</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6513,7 +6513,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31010-2022</t>
+          <t>A 44756-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44768</v>
+        <v>45917</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6586,7 +6586,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43026-2025</t>
+          <t>A 20357-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45909</v>
+        <v>46139</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43032-2025</t>
+          <t>A 31010-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45909</v>
+        <v>44768</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6732,7 +6732,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 62447-2025</t>
+          <t>A 1293-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46007</v>
+        <v>44936</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6761,13 +6761,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6810,7 +6805,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11944-2024</t>
+          <t>A 46164-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6824,10 +6819,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45376</v>
+        <v>45924</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6840,7 +6835,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6883,7 +6878,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44757-2025</t>
+          <t>A 46159-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6897,10 +6892,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6913,7 +6908,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6956,7 +6951,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 44756-2025</t>
+          <t>A 46144-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6970,10 +6965,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6986,7 +6981,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7029,7 +7024,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3681-2025</t>
+          <t>A 46521-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7043,10 +7038,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45681</v>
+        <v>45926</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7058,8 +7053,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7102,7 +7102,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46164-2025</t>
+          <t>A 41337-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7116,10 +7116,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45924</v>
+        <v>45174</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 46159-2025</t>
+          <t>A 10984-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7189,10 +7189,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45924</v>
+        <v>45370</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46144-2025</t>
+          <t>A 62447-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45924</v>
+        <v>46007</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7277,8 +7277,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7321,7 +7326,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59234-2022</t>
+          <t>A 10980-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7335,10 +7340,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44904</v>
+        <v>45370</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7350,13 +7355,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7399,7 +7399,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46521-2025</t>
+          <t>A 21518-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45926</v>
+        <v>46148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7428,13 +7428,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7477,7 +7472,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 2715-2022</t>
+          <t>A 32581-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7491,10 +7486,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44580</v>
+        <v>45838</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7507,7 +7502,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7550,7 +7545,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 961-2024</t>
+          <t>A 2073-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7564,10 +7559,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45301</v>
+        <v>46036</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7580,7 +7575,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7623,7 +7618,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1013-2025</t>
+          <t>A 11944-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7637,10 +7632,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45666</v>
+        <v>45376</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7653,7 +7648,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7696,7 +7691,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62570-2023</t>
+          <t>A 3681-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7710,10 +7705,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45269</v>
+        <v>45681</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7726,7 +7721,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7769,7 +7764,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 50883-2024</t>
+          <t>A 51326-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7783,10 +7778,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45602</v>
+        <v>45950</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7799,7 +7794,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7842,7 +7837,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 50896-2024</t>
+          <t>A 51335-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7856,10 +7851,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45602</v>
+        <v>45950</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7872,7 +7867,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7915,7 +7910,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21518-2026</t>
+          <t>A 59234-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7929,10 +7924,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46148</v>
+        <v>44904</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7944,8 +7939,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51326-2025</t>
+          <t>A 44769-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45950</v>
+        <v>45917</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 51335-2025</t>
+          <t>A 2715-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45950</v>
+        <v>44580</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3087-2023</t>
+          <t>A 44770-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8144,14 +8144,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44946</v>
+        <v>45917</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 32581-2025</t>
+          <t>A 961-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45838</v>
+        <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 4314-2024</t>
+          <t>A 1013-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8290,14 +8290,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45324</v>
+        <v>45666</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8309,13 +8309,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8358,7 +8353,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 2073-2026</t>
+          <t>A 55939-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8372,10 +8367,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46036</v>
+        <v>45973</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8388,7 +8383,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8431,7 +8426,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12769-2024</t>
+          <t>A 62570-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8445,10 +8440,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45384</v>
+        <v>45269</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8461,7 +8456,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8504,7 +8499,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 44769-2025</t>
+          <t>A 57194-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8514,14 +8509,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45917</v>
+        <v>45979</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8534,7 +8529,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8577,7 +8572,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 44770-2025</t>
+          <t>A 1011-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8587,14 +8582,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45917</v>
+        <v>45666</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8650,7 +8645,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 49915-2024</t>
+          <t>A 50883-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8664,10 +8659,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45597</v>
+        <v>45602</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8680,7 +8675,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8723,7 +8718,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 55939-2025</t>
+          <t>A 50896-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8737,10 +8732,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45973</v>
+        <v>45602</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8753,7 +8748,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8796,7 +8791,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 41819-2023</t>
+          <t>A 57942-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8810,10 +8805,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45176</v>
+        <v>45982</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8826,7 +8821,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8869,7 +8864,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58415-2021</t>
+          <t>A 58310-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8883,10 +8878,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44488</v>
+        <v>45985</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8899,7 +8894,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8942,7 +8937,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 57181-2025</t>
+          <t>A 58321-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8956,10 +8951,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45979</v>
+        <v>45985</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8972,7 +8967,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9015,7 +9010,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 57194-2025</t>
+          <t>A 58756-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9029,10 +9024,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45979</v>
+        <v>45986</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9045,7 +9040,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9088,7 +9083,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22307-2024</t>
+          <t>A 24139-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9102,10 +9097,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45446</v>
+        <v>46168</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9117,8 +9112,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9161,7 +9161,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57942-2025</t>
+          <t>A 58761-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9234,7 +9234,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 58310-2025</t>
+          <t>A 59105-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9248,10 +9248,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45985</v>
+        <v>45988</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9307,7 +9307,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 58321-2025</t>
+          <t>A 3087-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45985</v>
+        <v>44946</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9380,7 +9380,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 34431-2022</t>
+          <t>A 24457-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44792</v>
+        <v>46170</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9411,11 +9411,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9458,7 +9458,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58756-2025</t>
+          <t>A 25031-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45986</v>
+        <v>46174</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9487,8 +9487,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9531,7 +9536,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 58761-2025</t>
+          <t>A 24786-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9545,10 +9550,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45986</v>
+        <v>46171</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9560,8 +9565,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9604,7 +9614,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 59105-2025</t>
+          <t>A 24900-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9618,10 +9628,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45988</v>
+        <v>46174</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9633,8 +9643,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9677,7 +9692,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 60969-2023</t>
+          <t>A 24894-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9691,10 +9706,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45261</v>
+        <v>46174</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9706,8 +9721,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9750,7 +9770,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 60964-2023</t>
+          <t>A 24888-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9764,10 +9784,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45261</v>
+        <v>46174</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9779,8 +9799,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9823,7 +9848,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62129-2025</t>
+          <t>A 24896-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9837,10 +9862,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46006</v>
+        <v>46174</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9852,8 +9877,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9896,7 +9926,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 62123-2025</t>
+          <t>A 24903-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9906,14 +9936,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46006</v>
+        <v>46174</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9925,8 +9955,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9969,7 +10004,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 62391-2025</t>
+          <t>A 4314-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9979,14 +10014,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46007</v>
+        <v>45324</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10004,7 +10039,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>8.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10047,7 +10082,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1011-2025</t>
+          <t>A 12769-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10061,10 +10096,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45666</v>
+        <v>45384</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10077,7 +10112,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10120,7 +10155,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 63445-2025</t>
+          <t>A 62129-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10134,10 +10169,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46013</v>
+        <v>46006</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10150,7 +10185,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10193,7 +10228,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 24139-2026</t>
+          <t>A 62123-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10207,10 +10242,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46168</v>
+        <v>46006</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10222,13 +10257,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10271,7 +10301,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 42042-2023</t>
+          <t>A 49915-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10285,10 +10315,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45177</v>
+        <v>45597</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10301,7 +10331,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10344,7 +10374,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 24457-2026</t>
+          <t>A 62391-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10358,10 +10388,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46170</v>
+        <v>46007</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10375,11 +10405,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10422,7 +10452,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 25031-2026</t>
+          <t>A 25503-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10436,10 +10466,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10457,7 +10487,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10500,7 +10530,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 24786-2026</t>
+          <t>A 63445-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10514,10 +10544,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46171</v>
+        <v>46013</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10529,13 +10559,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10578,7 +10603,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 24900-2026</t>
+          <t>A 41819-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10592,10 +10617,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46174</v>
+        <v>45176</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10607,13 +10632,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10656,7 +10676,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 24894-2026</t>
+          <t>A 58415-2021</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10670,10 +10690,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46174</v>
+        <v>44488</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10685,13 +10705,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10734,7 +10749,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 24888-2026</t>
+          <t>A 22307-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10748,10 +10763,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46174</v>
+        <v>45446</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10763,13 +10778,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10812,7 +10822,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 24896-2026</t>
+          <t>A 34431-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10826,10 +10836,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46174</v>
+        <v>44792</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10843,11 +10853,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.3</v>
+        <v>6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10890,7 +10900,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24903-2026</t>
+          <t>A 27126-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10904,10 +10914,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10925,7 +10935,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10968,7 +10978,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 64934-2023</t>
+          <t>A 27137-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10982,10 +10992,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45282</v>
+        <v>46188</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10997,8 +11007,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11041,7 +11056,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 37631-2023</t>
+          <t>A 4852-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11055,10 +11070,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45159</v>
+        <v>46048</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11071,7 +11086,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11114,7 +11129,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 2231-2025</t>
+          <t>A 4837-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11128,10 +11143,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45673</v>
+        <v>46048</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11144,7 +11159,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11187,7 +11202,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 4852-2026</t>
+          <t>A 60969-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11201,10 +11216,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46048</v>
+        <v>45261</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11217,7 +11232,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11260,7 +11275,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 4837-2026</t>
+          <t>A 60964-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11274,10 +11289,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46048</v>
+        <v>45261</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11290,7 +11305,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11333,7 +11348,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 59410-2022</t>
+          <t>A 28652-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11343,14 +11358,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44907</v>
+        <v>46198</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11411,7 +11426,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 59411-2022</t>
+          <t>A 28525-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11421,14 +11436,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44907</v>
+        <v>46197</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11446,7 +11461,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11489,7 +11504,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 2800-2025</t>
+          <t>A 11064-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11503,10 +11518,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45677</v>
+        <v>46079</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11519,7 +11534,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11562,7 +11577,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 25503-2026</t>
+          <t>A 42042-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11576,10 +11591,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46177</v>
+        <v>45177</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11591,13 +11606,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11640,7 +11650,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 34521-2024</t>
+          <t>A 15032-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11654,10 +11664,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45525</v>
+        <v>46104</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11669,8 +11679,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11713,7 +11728,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 8658-2022</t>
+          <t>A 14928-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11727,10 +11742,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44613</v>
+        <v>46104</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11742,8 +11757,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11786,7 +11806,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 50570-2023</t>
+          <t>A 64934-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11800,10 +11820,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45217</v>
+        <v>45282</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11816,7 +11836,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11859,7 +11879,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 11064-2026</t>
+          <t>A 37631-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11873,10 +11893,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46079</v>
+        <v>45159</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11889,7 +11909,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11932,7 +11952,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 60977-2023</t>
+          <t>A 16110-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11946,10 +11966,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45261</v>
+        <v>46108</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11962,7 +11982,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12005,7 +12025,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 12253-2024</t>
+          <t>A 2231-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12019,10 +12039,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45378</v>
+        <v>45673</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12078,7 +12098,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 12254-2024</t>
+          <t>A 16173-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12092,10 +12112,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45378</v>
+        <v>46111</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12107,8 +12127,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12151,7 +12176,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 27126-2026</t>
+          <t>A 59410-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12165,10 +12190,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46188</v>
+        <v>44907</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12229,7 +12254,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 27137-2026</t>
+          <t>A 59411-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12239,14 +12264,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46188</v>
+        <v>44907</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12264,7 +12289,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12307,7 +12332,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 52655-2023</t>
+          <t>A 2800-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12317,14 +12342,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45225</v>
+        <v>45677</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12337,7 +12362,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12380,7 +12405,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24866-2023</t>
+          <t>A 17700-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12394,10 +12419,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45085</v>
+        <v>46121</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12410,7 +12435,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12453,7 +12478,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 39950-2024</t>
+          <t>A 17699-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12467,10 +12492,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45553</v>
+        <v>46121</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12482,13 +12507,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12531,7 +12551,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 11270-2022</t>
+          <t>A 34521-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12545,10 +12565,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44629</v>
+        <v>45525</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12561,7 +12581,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12604,7 +12624,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 15032-2026</t>
+          <t>A 18517-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12618,10 +12638,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46104</v>
+        <v>46127</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12639,7 +12659,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12682,7 +12702,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 14928-2026</t>
+          <t>A 8658-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12696,10 +12716,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46104</v>
+        <v>44613</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12711,13 +12731,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12760,7 +12775,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 28652-2026</t>
+          <t>A 50570-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12774,10 +12789,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46198</v>
+        <v>45217</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12789,13 +12804,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12838,7 +12848,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 68095-2021</t>
+          <t>A 60977-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12852,10 +12862,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44526</v>
+        <v>45261</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12868,7 +12878,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12911,7 +12921,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 16110-2026</t>
+          <t>A 12253-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12925,10 +12935,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46108</v>
+        <v>45378</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12941,7 +12951,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12984,7 +12994,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 28525-2026</t>
+          <t>A 12254-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12998,10 +13008,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46197</v>
+        <v>45378</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13013,13 +13023,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13062,7 +13067,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 16173-2026</t>
+          <t>A 34172-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13076,10 +13081,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46111</v>
+        <v>46253</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13097,7 +13102,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13140,7 +13145,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58800-2022</t>
+          <t>A 52655-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13154,10 +13159,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44903</v>
+        <v>45225</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13170,7 +13175,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13213,7 +13218,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 33010-2026</t>
+          <t>A 24866-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13227,10 +13232,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46244</v>
+        <v>45085</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13243,7 +13248,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13286,7 +13291,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4821-2023</t>
+          <t>A 44753-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13300,10 +13305,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44957</v>
+        <v>45917</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13316,7 +13321,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13359,7 +13364,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 11478-2024</t>
+          <t>A 39950-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13373,10 +13378,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45372</v>
+        <v>45553</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13388,8 +13393,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13432,7 +13442,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 17700-2026</t>
+          <t>A 11270-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13446,10 +13456,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46121</v>
+        <v>44629</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13462,7 +13472,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13505,7 +13515,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 51630-2021</t>
+          <t>A 31161-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13519,10 +13529,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44462</v>
+        <v>46216</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13535,7 +13545,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13578,7 +13588,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 17699-2026</t>
+          <t>A 34794-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13588,14 +13598,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46121</v>
+        <v>46258</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13607,8 +13617,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13651,7 +13666,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18517-2026</t>
+          <t>A 34730-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13665,10 +13680,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46127</v>
+        <v>46258</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13686,7 +13701,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13729,7 +13744,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 15491-2024</t>
+          <t>A 68095-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13743,10 +13758,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45401</v>
+        <v>44526</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13758,13 +13773,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13807,7 +13817,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 45918-2024</t>
+          <t>A 34748-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13821,10 +13831,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45580</v>
+        <v>46258</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13836,8 +13846,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13880,7 +13895,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 29580-2025</t>
+          <t>A 31193-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13894,10 +13909,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45825</v>
+        <v>46217</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13910,7 +13925,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13953,7 +13968,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 50906-2024</t>
+          <t>A 58800-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13963,14 +13978,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45602</v>
+        <v>44903</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13983,7 +13998,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14026,7 +14041,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 6785-2024</t>
+          <t>A 4821-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14040,10 +14055,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45342</v>
+        <v>44957</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14055,13 +14070,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14104,7 +14114,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 55730-2022</t>
+          <t>A 31192-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14118,10 +14128,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44888</v>
+        <v>46217</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14134,7 +14144,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14177,7 +14187,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 53520-2022</t>
+          <t>A 11478-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14191,10 +14201,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44879</v>
+        <v>45372</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14207,7 +14217,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14250,7 +14260,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 35404-2023</t>
+          <t>A 51630-2021</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14264,10 +14274,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45146</v>
+        <v>44462</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14280,7 +14290,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14323,7 +14333,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 34172-2026</t>
+          <t>A 60917-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14337,10 +14347,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46253</v>
+        <v>44908</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14352,13 +14362,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14401,7 +14406,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 61012-2023</t>
+          <t>A 36206-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14415,10 +14420,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45259</v>
+        <v>46267</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14431,7 +14436,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14474,7 +14479,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 15467-2023</t>
+          <t>A 15491-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14488,10 +14493,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45020</v>
+        <v>45401</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14503,8 +14508,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14547,7 +14557,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 72558-2021</t>
+          <t>A 36209-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14561,10 +14571,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44546</v>
+        <v>46267</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14577,7 +14587,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14620,7 +14630,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 44753-2025</t>
+          <t>A 45918-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14634,10 +14644,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45917</v>
+        <v>45580</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14650,7 +14660,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14693,7 +14703,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31161-2026</t>
+          <t>A 34167-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14707,10 +14717,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46216</v>
+        <v>46253</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14722,8 +14732,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14766,7 +14781,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35447-2023</t>
+          <t>A 50906-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14780,10 +14795,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45146</v>
+        <v>45602</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14796,7 +14811,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14839,7 +14854,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 79-2024</t>
+          <t>A 34162-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14849,14 +14864,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45293</v>
+        <v>46253</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14868,8 +14883,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14912,7 +14932,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 34794-2026</t>
+          <t>A 6785-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14922,14 +14942,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46258</v>
+        <v>45342</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14943,11 +14963,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14990,7 +15010,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34730-2026</t>
+          <t>A 55730-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15004,10 +15024,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46258</v>
+        <v>44888</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15019,13 +15039,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15068,7 +15083,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34748-2026</t>
+          <t>A 53520-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15082,10 +15097,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46258</v>
+        <v>44879</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15097,13 +15112,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15146,7 +15156,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 31193-2026</t>
+          <t>A 34834-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15160,10 +15170,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46217</v>
+        <v>46258</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15176,7 +15186,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15219,7 +15229,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 31192-2026</t>
+          <t>A 37226-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15233,10 +15243,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46217</v>
+        <v>46274</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15248,8 +15258,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15292,7 +15307,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 66977-2021</t>
+          <t>A 37355-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15306,10 +15321,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44522</v>
+        <v>46275</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15322,7 +15337,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15365,7 +15380,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 60917-2022</t>
+          <t>A 37174-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15379,10 +15394,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44908</v>
+        <v>46274</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15394,8 +15409,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15438,7 +15458,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 36206-2026</t>
+          <t>A 37364-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15452,10 +15472,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46267</v>
+        <v>46275</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15468,7 +15488,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.2</v>
+        <v>8.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15511,7 +15531,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 36209-2026</t>
+          <t>A 31928-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15525,10 +15545,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46267</v>
+        <v>46232</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15541,7 +15561,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15584,7 +15604,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 34167-2026</t>
+          <t>A 37353-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15598,10 +15618,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15613,13 +15633,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15662,7 +15677,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 15276-2022</t>
+          <t>A 37367-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15676,10 +15691,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44659</v>
+        <v>46275</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15691,13 +15706,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15740,7 +15750,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 17707-2023</t>
+          <t>A 35404-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15754,10 +15764,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45037</v>
+        <v>45146</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15770,7 +15780,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15813,7 +15823,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 46248-2024</t>
+          <t>A 31929-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15827,10 +15837,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45581</v>
+        <v>46232</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15843,7 +15853,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15886,7 +15896,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 34162-2026</t>
+          <t>A 31930-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15900,10 +15910,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46253</v>
+        <v>46232</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15915,13 +15925,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15964,7 +15969,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 61575-2023</t>
+          <t>A 37888-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15978,10 +15983,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45261</v>
+        <v>46279</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15993,8 +15998,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16037,7 +16047,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 34834-2026</t>
+          <t>A 28131-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16051,10 +16061,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46258</v>
+        <v>46195</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16067,7 +16077,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16110,7 +16120,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 37226-2026</t>
+          <t>A 61012-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16124,10 +16134,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46274</v>
+        <v>45259</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16139,13 +16149,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16188,7 +16193,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 37355-2026</t>
+          <t>A 15467-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16202,10 +16207,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46275</v>
+        <v>45020</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16218,7 +16223,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16261,7 +16266,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 37174-2026</t>
+          <t>A 32317-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16275,10 +16280,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46274</v>
+        <v>46237</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16290,13 +16295,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16339,7 +16339,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37364-2026</t>
+          <t>A 32574-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46275</v>
+        <v>46239</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16368,8 +16368,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16412,7 +16417,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 31928-2026</t>
+          <t>A 72558-2021</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16426,10 +16431,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46232</v>
+        <v>44546</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16442,7 +16447,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16485,7 +16490,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 34664-2024</t>
+          <t>A 32558-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16499,10 +16504,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45526</v>
+        <v>46239</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16514,8 +16519,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16558,7 +16568,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 37353-2026</t>
+          <t>A 32564-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16572,10 +16582,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46275</v>
+        <v>46239</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16587,8 +16597,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16631,7 +16646,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37367-2026</t>
+          <t>A 35447-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16645,10 +16660,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46275</v>
+        <v>45146</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16661,7 +16676,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16704,7 +16719,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 31929-2026</t>
+          <t>A 79-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16714,14 +16729,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46232</v>
+        <v>45293</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16734,7 +16749,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16777,7 +16792,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31930-2026</t>
+          <t>A 38985-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16791,10 +16806,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46232</v>
+        <v>46286</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16807,7 +16822,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16850,7 +16865,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37888-2026</t>
+          <t>A 33010-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16864,10 +16879,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46279</v>
+        <v>46244</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16879,13 +16894,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16928,7 +16938,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 28131-2026</t>
+          <t>A 66977-2021</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16942,10 +16952,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46195</v>
+        <v>44522</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16958,7 +16968,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17001,7 +17011,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37083-2024</t>
+          <t>A 15276-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17015,10 +17025,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45539</v>
+        <v>44659</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17030,8 +17040,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>7.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17074,7 +17089,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 12675-2024</t>
+          <t>A 17707-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17088,10 +17103,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45384</v>
+        <v>45037</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17104,7 +17119,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17147,7 +17162,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 49971-2023</t>
+          <t>A 46248-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17161,10 +17176,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45215</v>
+        <v>45581</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17177,7 +17192,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17220,7 +17235,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 13560-2025</t>
+          <t>A 61575-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17234,10 +17249,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45736</v>
+        <v>45261</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17250,7 +17265,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17293,7 +17308,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 38278-2024</t>
+          <t>A 34664-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17303,14 +17318,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45545</v>
+        <v>45526</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17323,7 +17338,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17366,7 +17381,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 23114-2025</t>
+          <t>A 37083-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17380,10 +17395,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45791</v>
+        <v>45539</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17396,7 +17411,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17439,7 +17454,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 57284-2024</t>
+          <t>A 12675-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17453,10 +17468,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45629</v>
+        <v>45384</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17469,7 +17484,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17512,7 +17527,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 2749-2024</t>
+          <t>A 49971-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17526,10 +17541,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45314</v>
+        <v>45215</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17542,7 +17557,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17585,7 +17600,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 32317-2026</t>
+          <t>A 13560-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17599,10 +17614,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46237</v>
+        <v>45736</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17615,7 +17630,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17658,7 +17673,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 32574-2026</t>
+          <t>A 38278-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17668,14 +17683,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46239</v>
+        <v>45545</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17687,13 +17702,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17736,7 +17746,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 32558-2026</t>
+          <t>A 23114-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17750,10 +17760,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46239</v>
+        <v>45791</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17765,13 +17775,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17814,7 +17819,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 32564-2026</t>
+          <t>A 57284-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17828,10 +17833,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46239</v>
+        <v>45629</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17843,13 +17848,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 24499-2025</t>
+          <t>A 2749-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17906,10 +17906,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45798</v>
+        <v>45314</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17965,7 +17965,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 18740-2025</t>
+          <t>A 24499-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17979,10 +17979,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45763</v>
+        <v>45798</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18038,7 +18038,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 27232-2025</t>
+          <t>A 18740-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18048,14 +18048,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45812</v>
+        <v>45763</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18111,7 +18111,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 28663-2025</t>
+          <t>A 27232-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18121,14 +18121,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45819</v>
+        <v>45812</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18184,7 +18184,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 30468-2025</t>
+          <t>A 28663-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45827</v>
+        <v>45819</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18257,7 +18257,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 23781-2025</t>
+          <t>A 30468-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18271,10 +18271,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45793</v>
+        <v>45827</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18330,7 +18330,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 31624-2025</t>
+          <t>A 23781-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18344,10 +18344,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45834</v>
+        <v>45793</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18403,7 +18403,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 31623-2025</t>
+          <t>A 31624-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18420,7 +18420,7 @@
         <v>45834</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18476,7 +18476,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 50339-2023</t>
+          <t>A 31623-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18490,10 +18490,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45216</v>
+        <v>45834</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18549,7 +18549,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 37806-2022</t>
+          <t>A 50339-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18563,10 +18563,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44810</v>
+        <v>45216</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18622,7 +18622,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 37802-2022</t>
+          <t>A 37806-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18639,7 +18639,7 @@
         <v>44810</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18695,7 +18695,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 38199-2025</t>
+          <t>A 37802-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18709,10 +18709,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45882</v>
+        <v>44810</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18785,7 +18785,7 @@
         <v>46197</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>

--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE236"/>
+  <dimension ref="A1:AE233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13567-2025</t>
+          <t>A 2230-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45736</v>
+        <v>45673</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1195,42 +1195,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 2230-2025 artfynd.xlsx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 2230-2025 karta.png", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 2230-2025 georefererad karta.tif", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 2230-2025 FSC-klagomål.docx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 2230-2025 FSC-klagomål mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 2230-2025 tillsynsbegäran.docx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 2230-2025 tillsynsbegäran mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 22327-2024</t>
+          <t>A 50403-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45446</v>
+        <v>44866</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,17 +1259,22 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1284,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1293,42 +1298,42 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 50403-2022 artfynd.xlsx", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 50403-2022 karta.png", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 50403-2022 georefererad karta.tif", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 50403-2022 FSC-klagomål.docx", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 50403-2022 FSC-klagomål mail.docx", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 50403-2022 tillsynsbegäran.docx", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 50403-2022 tillsynsbegäran mail.docx", "A 50403-2022")</f>
         <v/>
       </c>
     </row>
@@ -1352,7 +1357,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1457,7 +1462,7 @@
         <v>45898</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1562,7 +1567,7 @@
         <v>45924</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1667,7 +1672,7 @@
         <v>45924</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1759,7 +1764,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 46522-2025</t>
+          <t>A 54444-2021</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1773,10 +1778,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45926</v>
+        <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1788,29 +1793,24 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -1818,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1830,151 +1830,156 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Ängshök</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 46522-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45926</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Tibast</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 51642-2021</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44462</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Vårstarr</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 51642-2021</t>
+          <t>A 9030-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1988,10 +1993,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44462</v>
+        <v>44615</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2004,7 +2009,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2013,13 +2018,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2031,7 +2036,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2044,42 +2049,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 51642-2021 artfynd.xlsx", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 9030-2022 artfynd.xlsx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 51642-2021 karta.png", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 9030-2022 karta.png", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 51642-2021 georefererad karta.tif", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 9030-2022 georefererad karta.tif", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 51642-2021 FSC-klagomål.docx", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 9030-2022 FSC-klagomål.docx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 51642-2021 FSC-klagomål mail.docx", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 9030-2022 FSC-klagomål mail.docx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 51642-2021 tillsynsbegäran.docx", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 9030-2022 tillsynsbegäran.docx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 51642-2021 tillsynsbegäran mail.docx", "A 51642-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 9030-2022 tillsynsbegäran mail.docx", "A 9030-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60983-2023</t>
+          <t>A 45164-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2093,10 +2098,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45261</v>
+        <v>45191</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2109,7 +2114,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2145,581 +2150,576 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 62852-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 13567-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Klubbsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 22327-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45446</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 33532-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45519</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 60983-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9030-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44615</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 9030-2022 artfynd.xlsx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 9030-2022 karta.png", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 9030-2022 georefererad karta.tif", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 9030-2022 FSC-klagomål.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 9030-2022 FSC-klagomål mail.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 9030-2022 tillsynsbegäran.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 9030-2022 tillsynsbegäran mail.docx", "A 9030-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 62852-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 33532-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45519</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Backsippa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 45164-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45191</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skogsduva</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 50403-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Springkorn</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 50403-2022 artfynd.xlsx", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 50403-2022 karta.png", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 50403-2022 georefererad karta.tif", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 50403-2022 FSC-klagomål.docx", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 50403-2022 FSC-klagomål mail.docx", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 50403-2022 tillsynsbegäran.docx", "A 50403-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 50403-2022 tillsynsbegäran mail.docx", "A 50403-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34869-2026</t>
+          <t>A 53521-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46255</v>
+        <v>45230</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2773,383 +2773,383 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 53521-2023 artfynd.xlsx", "A 53521-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 53521-2023 karta.png", "A 53521-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 53521-2023 georefererad karta.tif", "A 53521-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 53521-2023 FSC-klagomål.docx", "A 53521-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 53521-2023 FSC-klagomål mail.docx", "A 53521-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 53521-2023 tillsynsbegäran.docx", "A 53521-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 53521-2023 tillsynsbegäran mail.docx", "A 53521-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 34869-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
         <v>2</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Backsippa</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 34869-2026 artfynd.xlsx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 34869-2026 karta.png", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 34869-2026 georefererad karta.tif", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 34869-2026 FSC-klagomål.docx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 34869-2026 FSC-klagomål mail.docx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 34869-2026 tillsynsbegäran.docx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 34869-2026 tillsynsbegäran mail.docx", "A 34869-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 32573-2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="E24" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>6.6</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>1</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Lunglav</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32573-2026 artfynd.xlsx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32573-2026 karta.png", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32573-2026 georefererad karta.tif", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32573-2026 FSC-klagomål.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32573-2026 FSC-klagomål mail.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32573-2026 tillsynsbegäran.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32573-2026 tillsynsbegäran mail.docx", "A 32573-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 32554-2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="E25" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>3.1</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Purpurknipprot</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 53521-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45230</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Skogsduva</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 53521-2023 artfynd.xlsx", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 53521-2023 karta.png", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 53521-2023 georefererad karta.tif", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 53521-2023 FSC-klagomål.docx", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 53521-2023 FSC-klagomål mail.docx", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 53521-2023 tillsynsbegäran.docx", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 53521-2023 tillsynsbegäran mail.docx", "A 53521-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2230-2025</t>
+          <t>A 1554-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3159,14 +3159,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45673</v>
+        <v>44573</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3209,52 +3209,20 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 2230-2025 artfynd.xlsx", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 2230-2025 karta.png", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 2230-2025 georefererad karta.tif", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 2230-2025 FSC-klagomål.docx", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 2230-2025 FSC-klagomål mail.docx", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 2230-2025 tillsynsbegäran.docx", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 2230-2025 tillsynsbegäran mail.docx", "A 2230-2025")</f>
-        <v/>
-      </c>
+      <c r="V26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54444-2021</t>
+          <t>A 44652-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3268,10 +3236,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44473</v>
+        <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3283,11 +3251,16 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3299,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3308,58 +3281,26 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Ängshök</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1554-2022</t>
+          <t>A 1552-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3376,7 +3317,7 @@
         <v>44573</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3389,7 +3330,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3432,7 +3373,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44652-2022</t>
+          <t>A 72290-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3446,10 +3387,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44840</v>
+        <v>44545</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3461,13 +3402,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3510,7 +3446,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1552-2022</t>
+          <t>A 56458-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3520,14 +3456,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44573</v>
+        <v>44480</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3540,7 +3476,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3583,7 +3519,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 72290-2021</t>
+          <t>A 63449-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3593,14 +3529,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44545</v>
+        <v>45273</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3613,7 +3549,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3656,7 +3592,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 56458-2021</t>
+          <t>A 3678-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3670,10 +3606,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44480</v>
+        <v>45681</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3686,7 +3622,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3729,7 +3665,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19352-2022</t>
+          <t>A 13560-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3743,10 +3679,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44692</v>
+        <v>45736</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3759,7 +3695,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3802,7 +3738,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10950-2022</t>
+          <t>A 36401-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3816,10 +3752,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44627</v>
+        <v>45152</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3831,8 +3767,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3875,7 +3816,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50901-2024</t>
+          <t>A 34664-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3889,10 +3830,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45602</v>
+        <v>45526</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3905,7 +3846,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3948,7 +3889,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36401-2023</t>
+          <t>A 19352-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3962,10 +3903,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45152</v>
+        <v>44692</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3977,13 +3918,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4026,7 +3962,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14210-2023</t>
+          <t>A 10950-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4040,10 +3976,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45009</v>
+        <v>44627</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4056,7 +3992,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4099,7 +4035,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50886-2024</t>
+          <t>A 7337-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4113,10 +4049,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45602</v>
+        <v>44971</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4129,7 +4065,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4172,7 +4108,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38300-2023</t>
+          <t>A 34431-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4186,10 +4122,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45161</v>
+        <v>44792</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4201,8 +4137,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4245,7 +4186,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 43012-2024</t>
+          <t>A 51475-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4255,14 +4196,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45567</v>
+        <v>45221</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4275,7 +4216,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4318,7 +4259,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16304-2024</t>
+          <t>A 12253-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4332,10 +4273,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45407</v>
+        <v>45378</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4348,7 +4289,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4391,7 +4332,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 72563-2021</t>
+          <t>A 12254-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4405,10 +4346,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44546</v>
+        <v>45378</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4421,7 +4362,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4464,7 +4405,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3877-2023</t>
+          <t>A 23114-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4478,10 +4419,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44951</v>
+        <v>45791</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4494,7 +4435,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4537,7 +4478,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22328-2024</t>
+          <t>A 60977-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4551,10 +4492,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45446</v>
+        <v>45261</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4567,7 +4508,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4610,7 +4551,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64930-2023</t>
+          <t>A 2749-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4624,10 +4565,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45282</v>
+        <v>45314</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4640,7 +4581,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4683,7 +4624,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40667-2023</t>
+          <t>A 57284-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4697,10 +4638,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45170</v>
+        <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4713,7 +4654,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4756,7 +4697,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9125-2023</t>
+          <t>A 17707-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4770,10 +4711,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44980</v>
+        <v>45037</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4785,13 +4726,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4851,7 +4787,7 @@
         <v>44879</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4907,7 +4843,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15783-2022</t>
+          <t>A 60969-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4921,10 +4857,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44663</v>
+        <v>45261</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4937,7 +4873,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4980,7 +4916,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50179-2023</t>
+          <t>A 38299-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4994,10 +4930,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45208</v>
+        <v>45161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5010,7 +4946,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5053,7 +4989,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 51475-2023</t>
+          <t>A 58800-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5063,14 +4999,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45221</v>
+        <v>44903</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5083,7 +5019,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5126,7 +5062,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38299-2023</t>
+          <t>A 6785-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5140,10 +5076,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45161</v>
+        <v>45342</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5155,8 +5091,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5199,7 +5140,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7337-2023</t>
+          <t>A 24499-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5213,10 +5154,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44971</v>
+        <v>45798</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5229,7 +5170,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5272,7 +5213,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 58412-2023</t>
+          <t>A 11944-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5286,10 +5227,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45250</v>
+        <v>45376</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5302,7 +5243,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5345,7 +5286,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 63449-2023</t>
+          <t>A 54442-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5355,14 +5296,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45273</v>
+        <v>44473</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5375,7 +5316,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5418,7 +5359,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3678-2025</t>
+          <t>A 59411-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5428,14 +5369,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45681</v>
+        <v>44907</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5447,8 +5388,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5491,7 +5437,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29580-2025</t>
+          <t>A 72563-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5505,10 +5451,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45825</v>
+        <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5521,7 +5467,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5564,7 +5510,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2418-2025</t>
+          <t>A 58412-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5578,10 +5524,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45674</v>
+        <v>45250</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5594,7 +5540,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5637,7 +5583,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 65921-2021</t>
+          <t>A 59410-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5647,14 +5593,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44517</v>
+        <v>44907</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5666,8 +5612,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5710,7 +5661,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38199-2025</t>
+          <t>A 45918-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5724,10 +5675,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45882</v>
+        <v>45580</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5740,7 +5691,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5783,7 +5734,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 54442-2021</t>
+          <t>A 72558-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5797,10 +5748,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44473</v>
+        <v>44546</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5813,7 +5764,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5856,7 +5807,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27251-2025</t>
+          <t>A 43032-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5870,10 +5821,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45812</v>
+        <v>45909</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5886,7 +5837,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5929,7 +5880,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41105-2025</t>
+          <t>A 43026-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5943,10 +5894,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45898</v>
+        <v>45909</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5959,7 +5910,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6002,7 +5953,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50181-2023</t>
+          <t>A 62570-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6016,10 +5967,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45208</v>
+        <v>45269</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6032,7 +5983,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6075,7 +6026,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39965-2025</t>
+          <t>A 66977-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6089,10 +6040,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45892</v>
+        <v>44522</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6105,7 +6056,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6148,7 +6099,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28321-2025</t>
+          <t>A 18740-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6162,10 +6113,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45818</v>
+        <v>45763</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6178,7 +6129,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6221,7 +6172,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 43026-2025</t>
+          <t>A 44756-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6235,10 +6186,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45909</v>
+        <v>45917</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6251,7 +6202,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6294,7 +6245,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 43032-2025</t>
+          <t>A 44757-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6308,10 +6259,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45909</v>
+        <v>45917</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6324,7 +6275,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6367,7 +6318,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 27255-2025</t>
+          <t>A 46164-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6381,10 +6332,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45812</v>
+        <v>45924</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6397,7 +6348,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6440,7 +6391,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44757-2025</t>
+          <t>A 46144-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6454,10 +6405,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6470,7 +6421,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6513,7 +6464,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44756-2025</t>
+          <t>A 46159-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6527,10 +6478,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6543,7 +6494,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6586,7 +6537,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20357-2026</t>
+          <t>A 46521-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6600,10 +6551,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46139</v>
+        <v>45926</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6615,8 +6566,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6659,7 +6615,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31010-2022</t>
+          <t>A 65921-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6673,10 +6629,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44768</v>
+        <v>44517</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6689,7 +6645,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6732,7 +6688,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 1293-2023</t>
+          <t>A 14210-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6746,10 +6702,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44936</v>
+        <v>45009</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6762,7 +6718,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6805,7 +6761,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46164-2025</t>
+          <t>A 50179-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6819,10 +6775,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45924</v>
+        <v>45208</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6835,7 +6791,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6878,7 +6834,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46159-2025</t>
+          <t>A 27232-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6888,14 +6844,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45924</v>
+        <v>45812</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6908,7 +6864,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6951,7 +6907,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 46144-2025</t>
+          <t>A 50570-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6965,10 +6921,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45924</v>
+        <v>45217</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6981,7 +6937,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7024,7 +6980,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46521-2025</t>
+          <t>A 35404-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7038,10 +6994,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45926</v>
+        <v>45146</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7053,13 +7009,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7102,7 +7053,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41337-2023</t>
+          <t>A 39950-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7116,10 +7067,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45174</v>
+        <v>45553</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7131,8 +7082,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7175,7 +7131,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10984-2024</t>
+          <t>A 4821-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7189,10 +7145,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45370</v>
+        <v>44957</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7205,7 +7161,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7248,7 +7204,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62447-2025</t>
+          <t>A 10980-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7262,10 +7218,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46007</v>
+        <v>45370</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7277,13 +7233,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7326,7 +7277,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10980-2024</t>
+          <t>A 68095-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7340,10 +7291,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45370</v>
+        <v>44526</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7356,7 +7307,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7399,7 +7350,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21518-2026</t>
+          <t>A 43012-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7409,14 +7360,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46148</v>
+        <v>45567</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7429,7 +7380,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7472,7 +7423,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32581-2025</t>
+          <t>A 60964-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7486,10 +7437,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45838</v>
+        <v>45261</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7502,7 +7453,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7545,7 +7496,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2073-2026</t>
+          <t>A 15276-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7559,10 +7510,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46036</v>
+        <v>44659</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7574,8 +7525,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>7.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7618,7 +7574,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11944-2024</t>
+          <t>A 51335-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7632,10 +7588,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45376</v>
+        <v>45950</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7648,7 +7604,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7691,7 +7647,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3681-2025</t>
+          <t>A 49915-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7705,10 +7661,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45681</v>
+        <v>45597</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7721,7 +7677,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7781,7 +7737,7 @@
         <v>45950</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7837,7 +7793,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 51335-2025</t>
+          <t>A 1293-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7851,10 +7807,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45950</v>
+        <v>44936</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7867,7 +7823,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7910,7 +7866,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59234-2022</t>
+          <t>A 64934-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7924,10 +7880,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44904</v>
+        <v>45282</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7939,13 +7895,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7988,7 +7939,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44769-2025</t>
+          <t>A 59234-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7998,14 +7949,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45917</v>
+        <v>44904</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8017,8 +7968,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8061,7 +8017,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2715-2022</t>
+          <t>A 37631-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8075,10 +8031,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44580</v>
+        <v>45159</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8091,7 +8047,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8134,7 +8090,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44770-2025</t>
+          <t>A 11270-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8144,14 +8100,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45917</v>
+        <v>44629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8164,7 +8120,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8207,7 +8163,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 961-2024</t>
+          <t>A 41337-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8221,10 +8177,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45301</v>
+        <v>45174</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8237,7 +8193,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8280,7 +8236,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 1013-2025</t>
+          <t>A 2800-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8294,10 +8250,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45666</v>
+        <v>45677</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8310,7 +8266,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8353,7 +8309,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 55939-2025</t>
+          <t>A 55730-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8367,10 +8323,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45973</v>
+        <v>44888</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8383,7 +8339,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8426,7 +8382,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62570-2023</t>
+          <t>A 28663-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8440,10 +8396,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45269</v>
+        <v>45819</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8456,7 +8412,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8499,7 +8455,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57194-2025</t>
+          <t>A 8658-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8513,10 +8469,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45979</v>
+        <v>44613</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8529,7 +8485,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8572,7 +8528,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 1011-2025</t>
+          <t>A 15491-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8586,10 +8542,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45666</v>
+        <v>45401</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8599,6 +8555,11 @@
       <c r="G99" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -8645,7 +8606,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 50883-2024</t>
+          <t>A 44770-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8655,14 +8616,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45602</v>
+        <v>45917</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8675,7 +8636,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8718,7 +8679,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50896-2024</t>
+          <t>A 44769-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8728,14 +8689,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45602</v>
+        <v>45917</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8748,7 +8709,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8791,7 +8752,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 57942-2025</t>
+          <t>A 2418-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8805,10 +8766,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45982</v>
+        <v>45674</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8821,7 +8782,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8864,7 +8825,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58310-2025</t>
+          <t>A 2231-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8878,10 +8839,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45985</v>
+        <v>45673</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8894,7 +8855,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8937,7 +8898,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 58321-2025</t>
+          <t>A 64930-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8951,10 +8912,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45985</v>
+        <v>45282</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8967,7 +8928,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9010,7 +8971,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58756-2025</t>
+          <t>A 24866-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9024,10 +8985,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45986</v>
+        <v>45085</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9040,7 +9001,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9083,7 +9044,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 24139-2026</t>
+          <t>A 55939-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9097,10 +9058,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46168</v>
+        <v>45973</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9112,13 +9073,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9161,7 +9117,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 58761-2025</t>
+          <t>A 3087-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9175,10 +9131,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45986</v>
+        <v>44946</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9191,7 +9147,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9234,7 +9190,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59105-2025</t>
+          <t>A 58415-2021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9248,10 +9204,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45988</v>
+        <v>44488</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9264,7 +9220,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9307,7 +9263,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 3087-2023</t>
+          <t>A 57194-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9321,10 +9277,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44946</v>
+        <v>45979</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9337,7 +9293,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9380,7 +9336,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 24457-2026</t>
+          <t>A 35447-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9394,10 +9350,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46170</v>
+        <v>45146</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9409,13 +9365,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9458,7 +9409,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 25031-2026</t>
+          <t>A 57942-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9472,10 +9423,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46174</v>
+        <v>45982</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9487,13 +9438,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9536,7 +9482,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 24786-2026</t>
+          <t>A 58321-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9550,10 +9496,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46171</v>
+        <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9565,13 +9511,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9614,7 +9555,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 24900-2026</t>
+          <t>A 58756-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9628,10 +9569,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46174</v>
+        <v>45986</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9643,13 +9584,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9692,7 +9628,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 24894-2026</t>
+          <t>A 58761-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9706,10 +9642,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46174</v>
+        <v>45986</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9721,13 +9657,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9770,7 +9701,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 24888-2026</t>
+          <t>A 58310-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9784,10 +9715,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46174</v>
+        <v>45985</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9799,13 +9730,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9848,7 +9774,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 24896-2026</t>
+          <t>A 59105-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9862,10 +9788,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46174</v>
+        <v>45988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9877,13 +9803,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9926,7 +9847,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 24903-2026</t>
+          <t>A 30468-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9936,14 +9857,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46174</v>
+        <v>45827</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9955,13 +9876,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10004,7 +9920,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 4314-2024</t>
+          <t>A 23781-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10014,14 +9930,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45324</v>
+        <v>45793</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10033,13 +9949,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10082,7 +9993,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 12769-2024</t>
+          <t>A 31623-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10096,10 +10007,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45384</v>
+        <v>45834</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10112,7 +10023,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10155,7 +10066,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 62129-2025</t>
+          <t>A 31624-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10169,10 +10080,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46006</v>
+        <v>45834</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10185,7 +10096,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10228,7 +10139,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 62123-2025</t>
+          <t>A 62129-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10245,7 +10156,7 @@
         <v>46006</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10258,7 +10169,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10301,7 +10212,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 49915-2024</t>
+          <t>A 62123-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10315,10 +10226,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45597</v>
+        <v>46006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10331,7 +10242,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10391,7 +10302,7 @@
         <v>46007</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10452,7 +10363,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 25503-2026</t>
+          <t>A 11478-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10466,10 +10377,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46177</v>
+        <v>45372</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10481,13 +10392,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10547,7 +10453,7 @@
         <v>46013</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10603,7 +10509,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 41819-2023</t>
+          <t>A 4837-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10617,10 +10523,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45176</v>
+        <v>46048</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10633,7 +10539,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10676,7 +10582,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 58415-2021</t>
+          <t>A 4852-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10690,10 +10596,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44488</v>
+        <v>46048</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10706,7 +10612,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10749,7 +10655,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22307-2024</t>
+          <t>A 50181-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10763,10 +10669,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45446</v>
+        <v>45208</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10779,7 +10685,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10822,7 +10728,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 34431-2022</t>
+          <t>A 53520-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10836,10 +10742,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44792</v>
+        <v>44879</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10851,13 +10757,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10900,7 +10801,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 27126-2026</t>
+          <t>A 52655-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10910,14 +10811,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46188</v>
+        <v>45225</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10929,13 +10830,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10978,7 +10874,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27137-2026</t>
+          <t>A 22307-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10992,10 +10888,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46188</v>
+        <v>45446</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11007,13 +10903,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11056,7 +10947,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 4852-2026</t>
+          <t>A 3877-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11070,10 +10961,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46048</v>
+        <v>44951</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11086,7 +10977,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11129,7 +11020,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 4837-2026</t>
+          <t>A 61012-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11143,10 +11034,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46048</v>
+        <v>45259</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11159,7 +11050,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11202,7 +11093,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 60969-2023</t>
+          <t>A 15783-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11216,10 +11107,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45261</v>
+        <v>44663</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11232,7 +11123,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11275,7 +11166,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60964-2023</t>
+          <t>A 34521-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11289,10 +11180,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45261</v>
+        <v>45525</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11305,7 +11196,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11348,7 +11239,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 28652-2026</t>
+          <t>A 1013-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11362,10 +11253,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46198</v>
+        <v>45666</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11377,13 +11268,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11426,7 +11312,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28525-2026</t>
+          <t>A 11064-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11440,10 +11326,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46197</v>
+        <v>46079</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11455,13 +11341,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11504,7 +11385,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 11064-2026</t>
+          <t>A 38985-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11518,10 +11399,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46079</v>
+        <v>46286</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11534,7 +11415,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11577,7 +11458,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 42042-2023</t>
+          <t>A 33010-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11591,10 +11472,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45177</v>
+        <v>46244</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11607,7 +11488,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11650,7 +11531,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 15032-2026</t>
+          <t>A 50339-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11664,10 +11545,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46104</v>
+        <v>45216</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11679,13 +11560,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11728,7 +11604,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 14928-2026</t>
+          <t>A 2715-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11742,10 +11618,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46104</v>
+        <v>44580</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11757,13 +11633,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11806,7 +11677,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 64934-2023</t>
+          <t>A 37806-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11820,10 +11691,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45282</v>
+        <v>44810</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11836,7 +11707,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11879,7 +11750,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37631-2023</t>
+          <t>A 14928-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11893,10 +11764,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45159</v>
+        <v>46104</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11908,8 +11779,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11952,7 +11828,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 16110-2026</t>
+          <t>A 15032-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11966,10 +11842,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46108</v>
+        <v>46104</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11981,8 +11857,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12025,7 +11906,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 2231-2025</t>
+          <t>A 16110-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12039,10 +11920,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45673</v>
+        <v>46108</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12055,7 +11936,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12115,7 +11996,7 @@
         <v>46111</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12176,7 +12057,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 59410-2022</t>
+          <t>A 37802-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12186,14 +12067,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44907</v>
+        <v>44810</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12205,13 +12086,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12254,7 +12130,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 59411-2022</t>
+          <t>A 4314-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12264,14 +12140,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44907</v>
+        <v>45324</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12285,11 +12161,11 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12332,7 +12208,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 2800-2025</t>
+          <t>A 17699-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12346,10 +12222,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45677</v>
+        <v>46121</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12362,7 +12238,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12422,7 +12298,7 @@
         <v>46121</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12478,7 +12354,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 17699-2026</t>
+          <t>A 3681-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12492,10 +12368,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46121</v>
+        <v>45681</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12508,7 +12384,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12551,7 +12427,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 34521-2024</t>
+          <t>A 18517-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12565,10 +12441,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45525</v>
+        <v>46127</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12580,8 +12456,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12624,7 +12505,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 18517-2026</t>
+          <t>A 41819-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12638,10 +12519,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46127</v>
+        <v>45176</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12653,13 +12534,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12702,7 +12578,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 8658-2022</t>
+          <t>A 39965-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12716,10 +12592,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44613</v>
+        <v>45892</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12732,7 +12608,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12775,7 +12651,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 50570-2023</t>
+          <t>A 50883-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12789,10 +12665,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45217</v>
+        <v>45602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12805,7 +12681,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12848,7 +12724,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 60977-2023</t>
+          <t>A 50896-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12862,10 +12738,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45261</v>
+        <v>45602</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12878,7 +12754,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12921,7 +12797,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 12253-2024</t>
+          <t>A 27255-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12935,10 +12811,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45378</v>
+        <v>45812</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12951,7 +12827,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12994,7 +12870,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 12254-2024</t>
+          <t>A 10984-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13008,10 +12884,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45378</v>
+        <v>45370</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13024,7 +12900,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13067,7 +12943,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 34172-2026</t>
+          <t>A 27251-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13081,10 +12957,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46253</v>
+        <v>45812</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13096,13 +12972,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13145,7 +13016,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 52655-2023</t>
+          <t>A 15467-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13155,14 +13026,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45225</v>
+        <v>45020</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13175,7 +13046,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13218,7 +13089,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24866-2023</t>
+          <t>A 41105-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13232,10 +13103,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45085</v>
+        <v>45898</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13248,7 +13119,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13291,7 +13162,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 44753-2025</t>
+          <t>A 29580-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13305,10 +13176,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45917</v>
+        <v>45825</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13321,7 +13192,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13364,7 +13235,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 39950-2024</t>
+          <t>A 38199-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13378,10 +13249,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45553</v>
+        <v>45882</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13393,13 +13264,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13442,7 +13308,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 11270-2022</t>
+          <t>A 40667-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13456,10 +13322,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44629</v>
+        <v>45170</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13472,7 +13338,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13515,7 +13381,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31161-2026</t>
+          <t>A 42042-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13529,10 +13395,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46216</v>
+        <v>45177</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13545,7 +13411,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13588,7 +13454,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 34794-2026</t>
+          <t>A 50886-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13598,14 +13464,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46258</v>
+        <v>45602</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13617,13 +13483,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13666,7 +13527,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 34730-2026</t>
+          <t>A 50901-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13680,10 +13541,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46258</v>
+        <v>45602</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13695,13 +13556,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13744,7 +13600,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 68095-2021</t>
+          <t>A 31010-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13758,10 +13614,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44526</v>
+        <v>44768</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13774,7 +13630,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13817,7 +13673,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 34748-2026</t>
+          <t>A 20357-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13831,10 +13687,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46258</v>
+        <v>46139</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13846,13 +13702,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13895,7 +13746,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 31193-2026</t>
+          <t>A 12769-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13909,10 +13760,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46217</v>
+        <v>45384</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13925,7 +13776,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13968,7 +13819,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 58800-2022</t>
+          <t>A 50906-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13978,14 +13829,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44903</v>
+        <v>45602</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13998,7 +13849,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14041,7 +13892,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 4821-2023</t>
+          <t>A 9125-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14055,10 +13906,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44957</v>
+        <v>44980</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14070,8 +13921,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14114,7 +13970,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 31192-2026</t>
+          <t>A 16304-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14128,10 +13984,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46217</v>
+        <v>45407</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14144,7 +14000,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14187,7 +14043,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 11478-2024</t>
+          <t>A 62447-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14201,10 +14057,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45372</v>
+        <v>46007</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14216,8 +14072,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14260,7 +14121,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 51630-2021</t>
+          <t>A 28321-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14274,10 +14135,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44462</v>
+        <v>45818</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14290,7 +14151,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14333,7 +14194,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 60917-2022</t>
+          <t>A 22328-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14347,10 +14208,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44908</v>
+        <v>45446</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14363,7 +14224,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14406,7 +14267,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 36206-2026</t>
+          <t>A 79-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14416,14 +14277,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46267</v>
+        <v>45293</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14436,7 +14297,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14479,7 +14340,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 15491-2024</t>
+          <t>A 961-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14493,10 +14354,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45401</v>
+        <v>45301</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14508,13 +14369,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14557,7 +14413,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 36209-2026</t>
+          <t>A 38300-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14571,10 +14427,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46267</v>
+        <v>45161</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14587,7 +14443,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14630,7 +14486,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 45918-2024</t>
+          <t>A 21518-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14644,10 +14500,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45580</v>
+        <v>46148</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14660,7 +14516,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14703,7 +14559,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34167-2026</t>
+          <t>A 46248-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14717,10 +14573,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46253</v>
+        <v>45581</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14732,13 +14588,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14781,7 +14632,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 50906-2024</t>
+          <t>A 61575-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14795,10 +14646,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45602</v>
+        <v>45261</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14811,7 +14662,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14854,7 +14705,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 34162-2026</t>
+          <t>A 32581-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14868,10 +14719,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46253</v>
+        <v>45838</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14881,11 +14732,6 @@
       <c r="G183" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I183" t="n">
@@ -14932,7 +14778,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 6785-2024</t>
+          <t>A 49971-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14946,10 +14792,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45342</v>
+        <v>45215</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14961,13 +14807,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15010,7 +14851,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 55730-2022</t>
+          <t>A 38278-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15020,14 +14861,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44888</v>
+        <v>45545</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15040,7 +14881,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15083,7 +14924,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 53520-2022</t>
+          <t>A 12675-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15097,10 +14938,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44879</v>
+        <v>45384</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15113,7 +14954,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15156,7 +14997,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 34834-2026</t>
+          <t>A 37083-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15170,10 +15011,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46258</v>
+        <v>45539</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15186,7 +15027,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15229,7 +15070,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37226-2026</t>
+          <t>A 2073-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15243,10 +15084,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46274</v>
+        <v>46036</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15258,13 +15099,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15307,7 +15143,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 37355-2026</t>
+          <t>A 24139-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15321,10 +15157,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46275</v>
+        <v>46168</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15336,8 +15172,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15380,7 +15221,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 37174-2026</t>
+          <t>A 1011-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15394,10 +15235,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46274</v>
+        <v>45666</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15409,13 +15250,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15458,7 +15294,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 37364-2026</t>
+          <t>A 24786-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15472,10 +15308,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46275</v>
+        <v>46171</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15487,8 +15323,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>8.5</v>
+        <v>3.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15531,7 +15372,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 31928-2026</t>
+          <t>A 24457-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15545,10 +15386,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46232</v>
+        <v>46170</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15560,8 +15401,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15604,7 +15450,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 37353-2026</t>
+          <t>A 24903-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15614,14 +15460,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46275</v>
+        <v>46174</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15633,8 +15479,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15677,7 +15528,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 37367-2026</t>
+          <t>A 24894-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15691,10 +15542,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46275</v>
+        <v>46174</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15706,8 +15557,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15750,7 +15606,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 35404-2023</t>
+          <t>A 25031-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15764,10 +15620,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45146</v>
+        <v>46174</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15777,6 +15633,11 @@
       <c r="G195" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I195" t="n">
@@ -15823,7 +15684,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31929-2026</t>
+          <t>A 24888-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15837,10 +15698,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46232</v>
+        <v>46174</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15852,8 +15713,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15896,7 +15762,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 31930-2026</t>
+          <t>A 24896-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15910,10 +15776,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46232</v>
+        <v>46174</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15925,8 +15791,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15969,7 +15840,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 37888-2026</t>
+          <t>A 24900-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15983,10 +15854,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46279</v>
+        <v>46174</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16000,11 +15871,11 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16047,7 +15918,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 28131-2026</t>
+          <t>A 25503-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16061,10 +15932,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46195</v>
+        <v>46177</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16076,8 +15947,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16120,7 +15996,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 61012-2023</t>
+          <t>A 27126-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16130,14 +16006,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45259</v>
+        <v>46188</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16149,8 +16025,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16193,7 +16074,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 15467-2023</t>
+          <t>A 27137-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16207,10 +16088,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45020</v>
+        <v>46188</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16222,8 +16103,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16266,7 +16152,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 32317-2026</t>
+          <t>A 28525-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16280,10 +16166,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46237</v>
+        <v>46197</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16295,8 +16181,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16339,7 +16230,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 32574-2026</t>
+          <t>A 28652-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16353,10 +16244,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46239</v>
+        <v>46198</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16374,7 +16265,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16417,7 +16308,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 72558-2021</t>
+          <t>A 44753-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16431,10 +16322,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44546</v>
+        <v>45917</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16447,7 +16338,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16490,7 +16381,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 32558-2026</t>
+          <t>A 34172-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16504,10 +16395,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46239</v>
+        <v>46253</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16525,7 +16416,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16568,7 +16459,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 32564-2026</t>
+          <t>A 34730-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16582,10 +16473,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46239</v>
+        <v>46258</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16603,7 +16494,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16646,7 +16537,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 35447-2023</t>
+          <t>A 34748-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16660,10 +16551,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45146</v>
+        <v>46258</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16675,8 +16566,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16719,7 +16615,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 79-2024</t>
+          <t>A 34794-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16733,10 +16629,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45293</v>
+        <v>46258</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16748,8 +16644,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16792,7 +16693,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 38985-2026</t>
+          <t>A 31161-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16806,10 +16707,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46286</v>
+        <v>46216</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16822,7 +16723,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16865,7 +16766,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 33010-2026</t>
+          <t>A 31192-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16879,10 +16780,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46244</v>
+        <v>46217</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16895,7 +16796,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16938,7 +16839,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 66977-2021</t>
+          <t>A 31193-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16952,10 +16853,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44522</v>
+        <v>46217</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16968,7 +16869,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17011,7 +16912,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 15276-2022</t>
+          <t>A 60917-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17025,10 +16926,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44659</v>
+        <v>44908</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17040,13 +16941,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>7.6</v>
+        <v>2.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17089,7 +16985,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 17707-2023</t>
+          <t>A 36209-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17103,10 +16999,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45037</v>
+        <v>46267</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17119,7 +17015,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17162,7 +17058,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 46248-2024</t>
+          <t>A 36206-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17176,10 +17072,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45581</v>
+        <v>46267</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17192,7 +17088,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17235,7 +17131,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 61575-2023</t>
+          <t>A 34167-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17249,10 +17145,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45261</v>
+        <v>46253</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17264,8 +17160,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17308,7 +17209,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 34664-2024</t>
+          <t>A 34162-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17322,10 +17223,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45526</v>
+        <v>46253</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17337,8 +17238,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17381,7 +17287,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 37083-2024</t>
+          <t>A 37226-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17395,10 +17301,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45539</v>
+        <v>46274</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17410,8 +17316,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17454,7 +17365,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 12675-2024</t>
+          <t>A 37174-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17468,10 +17379,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45384</v>
+        <v>46274</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17483,8 +17394,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17527,7 +17443,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 49971-2023</t>
+          <t>A 34834-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17541,10 +17457,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45215</v>
+        <v>46258</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17557,7 +17473,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17600,7 +17516,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 13560-2025</t>
+          <t>A 31929-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17614,10 +17530,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45736</v>
+        <v>46232</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17630,7 +17546,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17673,7 +17589,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 38278-2024</t>
+          <t>A 37367-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17683,14 +17599,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45545</v>
+        <v>46275</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17703,7 +17619,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17746,7 +17662,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 23114-2025</t>
+          <t>A 28131-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17760,10 +17676,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45791</v>
+        <v>46195</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17776,7 +17692,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17819,7 +17735,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 57284-2024</t>
+          <t>A 37364-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17833,10 +17749,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45629</v>
+        <v>46275</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17849,7 +17765,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.2</v>
+        <v>8.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17892,7 +17808,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 2749-2024</t>
+          <t>A 37353-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17906,10 +17822,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45314</v>
+        <v>46275</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17922,7 +17838,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17965,7 +17881,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 24499-2025</t>
+          <t>A 37355-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17979,10 +17895,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45798</v>
+        <v>46275</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17995,7 +17911,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18038,7 +17954,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 18740-2025</t>
+          <t>A 31928-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18052,10 +17968,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45763</v>
+        <v>46232</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18068,7 +17984,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18111,7 +18027,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 27232-2025</t>
+          <t>A 31930-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18121,14 +18037,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45812</v>
+        <v>46232</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18141,7 +18057,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18184,7 +18100,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 28663-2025</t>
+          <t>A 37888-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18198,10 +18114,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45819</v>
+        <v>46279</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18213,8 +18129,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18257,7 +18178,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 30468-2025</t>
+          <t>A 32317-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18271,10 +18192,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45827</v>
+        <v>46237</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18330,7 +18251,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 23781-2025</t>
+          <t>A 32558-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18344,10 +18265,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45793</v>
+        <v>46239</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18359,8 +18280,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18403,7 +18329,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 31624-2025</t>
+          <t>A 32574-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18417,10 +18343,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45834</v>
+        <v>46239</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18432,8 +18358,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18476,7 +18407,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 31623-2025</t>
+          <t>A 32564-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18490,10 +18421,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45834</v>
+        <v>46239</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18505,8 +18436,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18546,27 +18482,27 @@
       </c>
       <c r="V232" s="2" t="inlineStr"/>
     </row>
-    <row r="233" ht="15" customHeight="1">
+    <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 50339-2023</t>
+          <t>S 1827-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45216</v>
+        <v>46197</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18578,8 +18514,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18618,230 +18559,6 @@
         <v>0</v>
       </c>
       <c r="V233" s="2" t="inlineStr"/>
-    </row>
-    <row r="234" ht="15" customHeight="1">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>A 37806-2022</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D234" s="1" t="n">
-        <v>44810</v>
-      </c>
-      <c r="E234" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I234" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J234" t="n">
-        <v>0</v>
-      </c>
-      <c r="K234" t="n">
-        <v>0</v>
-      </c>
-      <c r="L234" t="n">
-        <v>0</v>
-      </c>
-      <c r="M234" t="n">
-        <v>0</v>
-      </c>
-      <c r="N234" t="n">
-        <v>0</v>
-      </c>
-      <c r="O234" t="n">
-        <v>0</v>
-      </c>
-      <c r="P234" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
-      <c r="R234" t="n">
-        <v>0</v>
-      </c>
-      <c r="S234" t="n">
-        <v>0</v>
-      </c>
-      <c r="T234" t="n">
-        <v>0</v>
-      </c>
-      <c r="U234" t="n">
-        <v>0</v>
-      </c>
-      <c r="V234" s="2" t="inlineStr"/>
-    </row>
-    <row r="235" ht="15" customHeight="1">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>A 37802-2022</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D235" s="1" t="n">
-        <v>44810</v>
-      </c>
-      <c r="E235" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I235" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J235" t="n">
-        <v>0</v>
-      </c>
-      <c r="K235" t="n">
-        <v>0</v>
-      </c>
-      <c r="L235" t="n">
-        <v>0</v>
-      </c>
-      <c r="M235" t="n">
-        <v>0</v>
-      </c>
-      <c r="N235" t="n">
-        <v>0</v>
-      </c>
-      <c r="O235" t="n">
-        <v>0</v>
-      </c>
-      <c r="P235" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
-      <c r="R235" t="n">
-        <v>0</v>
-      </c>
-      <c r="S235" t="n">
-        <v>0</v>
-      </c>
-      <c r="T235" t="n">
-        <v>0</v>
-      </c>
-      <c r="U235" t="n">
-        <v>0</v>
-      </c>
-      <c r="V235" s="2" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>S 1827-2026</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D236" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="E236" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I236" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J236" t="n">
-        <v>0</v>
-      </c>
-      <c r="K236" t="n">
-        <v>0</v>
-      </c>
-      <c r="L236" t="n">
-        <v>0</v>
-      </c>
-      <c r="M236" t="n">
-        <v>0</v>
-      </c>
-      <c r="N236" t="n">
-        <v>0</v>
-      </c>
-      <c r="O236" t="n">
-        <v>0</v>
-      </c>
-      <c r="P236" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
-      <c r="R236" t="n">
-        <v>0</v>
-      </c>
-      <c r="S236" t="n">
-        <v>0</v>
-      </c>
-      <c r="T236" t="n">
-        <v>0</v>
-      </c>
-      <c r="U236" t="n">
-        <v>0</v>
-      </c>
-      <c r="V236" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2230-2025</t>
+          <t>A 13567-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45673</v>
+        <v>45736</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1155,17 +1155,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1195,42 +1195,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 2230-2025 artfynd.xlsx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 2230-2025 karta.png", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 2230-2025 georefererad karta.tif", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 2230-2025 FSC-klagomål.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 2230-2025 FSC-klagomål mail.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 2230-2025 tillsynsbegäran.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 2230-2025 tillsynsbegäran mail.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50403-2022</t>
+          <t>A 22327-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44866</v>
+        <v>45446</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,23 +1259,18 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -1289,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1298,42 +1293,42 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 50403-2022 artfynd.xlsx", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 50403-2022 karta.png", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 50403-2022 georefererad karta.tif", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 50403-2022 FSC-klagomål.docx", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 50403-2022 FSC-klagomål mail.docx", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 50403-2022 tillsynsbegäran.docx", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 50403-2022 tillsynsbegäran mail.docx", "A 50403-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
     </row>
@@ -1357,7 +1352,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1462,7 +1457,7 @@
         <v>45898</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1567,7 +1562,7 @@
         <v>45924</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1672,7 +1667,7 @@
         <v>45924</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1764,7 +1759,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54444-2021</t>
+          <t>A 46522-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1778,10 +1773,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44473</v>
+        <v>45926</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1793,15 +1788,20 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1818,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1830,46 +1830,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Ängshök</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46522-2025</t>
+          <t>A 60983-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45926</v>
+        <v>45261</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1898,19 +1898,14 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1944,35 +1939,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
     </row>
@@ -1996,7 +1991,7 @@
         <v>44615</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2084,7 +2079,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45164-2023</t>
+          <t>A 62852-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2098,10 +2093,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45191</v>
+        <v>46008</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2113,14 +2108,19 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2150,261 +2150,256 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 33532-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45519</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 45164-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45191</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Skogsduva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 62852-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 13567-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45736</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Klubbsprötad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22327-2024</t>
+          <t>A 50403-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2418,10 +2413,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45446</v>
+        <v>44866</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2433,17 +2428,22 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2467,49 +2467,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 50403-2022 artfynd.xlsx", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 50403-2022 karta.png", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 50403-2022 georefererad karta.tif", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 50403-2022 FSC-klagomål.docx", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 50403-2022 FSC-klagomål mail.docx", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 50403-2022 tillsynsbegäran.docx", "A 50403-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 50403-2022 tillsynsbegäran mail.docx", "A 50403-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33532-2024</t>
+          <t>A 34869-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45519</v>
+        <v>46255</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2572,7 +2572,7 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2583,38 +2583,38 @@
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 34869-2026 artfynd.xlsx", "A 34869-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 34869-2026 karta.png", "A 34869-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 34869-2026 georefererad karta.tif", "A 34869-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 34869-2026 FSC-klagomål.docx", "A 34869-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 34869-2026 FSC-klagomål mail.docx", "A 34869-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 34869-2026 tillsynsbegäran.docx", "A 34869-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 34869-2026 tillsynsbegäran mail.docx", "A 34869-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60983-2023</t>
+          <t>A 32573-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45261</v>
+        <v>46239</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2643,18 +2643,23 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2668,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2684,42 +2689,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32573-2026 artfynd.xlsx", "A 32573-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32573-2026 karta.png", "A 32573-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32573-2026 georefererad karta.tif", "A 32573-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32573-2026 FSC-klagomål.docx", "A 32573-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32573-2026 FSC-klagomål mail.docx", "A 32573-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32573-2026 tillsynsbegäran.docx", "A 32573-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32573-2026 tillsynsbegäran mail.docx", "A 32573-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 53521-2023</t>
+          <t>A 32554-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45230</v>
+        <v>46239</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2748,14 +2753,19 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2789,147 +2799,147 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 53521-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45230</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Skogsduva</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 53521-2023 artfynd.xlsx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 53521-2023 karta.png", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 53521-2023 georefererad karta.tif", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 53521-2023 FSC-klagomål.docx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 53521-2023 FSC-klagomål mail.docx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 53521-2023 tillsynsbegäran.docx", "A 53521-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 53521-2023 tillsynsbegäran mail.docx", "A 53521-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 34869-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Backsippa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 34869-2026 artfynd.xlsx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 34869-2026 karta.png", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 34869-2026 georefererad karta.tif", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 34869-2026 FSC-klagomål.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 34869-2026 FSC-klagomål mail.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 34869-2026 tillsynsbegäran.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 34869-2026 tillsynsbegäran mail.docx", "A 34869-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32573-2026</t>
+          <t>A 2230-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2943,10 +2953,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46239</v>
+        <v>45673</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2958,22 +2968,17 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2988,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3004,42 +3009,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32573-2026 artfynd.xlsx", "A 32573-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 2230-2025 artfynd.xlsx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32573-2026 karta.png", "A 32573-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 2230-2025 karta.png", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32573-2026 georefererad karta.tif", "A 32573-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 2230-2025 georefererad karta.tif", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32573-2026 FSC-klagomål.docx", "A 32573-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 2230-2025 FSC-klagomål.docx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32573-2026 FSC-klagomål mail.docx", "A 32573-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 2230-2025 FSC-klagomål mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32573-2026 tillsynsbegäran.docx", "A 32573-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 2230-2025 tillsynsbegäran.docx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32573-2026 tillsynsbegäran mail.docx", "A 32573-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 2230-2025 tillsynsbegäran mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32554-2026</t>
+          <t>A 54444-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3053,10 +3058,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46239</v>
+        <v>44473</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3068,29 +3073,24 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3110,39 +3110,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Ängshök</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
         <v/>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
         <v>44573</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44573</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44545</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44480</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 63449-2023</t>
+          <t>A 19352-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3529,14 +3529,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45273</v>
+        <v>44692</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3678-2025</t>
+          <t>A 10950-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45681</v>
+        <v>44627</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3665,7 +3665,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13560-2025</t>
+          <t>A 50901-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45736</v>
+        <v>45602</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3738,7 +3738,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 36401-2023</t>
+          <t>A 3877-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45152</v>
+        <v>44951</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3767,13 +3767,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3816,7 +3811,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34664-2024</t>
+          <t>A 14210-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,10 +3825,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45526</v>
+        <v>45009</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3846,7 +3841,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3889,7 +3884,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19352-2022</t>
+          <t>A 36401-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3903,10 +3898,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44692</v>
+        <v>45152</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3918,8 +3913,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>6.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10950-2022</t>
+          <t>A 50886-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44627</v>
+        <v>45602</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4035,7 +4035,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7337-2023</t>
+          <t>A 38300-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4049,10 +4049,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44971</v>
+        <v>45161</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4108,7 +4108,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34431-2022</t>
+          <t>A 43012-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44792</v>
+        <v>45567</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4137,13 +4137,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4186,7 +4181,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51475-2023</t>
+          <t>A 72563-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4200,10 +4195,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45221</v>
+        <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4216,7 +4211,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4259,7 +4254,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12253-2024</t>
+          <t>A 16304-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4273,10 +4268,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45378</v>
+        <v>45407</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4289,7 +4284,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4332,7 +4327,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12254-2024</t>
+          <t>A 22328-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4346,10 +4341,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45378</v>
+        <v>45446</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4362,7 +4357,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4405,7 +4400,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23114-2025</t>
+          <t>A 64930-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4419,10 +4414,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45791</v>
+        <v>45282</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4435,7 +4430,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4478,7 +4473,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60977-2023</t>
+          <t>A 38299-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4492,10 +4487,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45261</v>
+        <v>45161</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4508,7 +4503,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4551,7 +4546,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2749-2024</t>
+          <t>A 40667-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4565,10 +4560,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45314</v>
+        <v>45170</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4581,7 +4576,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4624,7 +4619,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57284-2024</t>
+          <t>A 9125-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45629</v>
+        <v>44980</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4653,8 +4648,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4697,7 +4697,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17707-2023</t>
+          <t>A 53518-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45037</v>
+        <v>44879</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53518-2022</t>
+          <t>A 15783-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44879</v>
+        <v>44663</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4843,7 +4843,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60969-2023</t>
+          <t>A 50179-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45261</v>
+        <v>45208</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38299-2023</t>
+          <t>A 51475-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45161</v>
+        <v>45221</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 58800-2022</t>
+          <t>A 7337-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4999,14 +4999,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44903</v>
+        <v>44971</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5062,7 +5062,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6785-2024</t>
+          <t>A 58412-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45342</v>
+        <v>45250</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5091,13 +5091,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5140,7 +5135,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24499-2025</t>
+          <t>A 63449-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5150,14 +5145,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45798</v>
+        <v>45273</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5170,7 +5165,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5213,7 +5208,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11944-2024</t>
+          <t>A 3678-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5227,10 +5222,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45376</v>
+        <v>45681</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5243,7 +5238,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5286,7 +5281,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54442-2021</t>
+          <t>A 29580-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5300,10 +5295,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44473</v>
+        <v>45825</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5316,7 +5311,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5359,7 +5354,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59411-2022</t>
+          <t>A 2418-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5369,14 +5364,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44907</v>
+        <v>45674</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5388,13 +5383,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5437,7 +5427,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 72563-2021</t>
+          <t>A 65921-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5451,10 +5441,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44546</v>
+        <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5467,7 +5457,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5510,7 +5500,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58412-2023</t>
+          <t>A 38199-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5524,10 +5514,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45250</v>
+        <v>45882</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5540,7 +5530,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5583,7 +5573,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59410-2022</t>
+          <t>A 54442-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5593,14 +5583,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44907</v>
+        <v>44473</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5612,13 +5602,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5661,7 +5646,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45918-2024</t>
+          <t>A 50181-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5675,10 +5660,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45580</v>
+        <v>45208</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5691,7 +5676,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5734,7 +5719,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 72558-2021</t>
+          <t>A 27251-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5748,10 +5733,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44546</v>
+        <v>45812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5764,7 +5749,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5807,7 +5792,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 43032-2025</t>
+          <t>A 43026-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5824,7 +5809,7 @@
         <v>45909</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5837,7 +5822,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5880,7 +5865,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 43026-2025</t>
+          <t>A 43032-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5897,7 +5882,7 @@
         <v>45909</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5910,7 +5895,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5953,7 +5938,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62570-2023</t>
+          <t>A 44757-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5967,10 +5952,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45269</v>
+        <v>45917</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5983,7 +5968,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6026,7 +6011,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 66977-2021</t>
+          <t>A 1293-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6040,10 +6025,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44522</v>
+        <v>44936</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6056,7 +6041,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6099,7 +6084,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18740-2025</t>
+          <t>A 44756-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6113,10 +6098,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45763</v>
+        <v>45917</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6129,7 +6114,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6172,7 +6157,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44756-2025</t>
+          <t>A 46164-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6186,10 +6171,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6202,7 +6187,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6245,7 +6230,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44757-2025</t>
+          <t>A 46159-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6259,10 +6244,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6275,7 +6260,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6318,7 +6303,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46164-2025</t>
+          <t>A 46144-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6335,7 +6320,7 @@
         <v>45924</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6348,7 +6333,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6391,7 +6376,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 46144-2025</t>
+          <t>A 41105-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6405,10 +6390,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45924</v>
+        <v>45898</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6421,7 +6406,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6464,7 +6449,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 46159-2025</t>
+          <t>A 46521-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6478,10 +6463,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6493,8 +6478,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6537,7 +6527,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 46521-2025</t>
+          <t>A 41337-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6551,10 +6541,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45926</v>
+        <v>45174</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6566,13 +6556,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6615,7 +6600,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 65921-2021</t>
+          <t>A 10984-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6629,10 +6614,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44517</v>
+        <v>45370</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6645,7 +6630,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6688,7 +6673,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14210-2023</t>
+          <t>A 39965-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6702,10 +6687,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45009</v>
+        <v>45892</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6718,7 +6703,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6761,7 +6746,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50179-2023</t>
+          <t>A 10980-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6775,10 +6760,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45208</v>
+        <v>45370</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6791,7 +6776,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6834,7 +6819,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 27232-2025</t>
+          <t>A 28321-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6844,14 +6829,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45812</v>
+        <v>45818</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6864,7 +6849,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6907,7 +6892,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50570-2023</t>
+          <t>A 11944-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6921,10 +6906,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45217</v>
+        <v>45376</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6937,7 +6922,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6980,7 +6965,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35404-2023</t>
+          <t>A 27255-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6994,10 +6979,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45146</v>
+        <v>45812</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7010,7 +6995,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7053,7 +7038,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 39950-2024</t>
+          <t>A 3681-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7067,10 +7052,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45553</v>
+        <v>45681</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7082,13 +7067,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7131,7 +7111,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4821-2023</t>
+          <t>A 51326-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7145,10 +7125,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44957</v>
+        <v>45950</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7161,7 +7141,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7204,7 +7184,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10980-2024</t>
+          <t>A 51335-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7218,10 +7198,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45370</v>
+        <v>45950</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7234,7 +7214,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7277,7 +7257,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 68095-2021</t>
+          <t>A 59234-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7291,10 +7271,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44526</v>
+        <v>44904</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7306,8 +7286,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7350,7 +7335,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43012-2024</t>
+          <t>A 20357-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7360,14 +7345,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45567</v>
+        <v>46139</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7380,7 +7365,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7423,7 +7408,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60964-2023</t>
+          <t>A 31010-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7437,10 +7422,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45261</v>
+        <v>44768</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7453,7 +7438,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7496,7 +7481,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15276-2022</t>
+          <t>A 2715-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7510,10 +7495,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44659</v>
+        <v>44580</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7525,13 +7510,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7574,7 +7554,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 51335-2025</t>
+          <t>A 961-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7588,10 +7568,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45950</v>
+        <v>45301</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7647,7 +7627,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49915-2024</t>
+          <t>A 1013-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7661,10 +7641,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45597</v>
+        <v>45666</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7677,7 +7657,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7720,7 +7700,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 51326-2025</t>
+          <t>A 62570-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7734,10 +7714,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45950</v>
+        <v>45269</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7750,7 +7730,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7793,7 +7773,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 1293-2023</t>
+          <t>A 44769-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7803,14 +7783,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44936</v>
+        <v>45917</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7823,7 +7803,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7866,7 +7846,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 64934-2023</t>
+          <t>A 44770-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7876,14 +7856,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45282</v>
+        <v>45917</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7896,7 +7876,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7939,7 +7919,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59234-2022</t>
+          <t>A 55939-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7953,10 +7933,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44904</v>
+        <v>45973</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7968,13 +7948,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8017,7 +7992,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 37631-2023</t>
+          <t>A 50883-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8031,10 +8006,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45159</v>
+        <v>45602</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8047,7 +8022,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8090,7 +8065,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11270-2022</t>
+          <t>A 50896-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8104,10 +8079,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44629</v>
+        <v>45602</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8120,7 +8095,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8163,7 +8138,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41337-2023</t>
+          <t>A 62447-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8177,10 +8152,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45174</v>
+        <v>46007</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8192,8 +8167,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8236,7 +8216,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 2800-2025</t>
+          <t>A 57194-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8250,10 +8230,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45677</v>
+        <v>45979</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8266,7 +8246,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8309,7 +8289,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 55730-2022</t>
+          <t>A 3087-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8323,10 +8303,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44888</v>
+        <v>44946</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8339,7 +8319,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8382,7 +8362,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28663-2025</t>
+          <t>A 57942-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8396,10 +8376,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45819</v>
+        <v>45982</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8455,7 +8435,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8658-2022</t>
+          <t>A 58310-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8469,10 +8449,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44613</v>
+        <v>45985</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8528,7 +8508,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 15491-2024</t>
+          <t>A 58321-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8542,10 +8522,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45401</v>
+        <v>45985</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8557,13 +8537,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8606,7 +8581,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 44770-2025</t>
+          <t>A 58756-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8616,14 +8591,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45917</v>
+        <v>45986</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8636,7 +8611,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8679,7 +8654,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 44769-2025</t>
+          <t>A 58761-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8689,14 +8664,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45917</v>
+        <v>45986</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8709,7 +8684,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8752,7 +8727,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 2418-2025</t>
+          <t>A 59105-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8766,10 +8741,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45674</v>
+        <v>45988</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8782,7 +8757,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8825,7 +8800,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 2231-2025</t>
+          <t>A 21518-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8839,10 +8814,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45673</v>
+        <v>46148</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8855,7 +8830,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8898,7 +8873,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 64930-2023</t>
+          <t>A 4314-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8908,14 +8883,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45282</v>
+        <v>45324</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8927,8 +8902,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8971,7 +8951,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 24866-2023</t>
+          <t>A 12769-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8985,10 +8965,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45085</v>
+        <v>45384</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9044,7 +9024,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 55939-2025</t>
+          <t>A 32581-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9058,10 +9038,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45973</v>
+        <v>45838</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9074,7 +9054,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9117,7 +9097,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 3087-2023</t>
+          <t>A 2073-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9131,10 +9111,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44946</v>
+        <v>46036</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9147,7 +9127,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9190,7 +9170,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 58415-2021</t>
+          <t>A 49915-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9204,10 +9184,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44488</v>
+        <v>45597</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9220,7 +9200,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9263,7 +9243,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57194-2025</t>
+          <t>A 62129-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9277,10 +9257,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45979</v>
+        <v>46006</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9293,7 +9273,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9336,7 +9316,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 35447-2023</t>
+          <t>A 62123-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9350,10 +9330,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45146</v>
+        <v>46006</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9366,7 +9346,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9409,7 +9389,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 57942-2025</t>
+          <t>A 62391-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9423,10 +9403,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45982</v>
+        <v>46007</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9438,8 +9418,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9482,7 +9467,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 58321-2025</t>
+          <t>A 41819-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9496,10 +9481,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45985</v>
+        <v>45176</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9512,7 +9497,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9555,7 +9540,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 58756-2025</t>
+          <t>A 58415-2021</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9569,10 +9554,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45986</v>
+        <v>44488</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9585,7 +9570,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9628,7 +9613,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 58761-2025</t>
+          <t>A 22307-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9642,10 +9627,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45986</v>
+        <v>45446</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9658,7 +9643,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9701,7 +9686,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 58310-2025</t>
+          <t>A 63445-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9715,10 +9700,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45985</v>
+        <v>46013</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9774,7 +9759,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59105-2025</t>
+          <t>A 34431-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9788,10 +9773,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45988</v>
+        <v>44792</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9803,8 +9788,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9847,7 +9837,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 30468-2025</t>
+          <t>A 60969-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9861,10 +9851,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45827</v>
+        <v>45261</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9877,7 +9867,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9920,7 +9910,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23781-2025</t>
+          <t>A 60964-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9934,10 +9924,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45793</v>
+        <v>45261</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9950,7 +9940,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9993,7 +9983,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 31623-2025</t>
+          <t>A 4852-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10007,10 +9997,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45834</v>
+        <v>46048</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10023,7 +10013,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10066,7 +10056,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 31624-2025</t>
+          <t>A 4837-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10080,10 +10070,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45834</v>
+        <v>46048</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10096,7 +10086,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10139,7 +10129,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 62129-2025</t>
+          <t>A 1011-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10153,10 +10143,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46006</v>
+        <v>45666</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10169,7 +10159,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10212,7 +10202,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 62123-2025</t>
+          <t>A 24139-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10226,10 +10216,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46006</v>
+        <v>46168</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10241,8 +10231,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10285,7 +10280,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 62391-2025</t>
+          <t>A 24457-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10299,10 +10294,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46007</v>
+        <v>46170</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10316,11 +10311,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>8.300000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10363,7 +10358,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 11478-2024</t>
+          <t>A 42042-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10377,10 +10372,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45372</v>
+        <v>45177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10393,7 +10388,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10436,7 +10431,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 63445-2025</t>
+          <t>A 25031-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10450,10 +10445,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46013</v>
+        <v>46174</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10465,8 +10460,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10509,7 +10509,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 4837-2026</t>
+          <t>A 24786-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10523,10 +10523,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46048</v>
+        <v>46171</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10538,8 +10538,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10582,7 +10587,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 4852-2026</t>
+          <t>A 24900-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10596,10 +10601,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46048</v>
+        <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10611,8 +10616,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10655,7 +10665,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 50181-2023</t>
+          <t>A 24894-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10669,10 +10679,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45208</v>
+        <v>46174</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10684,8 +10694,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10728,7 +10743,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 53520-2022</t>
+          <t>A 11064-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10742,10 +10757,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44879</v>
+        <v>46079</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10758,7 +10773,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10801,7 +10816,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 52655-2023</t>
+          <t>A 24888-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10811,14 +10826,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45225</v>
+        <v>46174</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10830,8 +10845,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10874,7 +10894,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22307-2024</t>
+          <t>A 24896-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10888,10 +10908,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45446</v>
+        <v>46174</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10903,8 +10923,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10947,7 +10972,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3877-2023</t>
+          <t>A 24903-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10957,14 +10982,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44951</v>
+        <v>46174</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10974,6 +10999,11 @@
       <c r="G132" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -11020,7 +11050,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 61012-2023</t>
+          <t>A 64934-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11034,10 +11064,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45259</v>
+        <v>45282</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11050,7 +11080,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11093,7 +11123,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 15783-2022</t>
+          <t>A 37631-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11107,10 +11137,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44663</v>
+        <v>45159</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11123,7 +11153,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11166,7 +11196,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 34521-2024</t>
+          <t>A 2231-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11180,10 +11210,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45525</v>
+        <v>45673</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11196,7 +11226,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11239,7 +11269,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1013-2025</t>
+          <t>A 25503-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11253,10 +11283,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45666</v>
+        <v>46177</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11268,8 +11298,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11312,7 +11347,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 11064-2026</t>
+          <t>A 15032-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11326,10 +11361,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46079</v>
+        <v>46104</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11341,8 +11376,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11385,7 +11425,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 38985-2026</t>
+          <t>A 14928-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11399,10 +11439,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46286</v>
+        <v>46104</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11414,8 +11454,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11458,7 +11503,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 33010-2026</t>
+          <t>A 27126-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11468,14 +11513,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46244</v>
+        <v>46188</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11487,8 +11532,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11531,7 +11581,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 50339-2023</t>
+          <t>A 27137-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11545,10 +11595,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45216</v>
+        <v>46188</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11560,8 +11610,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11604,7 +11659,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 2715-2022</t>
+          <t>A 59410-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11614,14 +11669,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44580</v>
+        <v>44907</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11633,8 +11688,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11677,7 +11737,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 37806-2022</t>
+          <t>A 59411-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11687,14 +11747,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44810</v>
+        <v>44907</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11706,8 +11766,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11750,7 +11815,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 14928-2026</t>
+          <t>A 2800-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11764,10 +11829,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46104</v>
+        <v>45677</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11779,13 +11844,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11828,7 +11888,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 15032-2026</t>
+          <t>A 16110-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11842,10 +11902,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11857,13 +11917,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11906,7 +11961,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 16110-2026</t>
+          <t>A 16173-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11920,10 +11975,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11933,6 +11988,11 @@
       <c r="G145" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -11979,7 +12039,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 16173-2026</t>
+          <t>A 34521-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11993,10 +12053,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46111</v>
+        <v>45525</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12008,13 +12068,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12057,7 +12112,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 37802-2022</t>
+          <t>A 8658-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12071,10 +12126,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44810</v>
+        <v>44613</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12087,7 +12142,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12130,7 +12185,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4314-2024</t>
+          <t>A 17700-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12140,14 +12195,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45324</v>
+        <v>46121</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12159,13 +12214,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12208,7 +12258,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 17699-2026</t>
+          <t>A 50570-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12222,10 +12272,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46121</v>
+        <v>45217</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12238,7 +12288,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12281,7 +12331,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 17700-2026</t>
+          <t>A 17699-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12298,7 +12348,7 @@
         <v>46121</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12354,7 +12404,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3681-2025</t>
+          <t>A 18517-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12368,10 +12418,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45681</v>
+        <v>46127</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12383,8 +12433,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12427,7 +12482,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 18517-2026</t>
+          <t>A 60977-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12441,10 +12496,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46127</v>
+        <v>45261</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12456,13 +12511,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12505,7 +12555,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 41819-2023</t>
+          <t>A 12253-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12519,10 +12569,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45176</v>
+        <v>45378</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12535,7 +12585,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12578,7 +12628,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 39965-2025</t>
+          <t>A 12254-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12592,10 +12642,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45892</v>
+        <v>45378</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12608,7 +12658,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12651,7 +12701,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 50883-2024</t>
+          <t>A 28652-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12665,10 +12715,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45602</v>
+        <v>46198</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12680,8 +12730,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12724,7 +12779,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 50896-2024</t>
+          <t>A 28525-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12738,10 +12793,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45602</v>
+        <v>46197</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12753,8 +12808,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12797,7 +12857,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 27255-2025</t>
+          <t>A 52655-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12807,14 +12867,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45812</v>
+        <v>45225</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12827,7 +12887,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12870,7 +12930,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 10984-2024</t>
+          <t>A 24866-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12884,10 +12944,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45370</v>
+        <v>45085</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12900,7 +12960,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12943,7 +13003,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27251-2025</t>
+          <t>A 39950-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12957,10 +13017,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45812</v>
+        <v>45553</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12972,8 +13032,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13016,7 +13081,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 15467-2023</t>
+          <t>A 11270-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13030,10 +13095,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45020</v>
+        <v>44629</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13046,7 +13111,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13089,7 +13154,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 41105-2025</t>
+          <t>A 68095-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13103,10 +13168,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45898</v>
+        <v>44526</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13119,7 +13184,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13162,7 +13227,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 29580-2025</t>
+          <t>A 58800-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13172,14 +13237,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45825</v>
+        <v>44903</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13192,7 +13257,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13235,7 +13300,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 38199-2025</t>
+          <t>A 4821-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13249,10 +13314,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45882</v>
+        <v>44957</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13265,7 +13330,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13308,7 +13373,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 40667-2023</t>
+          <t>A 11478-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13322,10 +13387,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45170</v>
+        <v>45372</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13338,7 +13403,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13381,7 +13446,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 42042-2023</t>
+          <t>A 34172-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13395,10 +13460,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45177</v>
+        <v>46253</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13408,6 +13473,11 @@
       <c r="G165" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I165" t="n">
@@ -13454,7 +13524,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 50886-2024</t>
+          <t>A 15491-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13468,10 +13538,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45602</v>
+        <v>45401</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13483,8 +13553,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13527,7 +13602,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 50901-2024</t>
+          <t>A 45918-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13541,10 +13616,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45602</v>
+        <v>45580</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13557,7 +13632,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13600,7 +13675,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 31010-2022</t>
+          <t>A 44753-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13614,10 +13689,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44768</v>
+        <v>45917</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13630,7 +13705,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13673,7 +13748,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 20357-2026</t>
+          <t>A 31161-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13687,10 +13762,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46139</v>
+        <v>46216</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13703,7 +13778,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13746,7 +13821,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 12769-2024</t>
+          <t>A 50906-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13760,10 +13835,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45384</v>
+        <v>45602</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13776,7 +13851,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13819,7 +13894,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 50906-2024</t>
+          <t>A 34794-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13829,14 +13904,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45602</v>
+        <v>46258</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13848,8 +13923,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13892,7 +13972,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 9125-2023</t>
+          <t>A 34730-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13906,10 +13986,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44980</v>
+        <v>46258</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13923,11 +14003,11 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13970,7 +14050,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 16304-2024</t>
+          <t>A 6785-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13984,10 +14064,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45407</v>
+        <v>45342</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13999,8 +14079,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14043,7 +14128,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 62447-2025</t>
+          <t>A 55730-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14057,10 +14142,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46007</v>
+        <v>44888</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14072,13 +14157,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14121,7 +14201,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28321-2025</t>
+          <t>A 34748-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14135,10 +14215,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45818</v>
+        <v>46258</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14150,8 +14230,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14194,7 +14279,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 22328-2024</t>
+          <t>A 31193-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14208,10 +14293,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45446</v>
+        <v>46217</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14224,7 +14309,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14267,7 +14352,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 79-2024</t>
+          <t>A 53520-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14277,14 +14362,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45293</v>
+        <v>44879</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14297,7 +14382,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14340,7 +14425,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 961-2024</t>
+          <t>A 31192-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14354,10 +14439,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45301</v>
+        <v>46217</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14370,7 +14455,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14413,7 +14498,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 38300-2023</t>
+          <t>A 35404-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14427,10 +14512,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45161</v>
+        <v>45146</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14443,7 +14528,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14486,7 +14571,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 21518-2026</t>
+          <t>A 60917-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14500,10 +14585,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46148</v>
+        <v>44908</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14516,7 +14601,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14559,7 +14644,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 46248-2024</t>
+          <t>A 36206-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14573,10 +14658,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45581</v>
+        <v>46267</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14589,7 +14674,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14632,7 +14717,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 61575-2023</t>
+          <t>A 36209-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14646,10 +14731,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45261</v>
+        <v>46267</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14662,7 +14747,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14705,7 +14790,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 32581-2025</t>
+          <t>A 61012-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14719,10 +14804,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45838</v>
+        <v>45259</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14735,7 +14820,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14778,7 +14863,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 49971-2023</t>
+          <t>A 34167-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14792,10 +14877,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45215</v>
+        <v>46253</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14807,8 +14892,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14851,7 +14941,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 38278-2024</t>
+          <t>A 34162-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14861,14 +14951,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45545</v>
+        <v>46253</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14880,8 +14970,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14924,7 +15019,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 12675-2024</t>
+          <t>A 15467-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14938,10 +15033,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45384</v>
+        <v>45020</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14954,7 +15049,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14997,7 +15092,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37083-2024</t>
+          <t>A 72558-2021</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15011,10 +15106,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45539</v>
+        <v>44546</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15027,7 +15122,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15070,7 +15165,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 2073-2026</t>
+          <t>A 35447-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15084,10 +15179,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46036</v>
+        <v>45146</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15100,7 +15195,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15143,7 +15238,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 24139-2026</t>
+          <t>A 79-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15153,14 +15248,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46168</v>
+        <v>45293</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15170,11 +15265,6 @@
       <c r="G189" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I189" t="n">
@@ -15221,7 +15311,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 1011-2025</t>
+          <t>A 34834-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15235,10 +15325,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45666</v>
+        <v>46258</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15251,7 +15341,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15294,7 +15384,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 24786-2026</t>
+          <t>A 37226-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15308,10 +15398,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46171</v>
+        <v>46274</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15325,11 +15415,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15372,7 +15462,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 24457-2026</t>
+          <t>A 37355-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15386,10 +15476,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46170</v>
+        <v>46275</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15401,13 +15491,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15450,7 +15535,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 24903-2026</t>
+          <t>A 37174-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15460,14 +15545,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46174</v>
+        <v>46274</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15481,11 +15566,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15528,7 +15613,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24894-2026</t>
+          <t>A 37364-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15542,10 +15627,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46174</v>
+        <v>46275</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15557,13 +15642,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15606,7 +15686,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 25031-2026</t>
+          <t>A 31928-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15620,10 +15700,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46174</v>
+        <v>46232</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15635,13 +15715,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15684,7 +15759,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 24888-2026</t>
+          <t>A 37353-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15698,10 +15773,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46174</v>
+        <v>46275</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15713,13 +15788,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15762,7 +15832,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 24896-2026</t>
+          <t>A 37367-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15776,10 +15846,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46174</v>
+        <v>46275</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15791,13 +15861,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>0.3</v>
+        <v>5.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15840,7 +15905,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 24900-2026</t>
+          <t>A 31929-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15854,10 +15919,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46174</v>
+        <v>46232</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15867,11 +15932,6 @@
       <c r="G198" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I198" t="n">
@@ -15918,7 +15978,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 25503-2026</t>
+          <t>A 31930-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15932,10 +15992,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46177</v>
+        <v>46232</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15947,13 +16007,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15996,7 +16051,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 27126-2026</t>
+          <t>A 37888-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16006,14 +16061,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46188</v>
+        <v>46279</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16027,11 +16082,11 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16074,7 +16129,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 27137-2026</t>
+          <t>A 28131-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16088,10 +16143,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16103,13 +16158,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16152,7 +16202,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 28525-2026</t>
+          <t>A 66977-2021</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16166,10 +16216,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46197</v>
+        <v>44522</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16181,13 +16231,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16230,7 +16275,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28652-2026</t>
+          <t>A 32317-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16244,10 +16289,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46198</v>
+        <v>46237</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16259,13 +16304,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16308,7 +16348,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 44753-2025</t>
+          <t>A 32574-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16322,10 +16362,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45917</v>
+        <v>46239</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16337,8 +16377,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16381,7 +16426,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 34172-2026</t>
+          <t>A 32558-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16395,10 +16440,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46253</v>
+        <v>46239</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16416,7 +16461,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16459,7 +16504,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 34730-2026</t>
+          <t>A 15276-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16473,10 +16518,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46258</v>
+        <v>44659</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16490,11 +16535,11 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16537,7 +16582,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 34748-2026</t>
+          <t>A 17707-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16551,10 +16596,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46258</v>
+        <v>45037</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16566,13 +16611,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16615,7 +16655,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 34794-2026</t>
+          <t>A 32564-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16625,14 +16665,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46258</v>
+        <v>46239</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16650,7 +16690,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16693,7 +16733,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31161-2026</t>
+          <t>A 46248-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16707,10 +16747,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46216</v>
+        <v>45581</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16723,7 +16763,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16766,7 +16806,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 31192-2026</t>
+          <t>A 61575-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16780,10 +16820,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46217</v>
+        <v>45261</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16796,7 +16836,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16839,7 +16879,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 31193-2026</t>
+          <t>A 34664-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16853,10 +16893,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46217</v>
+        <v>45526</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16869,7 +16909,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16912,7 +16952,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 60917-2022</t>
+          <t>A 38985-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16926,10 +16966,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44908</v>
+        <v>46286</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16942,7 +16982,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16985,7 +17025,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 36209-2026</t>
+          <t>A 37083-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16999,10 +17039,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46267</v>
+        <v>45539</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17015,7 +17055,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17058,7 +17098,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 36206-2026</t>
+          <t>A 12675-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17072,10 +17112,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46267</v>
+        <v>45384</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17088,7 +17128,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17131,7 +17171,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 34167-2026</t>
+          <t>A 49971-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17145,10 +17185,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46253</v>
+        <v>45215</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17160,13 +17200,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17209,7 +17244,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 34162-2026</t>
+          <t>A 13560-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17223,10 +17258,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46253</v>
+        <v>45736</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17238,13 +17273,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17287,7 +17317,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 37226-2026</t>
+          <t>A 38278-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17297,14 +17327,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46274</v>
+        <v>45545</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17316,13 +17346,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17365,7 +17390,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 37174-2026</t>
+          <t>A 23114-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17379,10 +17404,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46274</v>
+        <v>45791</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17394,13 +17419,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17443,7 +17463,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 34834-2026</t>
+          <t>A 33010-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17457,10 +17477,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17473,7 +17493,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17516,7 +17536,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 31929-2026</t>
+          <t>A 57284-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17530,10 +17550,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46232</v>
+        <v>45629</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17546,7 +17566,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17589,7 +17609,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 37367-2026</t>
+          <t>A 2749-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17603,10 +17623,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46275</v>
+        <v>45314</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17619,7 +17639,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17662,7 +17682,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 28131-2026</t>
+          <t>A 24499-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17676,10 +17696,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46195</v>
+        <v>45798</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17692,7 +17712,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17735,7 +17755,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 37364-2026</t>
+          <t>A 18740-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17749,10 +17769,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46275</v>
+        <v>45763</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17765,7 +17785,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17808,7 +17828,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 37353-2026</t>
+          <t>A 27232-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17818,14 +17838,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46275</v>
+        <v>45812</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17838,7 +17858,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17881,7 +17901,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 37355-2026</t>
+          <t>A 28663-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17895,10 +17915,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46275</v>
+        <v>45819</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17911,7 +17931,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17954,7 +17974,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 31928-2026</t>
+          <t>A 30468-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17968,10 +17988,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46232</v>
+        <v>45827</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17984,7 +18004,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18027,7 +18047,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 31930-2026</t>
+          <t>A 23781-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18041,10 +18061,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46232</v>
+        <v>45793</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18057,7 +18077,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18100,7 +18120,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 37888-2026</t>
+          <t>A 31624-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18114,10 +18134,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46279</v>
+        <v>45834</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18129,13 +18149,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18178,7 +18193,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 32317-2026</t>
+          <t>A 31623-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18192,10 +18207,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46237</v>
+        <v>45834</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18208,7 +18223,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18251,7 +18266,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 32558-2026</t>
+          <t>A 50339-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18265,10 +18280,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46239</v>
+        <v>45216</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18280,13 +18295,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18329,7 +18339,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 32574-2026</t>
+          <t>A 37806-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18343,10 +18353,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46239</v>
+        <v>44810</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18358,13 +18368,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18407,7 +18412,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 32564-2026</t>
+          <t>A 37802-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18421,10 +18426,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46239</v>
+        <v>44810</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18436,13 +18441,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18502,7 +18502,7 @@
         <v>46197</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>

--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>45705</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>45898</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>45924</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>45924</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45926</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>44615</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>46255</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>45191</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>46239</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>46239</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>46008</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45736</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45446</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>45519</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>45261</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>45230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>45673</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>44573</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44573</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44545</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44480</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>44692</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>44627</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>44792</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45378</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45378</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>45221</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>44879</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>45037</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>44473</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>46013</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>44546</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>44546</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45798</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>44522</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>46048</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>46048</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44517</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45909</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>45909</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>45763</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45208</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>45217</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>45917</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>45917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>45553</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45924</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>45924</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>44957</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>45926</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>45370</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>45567</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>45261</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44659</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>46079</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44936</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>45282</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44904</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44888</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45950</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>46104</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>45401</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45950</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>46104</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>45812</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>46108</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>46111</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>45282</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>45085</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>46121</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>46121</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>45917</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44946</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>46127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44488</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45146</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45973</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>45979</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>45982</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45892</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45985</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>45812</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>45986</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>45986</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>45985</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45273</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>45812</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>45681</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>45988</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>45898</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>45152</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45825</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>44971</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>44768</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>46139</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>46006</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>46006</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45819</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>46007</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45818</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45261</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45827</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45261</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>46148</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45793</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>45834</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>45161</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>45838</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>45834</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>46036</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44903</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>45342</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>45376</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>44907</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45216</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45250</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>46168</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44907</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44810</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>45666</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45580</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46171</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46170</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45269</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46174</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44810</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>46174</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>46174</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>46174</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>46174</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>46177</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45009</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>46188</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>46188</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45146</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44526</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>46197</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45597</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>46198</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45882</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45159</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>44629</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45174</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45677</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44613</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45674</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45673</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>46253</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>46258</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>46258</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>46258</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>46216</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>46217</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>46217</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44908</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>46267</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>46267</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>46253</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>46253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>46274</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45372</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>46274</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>46258</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>46232</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>46195</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>46275</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>46275</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>46232</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>46232</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>46279</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>46237</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45208</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44879</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>46239</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>46239</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>46239</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45225</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>45446</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44951</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45259</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>44663</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45525</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45666</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>46286</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>46244</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>46275</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>46290</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>44580</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>46290</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>46275</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45324</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45681</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45176</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45602</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45602</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45370</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45020</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45170</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45177</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45384</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45602</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44980</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45407</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45446</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45293</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45301</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45161</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45581</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45261</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45215</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>45545</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45384</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45539</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45736</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45526</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45791</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45314</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45629</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46197</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>

--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>45705</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>45898</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>45924</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>45924</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45926</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>44615</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>46255</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>45191</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>46239</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>46239</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>46008</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45736</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45446</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>45519</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>45261</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>45230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>45673</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>44573</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44573</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44545</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44480</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>44692</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>44627</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>44792</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45378</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45378</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>45221</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>44879</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>45037</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>44473</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>46013</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>44546</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>44546</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45798</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>44522</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>46048</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>46048</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44517</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45909</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>45909</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>45763</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45208</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>45217</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>45917</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>45917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>45553</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45924</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>45924</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>44957</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>45926</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>45370</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>45567</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>45261</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44659</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>46079</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44936</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>45282</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44904</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44888</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45950</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>46104</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>45401</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45950</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>46104</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>45812</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>46108</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>46111</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>45282</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>45085</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>46121</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>46121</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>45917</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44946</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>46127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44488</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45146</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45973</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>45979</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>45982</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45892</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45985</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>45812</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>45986</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>45986</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>45985</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45273</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>45812</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>45681</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>45988</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>45898</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>45152</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45825</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>44971</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>44768</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>46139</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>46006</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>46006</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45819</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>46007</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45818</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45261</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45827</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45261</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>46148</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45793</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>45834</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>45161</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>45838</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>45834</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>46036</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44903</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>45342</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>45376</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>44907</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45216</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45250</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>46168</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44907</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44810</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>45666</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45580</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>46171</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46170</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45269</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46174</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44810</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>46174</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>46174</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>46174</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>46174</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>46177</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45009</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>46188</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>46188</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45146</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44526</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>46197</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45597</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>46198</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45882</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45159</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>44629</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45174</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45677</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>44613</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45674</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45673</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>46253</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>46258</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>46258</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>46258</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>46216</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>46217</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>46217</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44908</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>46267</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>46267</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>46253</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>46253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>46274</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45372</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>46274</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>46258</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>46232</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>46195</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>46275</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>46275</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>46232</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>46232</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>46279</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>46237</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45208</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44879</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>46239</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>46239</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>46239</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45225</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>45446</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44951</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45259</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>44663</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45525</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45666</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>46286</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>46244</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>46275</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>46290</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>44580</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>46290</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>46275</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45324</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45681</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45176</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45602</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45602</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45370</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45020</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45170</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45177</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45384</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45602</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44980</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45407</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45446</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45293</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45301</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45161</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45581</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45261</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45215</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>45545</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45384</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45539</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45736</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45526</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45791</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45314</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45629</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46197</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>

--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 7564-2025</t>
+          <t>A 22327-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45705</v>
+        <v>45446</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1188,49 +1188,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 7564-2025 artfynd.xlsx", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 7564-2025 karta.png", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 7564-2025 georefererad karta.tif", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 7564-2025 FSC-klagomål.docx", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 7564-2025 FSC-klagomål mail.docx", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 7564-2025 tillsynsbegäran.docx", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 7564-2025 tillsynsbegäran mail.docx", "A 7564-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 41274-2025</t>
+          <t>A 45164-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45898</v>
+        <v>45191</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1272,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1284,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1300,42 +1300,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 41274-2025 artfynd.xlsx", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 41274-2025 karta.png", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 41274-2025 georefererad karta.tif", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 41274-2025 FSC-klagomål.docx", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 41274-2025 FSC-klagomål mail.docx", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 41274-2025 tillsynsbegäran.docx", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 41274-2025 tillsynsbegäran mail.docx", "A 41274-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 54444-2021</t>
+          <t>A 13567-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44473</v>
+        <v>45736</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1392,7 +1392,7 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1401,46 +1401,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Ängshök</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 46156-2025</t>
+          <t>A 53521-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45924</v>
+        <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1470,13 +1470,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1510,42 +1510,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46156-2025 artfynd.xlsx", "A 46156-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 53521-2023 artfynd.xlsx", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46156-2025 karta.png", "A 46156-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 53521-2023 karta.png", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46156-2025 georefererad karta.tif", "A 46156-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 53521-2023 georefererad karta.tif", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46156-2025 FSC-klagomål.docx", "A 46156-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 53521-2023 FSC-klagomål.docx", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46156-2025 FSC-klagomål mail.docx", "A 46156-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 53521-2023 FSC-klagomål mail.docx", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46156-2025 tillsynsbegäran.docx", "A 46156-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 53521-2023 tillsynsbegäran.docx", "A 53521-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46156-2025 tillsynsbegäran mail.docx", "A 46156-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 53521-2023 tillsynsbegäran mail.docx", "A 53521-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 46123-2025</t>
+          <t>A 2230-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45924</v>
+        <v>45673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1599,10 +1599,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1615,46 +1615,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46123-2025 artfynd.xlsx", "A 46123-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 2230-2025 artfynd.xlsx", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46123-2025 karta.png", "A 46123-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 2230-2025 karta.png", "A 2230-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46123-2025 georefererad karta.tif", "A 46123-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 2230-2025 georefererad karta.tif", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/knärot/A 46123-2025 karta knärot.png", "A 46123-2025")</f>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 2230-2025 FSC-klagomål.docx", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46123-2025 FSC-klagomål.docx", "A 46123-2025")</f>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 2230-2025 FSC-klagomål mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46123-2025 FSC-klagomål mail.docx", "A 46123-2025")</f>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 2230-2025 tillsynsbegäran.docx", "A 2230-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46123-2025 tillsynsbegäran.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46123-2025 tillsynsbegäran mail.docx", "A 46123-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 2230-2025 tillsynsbegäran mail.docx", "A 2230-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46522-2025</t>
+          <t>A 60983-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1668,10 +1664,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45926</v>
+        <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1683,19 +1679,14 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1729,35 +1720,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
         <v/>
       </c>
     </row>
@@ -1781,7 +1772,7 @@
         <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1874,7 +1865,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 9030-2022</t>
+          <t>A 54444-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1888,10 +1879,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44615</v>
+        <v>44473</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1904,10 +1895,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1940,151 +1931,151 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>Ängshök</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9030-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44615</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Skogsalm</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 9030-2022 artfynd.xlsx", "A 9030-2022")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 9030-2022 karta.png", "A 9030-2022")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 9030-2022 georefererad karta.tif", "A 9030-2022")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 9030-2022 FSC-klagomål.docx", "A 9030-2022")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 9030-2022 FSC-klagomål mail.docx", "A 9030-2022")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 9030-2022 tillsynsbegäran.docx", "A 9030-2022")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 9030-2022 tillsynsbegäran mail.docx", "A 9030-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 45164-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45191</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Skogsduva</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34869-2026</t>
+          <t>A 33532-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2098,10 +2089,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46255</v>
+        <v>45519</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2114,7 +2105,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2147,1005 +2138,1014 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 7564-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45705</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 7564-2025 artfynd.xlsx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 7564-2025 karta.png", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 7564-2025 georefererad karta.tif", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 7564-2025 FSC-klagomål.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 7564-2025 FSC-klagomål mail.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 7564-2025 tillsynsbegäran.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 7564-2025 tillsynsbegäran mail.docx", "A 7564-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 41274-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45898</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 41274-2025 artfynd.xlsx", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 41274-2025 karta.png", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 41274-2025 georefererad karta.tif", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 41274-2025 FSC-klagomål.docx", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 41274-2025 FSC-klagomål mail.docx", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 41274-2025 tillsynsbegäran.docx", "A 41274-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 41274-2025 tillsynsbegäran mail.docx", "A 41274-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 46156-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45924</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46156-2025 artfynd.xlsx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46156-2025 karta.png", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46156-2025 georefererad karta.tif", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46156-2025 FSC-klagomål.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46156-2025 FSC-klagomål mail.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46156-2025 tillsynsbegäran.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46156-2025 tillsynsbegäran mail.docx", "A 46156-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 46123-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45924</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46123-2025 artfynd.xlsx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46123-2025 karta.png", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46123-2025 georefererad karta.tif", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/knärot/A 46123-2025 karta knärot.png", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46123-2025 FSC-klagomål.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46123-2025 FSC-klagomål mail.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46123-2025 tillsynsbegäran.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46123-2025 tillsynsbegäran mail.docx", "A 46123-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 46522-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45926</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 34869-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Backsippa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 34869-2026 artfynd.xlsx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 34869-2026 karta.png", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 34869-2026 georefererad karta.tif", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 34869-2026 FSC-klagomål.docx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 34869-2026 FSC-klagomål mail.docx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 34869-2026 tillsynsbegäran.docx", "A 34869-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 34869-2026 tillsynsbegäran mail.docx", "A 34869-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 13567-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45736</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 32573-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T23" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Klubbsprötad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 22327-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45446</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 32573-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Lunglav</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32573-2026 artfynd.xlsx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32573-2026 karta.png", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32573-2026 georefererad karta.tif", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32573-2026 FSC-klagomål.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32573-2026 FSC-klagomål mail.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32573-2026 tillsynsbegäran.docx", "A 32573-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32573-2026 tillsynsbegäran mail.docx", "A 32573-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 33532-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45519</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J20" t="n">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 32554-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T24" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Backsippa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 32554-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Purpurknipprot</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 60983-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J22" t="n">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 62852-2025</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T25" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 62852-2025</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Tibast</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 53521-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45230</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Skogsduva</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 53521-2023 artfynd.xlsx", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 53521-2023 karta.png", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 53521-2023 georefererad karta.tif", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 53521-2023 FSC-klagomål.docx", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 53521-2023 FSC-klagomål mail.docx", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 53521-2023 tillsynsbegäran.docx", "A 53521-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 53521-2023 tillsynsbegäran mail.docx", "A 53521-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 2230-2025</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45673</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 2230-2025 artfynd.xlsx", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 2230-2025 karta.png", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 2230-2025 georefererad karta.tif", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 2230-2025 FSC-klagomål.docx", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 2230-2025 FSC-klagomål mail.docx", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 2230-2025 tillsynsbegäran.docx", "A 2230-2025")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 2230-2025 tillsynsbegäran mail.docx", "A 2230-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>44573</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1552-2022</t>
+          <t>A 72290-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3310,14 +3310,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44573</v>
+        <v>44545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 72290-2021</t>
+          <t>A 1552-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3383,14 +3383,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44545</v>
+        <v>44573</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>44480</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19352-2022</t>
+          <t>A 3877-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44692</v>
+        <v>44951</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10950-2022</t>
+          <t>A 19352-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44627</v>
+        <v>44692</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3665,7 +3665,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34431-2022</t>
+          <t>A 50901-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44792</v>
+        <v>45602</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3694,13 +3694,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3743,7 +3738,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 51475-2023</t>
+          <t>A 10950-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3757,10 +3752,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45221</v>
+        <v>44627</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3773,7 +3768,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3816,7 +3811,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12253-2024</t>
+          <t>A 58412-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3830,10 +3825,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45378</v>
+        <v>45250</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3846,7 +3841,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3889,7 +3884,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12254-2024</t>
+          <t>A 63449-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3899,14 +3894,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45378</v>
+        <v>45273</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3919,7 +3914,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3962,7 +3957,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 53518-2022</t>
+          <t>A 60969-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3976,10 +3971,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44879</v>
+        <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3992,7 +3987,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4035,7 +4030,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17707-2023</t>
+          <t>A 35404-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4049,10 +4044,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45037</v>
+        <v>45146</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4065,7 +4060,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4108,7 +4103,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23114-2025</t>
+          <t>A 60964-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4122,10 +4117,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45791</v>
+        <v>45261</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4138,7 +4133,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4181,7 +4176,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2749-2024</t>
+          <t>A 61012-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4195,10 +4190,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45314</v>
+        <v>45259</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4211,7 +4206,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4254,7 +4249,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 63445-2025</t>
+          <t>A 3678-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4268,10 +4263,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46013</v>
+        <v>45681</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4284,7 +4279,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4327,7 +4322,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54442-2021</t>
+          <t>A 36401-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4341,10 +4336,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44473</v>
+        <v>45152</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4356,8 +4351,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57284-2024</t>
+          <t>A 50886-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45629</v>
+        <v>45602</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 72563-2021</t>
+          <t>A 15467-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44546</v>
+        <v>45020</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 72558-2021</t>
+          <t>A 14210-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44546</v>
+        <v>45009</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4619,7 +4619,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24499-2025</t>
+          <t>A 72558-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45798</v>
+        <v>44546</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4692,7 +4692,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18740-2025</t>
+          <t>A 2418-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45763</v>
+        <v>45674</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4765,7 +4765,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 66977-2021</t>
+          <t>A 42042-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44522</v>
+        <v>45177</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43032-2025</t>
+          <t>A 65921-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45909</v>
+        <v>44517</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4911,7 +4911,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27232-2025</t>
+          <t>A 35447-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45812</v>
+        <v>45146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4984,7 +4984,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 43026-2025</t>
+          <t>A 79-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4994,14 +4994,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45909</v>
+        <v>45293</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5057,7 +5057,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 65921-2021</t>
+          <t>A 54442-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44517</v>
+        <v>44473</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5130,7 +5130,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28663-2025</t>
+          <t>A 50181-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5144,10 +5144,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45819</v>
+        <v>45208</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5203,7 +5203,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 50179-2023</t>
+          <t>A 64934-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45208</v>
+        <v>45282</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5276,7 +5276,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 50570-2023</t>
+          <t>A 37631-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45217</v>
+        <v>45159</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5349,7 +5349,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39950-2024</t>
+          <t>A 2231-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5363,10 +5363,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45553</v>
+        <v>45673</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5378,13 +5378,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5427,7 +5422,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 44757-2025</t>
+          <t>A 1293-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5441,10 +5436,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45917</v>
+        <v>44936</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5457,7 +5452,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5500,7 +5495,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30468-2025</t>
+          <t>A 59410-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5510,14 +5505,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45827</v>
+        <v>44907</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5529,8 +5524,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5573,7 +5573,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4821-2023</t>
+          <t>A 59411-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44957</v>
+        <v>44907</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5602,8 +5602,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5646,7 +5651,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10980-2024</t>
+          <t>A 66977-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5660,10 +5665,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45370</v>
+        <v>44522</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5676,7 +5681,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5719,7 +5724,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 46164-2025</t>
+          <t>A 2800-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5733,10 +5738,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45924</v>
+        <v>45677</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5749,7 +5754,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5792,7 +5797,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 43012-2024</t>
+          <t>A 16304-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5802,14 +5807,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45567</v>
+        <v>45407</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5822,7 +5827,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5865,7 +5870,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 23781-2025</t>
+          <t>A 41337-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5879,10 +5884,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45793</v>
+        <v>45174</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5895,7 +5900,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5938,7 +5943,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 46144-2025</t>
+          <t>A 10984-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5952,10 +5957,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45924</v>
+        <v>45370</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5968,7 +5973,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6011,7 +6016,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46159-2025</t>
+          <t>A 34521-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6025,10 +6030,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45924</v>
+        <v>45525</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6041,7 +6046,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6084,7 +6089,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60964-2023</t>
+          <t>A 38300-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6098,10 +6103,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45261</v>
+        <v>45161</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6114,7 +6119,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6157,7 +6162,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31623-2025</t>
+          <t>A 43012-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6167,14 +6172,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45834</v>
+        <v>45567</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6187,7 +6192,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6230,7 +6235,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15276-2022</t>
+          <t>A 8658-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6244,10 +6249,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44659</v>
+        <v>44613</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6259,13 +6264,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6308,7 +6308,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31624-2025</t>
+          <t>A 15276-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45834</v>
+        <v>44659</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6337,8 +6337,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6381,7 +6386,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 46521-2025</t>
+          <t>A 17707-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6395,10 +6400,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45926</v>
+        <v>45037</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6410,13 +6415,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1293-2023</t>
+          <t>A 10980-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44936</v>
+        <v>45370</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6532,7 +6532,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64934-2023</t>
+          <t>A 50570-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45282</v>
+        <v>45217</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6605,7 +6605,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50339-2023</t>
+          <t>A 46248-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45216</v>
+        <v>45581</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 59234-2022</t>
+          <t>A 61575-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44904</v>
+        <v>45261</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6707,13 +6707,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6756,7 +6751,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 37806-2022</t>
+          <t>A 11944-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6770,10 +6765,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44810</v>
+        <v>45376</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6786,7 +6781,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6829,7 +6824,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 55730-2022</t>
+          <t>A 34664-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6843,10 +6838,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44888</v>
+        <v>45526</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6902,7 +6897,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4837-2026</t>
+          <t>A 60977-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6916,10 +6911,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46048</v>
+        <v>45261</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6932,7 +6927,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6975,7 +6970,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37802-2022</t>
+          <t>A 12253-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6989,10 +6984,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44810</v>
+        <v>45378</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7005,7 +7000,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7048,7 +7043,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4852-2026</t>
+          <t>A 12254-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7062,10 +7057,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46048</v>
+        <v>45378</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7078,7 +7073,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7121,7 +7116,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 51335-2025</t>
+          <t>A 3681-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7135,10 +7130,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45950</v>
+        <v>45681</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7151,7 +7146,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7194,7 +7189,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15491-2024</t>
+          <t>A 72563-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7208,10 +7203,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45401</v>
+        <v>44546</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7223,13 +7218,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7272,7 +7262,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 51326-2025</t>
+          <t>A 37083-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7286,10 +7276,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45950</v>
+        <v>45539</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7302,7 +7292,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7345,7 +7335,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 64930-2023</t>
+          <t>A 12675-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7359,10 +7349,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45282</v>
+        <v>45384</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7375,7 +7365,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7418,7 +7408,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24866-2023</t>
+          <t>A 49971-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7432,10 +7422,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45085</v>
+        <v>45215</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7448,7 +7438,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7491,7 +7481,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38199-2025</t>
+          <t>A 13560-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7505,10 +7495,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45882</v>
+        <v>45736</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7521,7 +7511,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7564,7 +7554,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 44770-2025</t>
+          <t>A 38278-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7574,14 +7564,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45917</v>
+        <v>45545</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7594,7 +7584,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7637,7 +7627,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44769-2025</t>
+          <t>A 59234-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7647,14 +7637,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45917</v>
+        <v>44904</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7666,8 +7656,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7710,7 +7705,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3087-2023</t>
+          <t>A 23114-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7724,10 +7719,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44946</v>
+        <v>45791</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7740,7 +7735,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7783,7 +7778,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58415-2021</t>
+          <t>A 57284-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7797,10 +7792,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44488</v>
+        <v>45629</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7813,7 +7808,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7856,7 +7851,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35447-2023</t>
+          <t>A 2749-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7870,10 +7865,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45146</v>
+        <v>45314</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7886,7 +7881,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7929,7 +7924,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 55939-2025</t>
+          <t>A 2715-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7943,10 +7938,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45973</v>
+        <v>44580</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7959,7 +7954,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8002,7 +7997,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57194-2025</t>
+          <t>A 961-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8016,10 +8011,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45979</v>
+        <v>45301</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8032,7 +8027,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8075,7 +8070,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57942-2025</t>
+          <t>A 52655-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8085,14 +8080,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45982</v>
+        <v>45225</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8105,7 +8100,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8148,7 +8143,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 58321-2025</t>
+          <t>A 1013-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8162,10 +8157,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45985</v>
+        <v>45666</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8178,7 +8173,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8221,7 +8216,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58756-2025</t>
+          <t>A 24866-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8235,10 +8230,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45986</v>
+        <v>45085</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8251,7 +8246,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8294,7 +8289,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58761-2025</t>
+          <t>A 39950-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8308,10 +8303,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45986</v>
+        <v>45553</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8323,8 +8318,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8367,7 +8367,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 58310-2025</t>
+          <t>A 11270-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45985</v>
+        <v>44629</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8440,7 +8440,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 63449-2023</t>
+          <t>A 22328-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8450,14 +8450,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45273</v>
+        <v>45446</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8513,7 +8513,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 3678-2025</t>
+          <t>A 62570-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45681</v>
+        <v>45269</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8586,7 +8586,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 59105-2025</t>
+          <t>A 64930-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45988</v>
+        <v>45282</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8659,7 +8659,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 36401-2023</t>
+          <t>A 24499-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45152</v>
+        <v>45798</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8688,13 +8688,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8737,7 +8732,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 11064-2026</t>
+          <t>A 50883-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8751,10 +8746,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46079</v>
+        <v>45602</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8767,7 +8762,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8810,7 +8805,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 7337-2023</t>
+          <t>A 50896-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8824,10 +8819,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44971</v>
+        <v>45602</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8840,7 +8835,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8883,7 +8878,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 62129-2025</t>
+          <t>A 68095-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8897,10 +8892,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46006</v>
+        <v>44526</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8913,7 +8908,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8956,7 +8951,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 62123-2025</t>
+          <t>A 18740-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8970,10 +8965,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46006</v>
+        <v>45763</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8986,7 +8981,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9029,7 +9024,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 14928-2026</t>
+          <t>A 58800-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9039,14 +9034,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46104</v>
+        <v>44903</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9058,13 +9053,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9107,7 +9097,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15032-2026</t>
+          <t>A 4821-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9121,10 +9111,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46104</v>
+        <v>44957</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9136,13 +9126,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9185,7 +9170,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60977-2023</t>
+          <t>A 11478-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9199,10 +9184,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45261</v>
+        <v>45372</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9215,7 +9200,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9258,7 +9243,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16110-2026</t>
+          <t>A 38299-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9272,10 +9257,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46108</v>
+        <v>45161</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9288,7 +9273,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9331,7 +9316,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 16173-2026</t>
+          <t>A 3087-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9345,10 +9330,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46111</v>
+        <v>44946</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9360,13 +9345,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9409,7 +9389,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17699-2026</t>
+          <t>A 27232-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9419,14 +9399,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46121</v>
+        <v>45812</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9439,7 +9419,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9482,7 +9462,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 17700-2026</t>
+          <t>A 28663-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9496,10 +9476,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46121</v>
+        <v>45819</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9512,7 +9492,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9555,7 +9535,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60969-2023</t>
+          <t>A 15491-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9569,10 +9549,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45261</v>
+        <v>45401</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9584,8 +9564,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9628,7 +9613,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 38299-2023</t>
+          <t>A 45918-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9642,10 +9627,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45161</v>
+        <v>45580</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9658,7 +9643,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9701,7 +9686,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 18517-2026</t>
+          <t>A 4314-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9711,14 +9696,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46127</v>
+        <v>45324</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9732,11 +9717,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9779,7 +9764,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58800-2022</t>
+          <t>A 12769-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9789,14 +9774,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44903</v>
+        <v>45384</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9809,7 +9794,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9852,7 +9837,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 6785-2024</t>
+          <t>A 40667-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9866,10 +9851,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45342</v>
+        <v>45170</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9881,13 +9866,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9930,7 +9910,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 11944-2024</t>
+          <t>A 9125-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9944,10 +9924,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45376</v>
+        <v>44980</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9959,8 +9939,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10003,7 +9988,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 39965-2025</t>
+          <t>A 49915-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10017,10 +10002,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45892</v>
+        <v>45597</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10033,7 +10018,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10076,7 +10061,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 27255-2025</t>
+          <t>A 50906-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10090,10 +10075,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45812</v>
+        <v>45602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10106,7 +10091,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10149,7 +10134,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 27251-2025</t>
+          <t>A 30468-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10163,10 +10148,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45812</v>
+        <v>45827</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10179,7 +10164,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10222,7 +10207,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 59411-2022</t>
+          <t>A 23781-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10232,14 +10217,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44907</v>
+        <v>45793</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10251,13 +10236,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10300,7 +10280,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 41105-2025</t>
+          <t>A 31624-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10314,10 +10294,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45898</v>
+        <v>45834</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10330,7 +10310,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10373,7 +10353,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58412-2023</t>
+          <t>A 31623-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10387,10 +10367,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45250</v>
+        <v>45834</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10403,7 +10383,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10446,7 +10426,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29580-2025</t>
+          <t>A 6785-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10460,10 +10440,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45825</v>
+        <v>45342</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10475,8 +10455,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10519,7 +10504,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 59410-2022</t>
+          <t>A 55730-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10529,14 +10514,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44907</v>
+        <v>44888</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10548,13 +10533,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10597,7 +10577,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 45918-2024</t>
+          <t>A 41819-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10611,10 +10591,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45580</v>
+        <v>45176</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10627,7 +10607,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10670,7 +10650,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 62570-2023</t>
+          <t>A 58415-2021</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10684,10 +10664,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45269</v>
+        <v>44488</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10700,7 +10680,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10743,7 +10723,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31010-2022</t>
+          <t>A 53518-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10757,10 +10737,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44768</v>
+        <v>44879</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10773,7 +10753,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10816,7 +10796,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20357-2026</t>
+          <t>A 53520-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10830,10 +10810,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46139</v>
+        <v>44879</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10846,7 +10826,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10889,7 +10869,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 62447-2025</t>
+          <t>A 50339-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10903,10 +10883,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46007</v>
+        <v>45216</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10918,13 +10898,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10967,7 +10942,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 28321-2025</t>
+          <t>A 22307-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10981,10 +10956,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45818</v>
+        <v>45446</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10997,7 +10972,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11040,7 +11015,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 14210-2023</t>
+          <t>A 15783-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11054,10 +11029,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45009</v>
+        <v>44663</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11070,7 +11045,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11113,7 +11088,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 35404-2023</t>
+          <t>A 37806-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11127,10 +11102,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45146</v>
+        <v>44810</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11143,7 +11118,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11186,7 +11161,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 68095-2021</t>
+          <t>A 34431-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11200,10 +11175,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44526</v>
+        <v>44792</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11215,8 +11190,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11259,7 +11239,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21518-2026</t>
+          <t>A 37802-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11273,10 +11253,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46148</v>
+        <v>44810</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11289,7 +11269,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11332,7 +11312,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 49915-2024</t>
+          <t>A 50179-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11346,10 +11326,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45597</v>
+        <v>45208</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11362,7 +11342,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.4</v>
+        <v>5.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11405,7 +11385,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 37631-2023</t>
+          <t>A 51475-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11419,10 +11399,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45159</v>
+        <v>45221</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11435,7 +11415,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11478,7 +11458,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32581-2025</t>
+          <t>A 7337-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11492,10 +11472,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45838</v>
+        <v>44971</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11508,7 +11488,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11551,7 +11531,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 11270-2022</t>
+          <t>A 38199-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11565,10 +11545,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44629</v>
+        <v>45882</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11581,7 +11561,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11624,7 +11604,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 41337-2023</t>
+          <t>A 51326-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11638,10 +11618,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45174</v>
+        <v>45950</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11654,7 +11634,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11697,7 +11677,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 2800-2025</t>
+          <t>A 51335-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11711,10 +11691,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45677</v>
+        <v>45950</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11727,7 +11707,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11770,7 +11750,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 2073-2026</t>
+          <t>A 43026-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11784,10 +11764,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46036</v>
+        <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11800,7 +11780,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11843,7 +11823,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 8658-2022</t>
+          <t>A 43032-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11857,10 +11837,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44613</v>
+        <v>45909</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11873,7 +11853,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11916,7 +11896,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 2418-2025</t>
+          <t>A 44769-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11926,14 +11906,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45674</v>
+        <v>45917</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11989,7 +11969,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 2231-2025</t>
+          <t>A 44757-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12003,10 +11983,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45673</v>
+        <v>45917</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12019,7 +11999,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12062,7 +12042,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24139-2026</t>
+          <t>A 44770-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12072,14 +12052,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46168</v>
+        <v>45917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12091,13 +12071,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12140,7 +12115,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 1011-2025</t>
+          <t>A 46164-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12154,10 +12129,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45666</v>
+        <v>45924</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12170,7 +12145,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12213,7 +12188,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 24786-2026</t>
+          <t>A 46159-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12227,10 +12202,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46171</v>
+        <v>45924</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12242,13 +12217,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12291,7 +12261,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24457-2026</t>
+          <t>A 55939-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12305,10 +12275,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46170</v>
+        <v>45973</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12320,13 +12290,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12369,7 +12334,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24903-2026</t>
+          <t>A 46144-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12379,14 +12344,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46174</v>
+        <v>45924</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12398,13 +12363,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12447,7 +12407,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 24894-2026</t>
+          <t>A 46521-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12461,10 +12421,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46174</v>
+        <v>45926</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12478,11 +12438,11 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12525,7 +12485,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 25031-2026</t>
+          <t>A 57194-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12539,10 +12499,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46174</v>
+        <v>45979</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12554,13 +12514,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12603,7 +12558,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 24888-2026</t>
+          <t>A 57942-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12617,10 +12572,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46174</v>
+        <v>45982</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12632,13 +12587,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12681,7 +12631,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24896-2026</t>
+          <t>A 58310-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12695,10 +12645,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46174</v>
+        <v>45985</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12710,13 +12660,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12759,7 +12704,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24900-2026</t>
+          <t>A 58321-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12773,10 +12718,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46174</v>
+        <v>45985</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12788,13 +12733,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12837,7 +12777,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 25503-2026</t>
+          <t>A 58756-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12851,10 +12791,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46177</v>
+        <v>45986</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12864,11 +12804,6 @@
       <c r="G157" t="inlineStr">
         <is>
           <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I157" t="n">
@@ -12915,7 +12850,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 27126-2026</t>
+          <t>A 58761-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12925,14 +12860,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46188</v>
+        <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12944,13 +12879,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12993,7 +12923,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27137-2026</t>
+          <t>A 59105-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13007,10 +12937,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46188</v>
+        <v>45988</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13022,13 +12952,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13071,7 +12996,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 11478-2024</t>
+          <t>A 62129-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13085,10 +13010,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45372</v>
+        <v>46006</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13101,7 +13026,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13144,7 +13069,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 28525-2026</t>
+          <t>A 62123-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13158,10 +13083,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46197</v>
+        <v>46006</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13173,13 +13098,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13222,7 +13142,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 50181-2023</t>
+          <t>A 63445-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13236,10 +13156,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45208</v>
+        <v>46013</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13252,7 +13172,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13295,7 +13215,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 53520-2022</t>
+          <t>A 4852-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13309,10 +13229,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44879</v>
+        <v>46048</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13325,7 +13245,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13368,7 +13288,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 52655-2023</t>
+          <t>A 4837-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13378,14 +13298,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45225</v>
+        <v>46048</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13398,7 +13318,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13441,7 +13361,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 22307-2024</t>
+          <t>A 11064-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13455,10 +13375,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45446</v>
+        <v>46079</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13471,7 +13391,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13514,7 +13434,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 3877-2023</t>
+          <t>A 15032-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13528,10 +13448,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44951</v>
+        <v>46104</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13543,8 +13463,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13587,7 +13512,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 28652-2026</t>
+          <t>A 14928-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13601,10 +13526,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46198</v>
+        <v>46104</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13622,7 +13547,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13665,7 +13590,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 61012-2023</t>
+          <t>A 16110-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13679,10 +13604,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45259</v>
+        <v>46108</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13695,7 +13620,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13738,7 +13663,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15783-2022</t>
+          <t>A 16173-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13752,10 +13677,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44663</v>
+        <v>46111</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13767,8 +13692,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13811,7 +13741,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 34521-2024</t>
+          <t>A 17700-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13825,10 +13755,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45525</v>
+        <v>46121</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13841,7 +13771,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13884,7 +13814,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 1013-2025</t>
+          <t>A 17699-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13898,10 +13828,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45666</v>
+        <v>46121</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13914,7 +13844,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13957,7 +13887,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 2715-2022</t>
+          <t>A 18517-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13971,10 +13901,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44580</v>
+        <v>46127</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13986,8 +13916,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14030,7 +13965,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 34172-2026</t>
+          <t>A 29580-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14044,10 +13979,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46253</v>
+        <v>45825</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14059,13 +13994,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14108,7 +14038,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 34730-2026</t>
+          <t>A 27251-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14122,10 +14052,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46258</v>
+        <v>45812</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14137,13 +14067,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14186,7 +14111,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 34748-2026</t>
+          <t>A 41105-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14200,10 +14125,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46258</v>
+        <v>45898</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14215,13 +14140,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14264,7 +14184,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 34794-2026</t>
+          <t>A 39965-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14274,14 +14194,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46258</v>
+        <v>45892</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14293,13 +14213,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14342,7 +14257,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 31161-2026</t>
+          <t>A 28321-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14356,10 +14271,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46216</v>
+        <v>45818</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14372,7 +14287,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14415,7 +14330,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 31192-2026</t>
+          <t>A 27255-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14429,10 +14344,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46217</v>
+        <v>45812</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14445,7 +14360,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14488,7 +14403,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 31193-2026</t>
+          <t>A 20357-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14502,10 +14417,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46217</v>
+        <v>46139</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14518,7 +14433,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14561,7 +14476,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 4314-2024</t>
+          <t>A 31010-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14571,14 +14486,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45324</v>
+        <v>44768</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14590,13 +14505,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14639,7 +14549,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 60917-2022</t>
+          <t>A 62447-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14653,10 +14563,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44908</v>
+        <v>46007</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14668,8 +14578,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14712,7 +14627,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 3681-2025</t>
+          <t>A 21518-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14726,10 +14641,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45681</v>
+        <v>46148</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14742,7 +14657,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14785,7 +14700,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 41819-2023</t>
+          <t>A 32581-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14799,10 +14714,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45176</v>
+        <v>45838</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14815,7 +14730,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14858,7 +14773,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 36209-2026</t>
+          <t>A 2073-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14872,10 +14787,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46267</v>
+        <v>46036</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14888,7 +14803,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14931,7 +14846,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36206-2026</t>
+          <t>A 1011-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14945,10 +14860,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46267</v>
+        <v>45666</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14961,7 +14876,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15004,7 +14919,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 50883-2024</t>
+          <t>A 24139-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15018,10 +14933,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45602</v>
+        <v>46168</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15033,8 +14948,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15077,7 +14997,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 50896-2024</t>
+          <t>A 24457-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15091,10 +15011,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45602</v>
+        <v>46170</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15106,8 +15026,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15150,7 +15075,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 10984-2024</t>
+          <t>A 25031-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15164,10 +15089,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45370</v>
+        <v>46174</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15179,8 +15104,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15223,7 +15153,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 34167-2026</t>
+          <t>A 24786-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15237,10 +15167,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46253</v>
+        <v>46171</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15258,7 +15188,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15301,7 +15231,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 15467-2023</t>
+          <t>A 24900-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15315,10 +15245,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45020</v>
+        <v>46174</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15330,8 +15260,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15374,7 +15309,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 34162-2026</t>
+          <t>A 24894-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15388,10 +15323,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46253</v>
+        <v>46174</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15409,7 +15344,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15452,7 +15387,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 37226-2026</t>
+          <t>A 24888-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15466,10 +15401,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46274</v>
+        <v>46174</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15483,11 +15418,11 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15530,7 +15465,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 37174-2026</t>
+          <t>A 24896-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15544,10 +15479,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46274</v>
+        <v>46174</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15561,11 +15496,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15608,7 +15543,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 34834-2026</t>
+          <t>A 24903-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15618,14 +15553,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46258</v>
+        <v>46174</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15637,8 +15572,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15681,7 +15621,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 40667-2023</t>
+          <t>A 25503-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15695,10 +15635,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45170</v>
+        <v>46177</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15710,8 +15650,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15754,7 +15699,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31929-2026</t>
+          <t>A 27126-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15764,14 +15709,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15783,8 +15728,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15827,7 +15777,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 28131-2026</t>
+          <t>A 27137-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15841,10 +15791,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15856,8 +15806,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15900,7 +15855,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 37353-2026</t>
+          <t>A 28652-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15914,10 +15869,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46275</v>
+        <v>46198</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15929,8 +15884,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15973,7 +15933,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 37355-2026</t>
+          <t>A 28525-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15987,10 +15947,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46275</v>
+        <v>46197</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16002,8 +15962,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16046,7 +16011,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 31928-2026</t>
+          <t>A 31161-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16060,10 +16025,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46232</v>
+        <v>46216</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16076,7 +16041,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16119,7 +16084,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 31930-2026</t>
+          <t>A 34794-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16129,14 +16094,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46232</v>
+        <v>46258</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16148,8 +16113,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16192,7 +16162,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 42042-2023</t>
+          <t>A 34730-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16206,10 +16176,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45177</v>
+        <v>46258</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16221,8 +16191,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16265,7 +16240,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37888-2026</t>
+          <t>A 34748-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16279,10 +16254,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46279</v>
+        <v>46258</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16296,11 +16271,11 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16343,7 +16318,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 50886-2024</t>
+          <t>A 31193-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16357,10 +16332,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45602</v>
+        <v>46217</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16373,7 +16348,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16416,7 +16391,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 50901-2024</t>
+          <t>A 31192-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16430,10 +16405,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45602</v>
+        <v>46217</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16446,7 +16421,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16489,7 +16464,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 32317-2026</t>
+          <t>A 60917-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16503,10 +16478,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46237</v>
+        <v>44908</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16519,7 +16494,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16562,7 +16537,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 32558-2026</t>
+          <t>A 36206-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16576,10 +16551,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46239</v>
+        <v>46267</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16591,13 +16566,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16640,7 +16610,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 32574-2026</t>
+          <t>A 36209-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16654,10 +16624,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46239</v>
+        <v>46267</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16669,13 +16639,8 @@
           <t>MJÖLBY</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16718,7 +16683,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 12769-2024</t>
+          <t>A 34834-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16732,10 +16697,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45384</v>
+        <v>46258</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16748,7 +16713,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16791,7 +16756,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 32564-2026</t>
+          <t>A 37226-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16805,10 +16770,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46239</v>
+        <v>46274</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16822,11 +16787,11 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16869,7 +16834,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 50906-2024</t>
+          <t>A 37355-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16883,10 +16848,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45602</v>
+        <v>46275</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16899,7 +16864,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16942,7 +16907,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 9125-2023</t>
+          <t>A 37174-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16956,10 +16921,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44980</v>
+        <v>46274</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16977,7 +16942,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17020,7 +16985,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 16304-2024</t>
+          <t>A 31928-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17034,10 +16999,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45407</v>
+        <v>46232</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17050,7 +17015,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17093,7 +17058,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 22328-2024</t>
+          <t>A 37353-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17107,10 +17072,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45446</v>
+        <v>46275</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17123,7 +17088,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17166,7 +17131,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 79-2024</t>
+          <t>A 31929-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17176,14 +17141,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45293</v>
+        <v>46232</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17196,7 +17161,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17239,7 +17204,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 961-2024</t>
+          <t>A 31930-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17253,10 +17218,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45301</v>
+        <v>46232</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17269,7 +17234,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17312,7 +17277,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 38985-2026</t>
+          <t>A 37888-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17326,10 +17291,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17341,8 +17306,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17385,7 +17355,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 38300-2023</t>
+          <t>A 28131-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17399,10 +17369,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45161</v>
+        <v>46195</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17415,7 +17385,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17458,7 +17428,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 33010-2026</t>
+          <t>A 32317-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17472,10 +17442,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17488,7 +17458,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17531,7 +17501,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 46248-2024</t>
+          <t>A 32574-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17545,10 +17515,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45581</v>
+        <v>46239</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17560,8 +17530,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17604,7 +17579,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 39762-2026</t>
+          <t>A 32558-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17618,10 +17593,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46290</v>
+        <v>46239</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17633,8 +17608,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17677,7 +17657,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 61575-2023</t>
+          <t>A 32564-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17691,10 +17671,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45261</v>
+        <v>46239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17706,8 +17686,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17750,7 +17735,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 39898-2026</t>
+          <t>A 38985-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17764,10 +17749,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17780,7 +17765,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17823,7 +17808,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 49971-2023</t>
+          <t>A 33010-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17837,10 +17822,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45215</v>
+        <v>46244</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17853,7 +17838,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17913,7 +17898,7 @@
         <v>46275</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17969,7 +17954,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 38278-2024</t>
+          <t>A 37367-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17979,14 +17964,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45545</v>
+        <v>46275</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17999,7 +17984,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18042,7 +18027,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 12675-2024</t>
+          <t>A 39898-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18056,10 +18041,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45384</v>
+        <v>46290</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18072,7 +18057,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18115,7 +18100,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 37083-2024</t>
+          <t>A 39762-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18129,10 +18114,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45539</v>
+        <v>46290</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18145,7 +18130,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18188,7 +18173,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 13560-2025</t>
+          <t>A 34167-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18202,10 +18187,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45736</v>
+        <v>46253</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18217,8 +18202,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18261,7 +18251,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 34664-2024</t>
+          <t>A 34172-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18275,10 +18265,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45526</v>
+        <v>46253</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18290,8 +18280,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18334,7 +18329,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 37367-2026</t>
+          <t>A 34162-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18348,10 +18343,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46275</v>
+        <v>46253</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18363,8 +18358,13 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18424,7 +18424,7 @@
         <v>46197</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>

--- a/Översikt MJÖLBY.xlsx
+++ b/Översikt MJÖLBY.xlsx
@@ -601,7 +601,7 @@
         <v>44482</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44524</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46216</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>45791</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>44695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 22327-2024</t>
+          <t>A 7564-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45446</v>
+        <v>45705</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1188,49 +1188,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 7564-2025 artfynd.xlsx", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 7564-2025 karta.png", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 7564-2025 georefererad karta.tif", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 7564-2025 FSC-klagomål.docx", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 7564-2025 FSC-klagomål mail.docx", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 7564-2025 tillsynsbegäran.docx", "A 7564-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 7564-2025 tillsynsbegäran mail.docx", "A 7564-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 45164-2023</t>
+          <t>A 41274-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45191</v>
+        <v>45898</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1260,20 +1260,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1284,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1300,42 +1300,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 41274-2025 artfynd.xlsx", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 41274-2025 karta.png", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 41274-2025 georefererad karta.tif", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 41274-2025 FSC-klagomål.docx", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 41274-2025 FSC-klagomål mail.docx", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 41274-2025 tillsynsbegäran.docx", "A 41274-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 41274-2025 tillsynsbegäran mail.docx", "A 41274-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 13567-2025</t>
+          <t>A 46156-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45736</v>
+        <v>45924</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1389,7 +1389,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1405,42 +1405,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46156-2025 artfynd.xlsx", "A 46156-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46156-2025 karta.png", "A 46156-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46156-2025 georefererad karta.tif", "A 46156-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46156-2025 FSC-klagomål.docx", "A 46156-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46156-2025 FSC-klagomål mail.docx", "A 46156-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46156-2025 tillsynsbegäran.docx", "A 46156-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46156-2025 tillsynsbegäran mail.docx", "A 46156-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53521-2023</t>
+          <t>A 46123-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45230</v>
+        <v>45924</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1510,42 +1510,46 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 53521-2023 artfynd.xlsx", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46123-2025 artfynd.xlsx", "A 46123-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 53521-2023 karta.png", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46123-2025 karta.png", "A 46123-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 53521-2023 georefererad karta.tif", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46123-2025 georefererad karta.tif", "A 46123-2025")</f>
         <v/>
       </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/knärot/A 46123-2025 karta knärot.png", "A 46123-2025")</f>
+        <v/>
+      </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 53521-2023 FSC-klagomål.docx", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46123-2025 FSC-klagomål.docx", "A 46123-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 53521-2023 FSC-klagomål mail.docx", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46123-2025 FSC-klagomål mail.docx", "A 46123-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 53521-2023 tillsynsbegäran.docx", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46123-2025 tillsynsbegäran.docx", "A 46123-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 53521-2023 tillsynsbegäran mail.docx", "A 53521-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46123-2025 tillsynsbegäran mail.docx", "A 46123-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2230-2025</t>
+          <t>A 46522-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1559,10 +1563,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45673</v>
+        <v>45926</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1574,14 +1578,19 @@
           <t>MJÖLBY</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1615,42 +1624,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 2230-2025 artfynd.xlsx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 2230-2025 karta.png", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 2230-2025 georefererad karta.tif", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 2230-2025 FSC-klagomål.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 2230-2025 FSC-klagomål mail.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 2230-2025 tillsynsbegäran.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 2230-2025 tillsynsbegäran mail.docx", "A 2230-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46522-2025 tillsynsbegäran mail.docx", "A 46522-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60983-2023</t>
+          <t>A 54444-2021</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1664,10 +1673,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45261</v>
+        <v>44473</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1680,7 +1689,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1695,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1704,10 +1713,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1716,39 +1725,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ängshök</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 60983-2023 artfynd.xlsx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 60983-2023 karta.png", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 60983-2023 georefererad karta.tif", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 60983-2023 FSC-klagomål.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 60983-2023 FSC-klagomål mail.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 60983-2023 tillsynsbegäran.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 60983-2023 tillsynsbegäran mail.docx", "A 60983-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
         <v/>
       </c>
     </row>
@@ -1772,7 +1781,7 @@
         <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1865,7 +1874,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54444-2021</t>
+          <t>A 9030-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1879,10 +1888,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44473</v>
+        <v>44615</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1895,10 +1904,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1931,46 +1940,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Ängshök</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 54444-2021 artfynd.xlsx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 9030-2022 artfynd.xlsx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 54444-2021 karta.png", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 9030-2022 karta.png", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 54444-2021 georefererad karta.tif", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 9030-2022 georefererad karta.tif", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 54444-2021 FSC-klagomål.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 9030-2022 FSC-klagomål.docx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 54444-2021 FSC-klagomål mail.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 9030-2022 FSC-klagomål mail.docx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 54444-2021 tillsynsbegäran.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 9030-2022 tillsynsbegäran.docx", "A 9030-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 54444-2021 tillsynsbegäran mail.docx", "A 54444-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 9030-2022 tillsynsbegäran mail.docx", "A 9030-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 9030-2022</t>
+          <t>A 45164-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1984,10 +1993,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44615</v>
+        <v>45191</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2000,10 +2009,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2015,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2024,10 +2033,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2036,46 +2045,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 9030-2022 artfynd.xlsx", "A 9030-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 45164-2023 artfynd.xlsx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 9030-2022 karta.png", "A 9030-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 45164-2023 karta.png", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 9030-2022 georefererad karta.tif", "A 9030-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 45164-2023 georefererad karta.tif", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 9030-2022 FSC-klagomål.docx", "A 9030-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 45164-2023 FSC-klagomål.docx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 9030-2022 FSC-klagomål mail.docx", "A 9030-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 45164-2023 FSC-klagomål mail.docx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 9030-2022 tillsynsbegäran.docx", "A 9030-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 45164-2023 tillsynsbegäran.docx", "A 45164-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 9030-2022 tillsynsbegäran mail.docx", "A 9030-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 45164-2023 tillsynsbegäran mail.docx", "A 45164-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33532-2024</t>
+          <t>A 34869-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2089,10 +2098,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45519</v>
+        <v>46255</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2105,7 +2114,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2138,688 +2147,694 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 34869-2026 artfynd.xlsx", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 34869-2026 karta.png", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 34869-2026 georefererad karta.tif", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 34869-2026 FSC-klagomål.docx", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 34869-2026 FSC-klagomål mail.docx", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 34869-2026 tillsynsbegäran.docx", "A 34869-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 34869-2026 tillsynsbegäran mail.docx", "A 34869-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 32573-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32573-2026 artfynd.xlsx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32573-2026 karta.png", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32573-2026 georefererad karta.tif", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32573-2026 FSC-klagomål.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32573-2026 FSC-klagomål mail.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32573-2026 tillsynsbegäran.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32573-2026 tillsynsbegäran mail.docx", "A 32573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 32554-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 32554-2026 artfynd.xlsx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 32554-2026 karta.png", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 32554-2026 georefererad karta.tif", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 32554-2026 FSC-klagomål.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 32554-2026 FSC-klagomål mail.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 32554-2026 tillsynsbegäran.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 32554-2026 tillsynsbegäran mail.docx", "A 32554-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 13567-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Klubbsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 13567-2025 artfynd.xlsx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 13567-2025 karta.png", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 13567-2025 georefererad karta.tif", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 13567-2025 FSC-klagomål.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 13567-2025 FSC-klagomål mail.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 13567-2025 tillsynsbegäran.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 13567-2025 tillsynsbegäran mail.docx", "A 13567-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 62852-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 62852-2025 artfynd.xlsx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 62852-2025 karta.png", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 62852-2025 georefererad karta.tif", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 62852-2025 FSC-klagomål.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 62852-2025 FSC-klagomål mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 62852-2025 tillsynsbegäran.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 62852-2025 tillsynsbegäran mail.docx", "A 62852-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 22327-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45446</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 22327-2024 artfynd.xlsx", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 22327-2024 karta.png", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 22327-2024 georefererad karta.tif", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 22327-2024 FSC-klagomål.docx", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 22327-2024 FSC-klagomål mail.docx", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 22327-2024 tillsynsbegäran.docx", "A 22327-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 22327-2024 tillsynsbegäran mail.docx", "A 22327-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 33532-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45519</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MJÖLBY</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Backsippa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 33532-2024 artfynd.xlsx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 33532-2024 karta.png", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 33532-2024 georefererad karta.tif", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 33532-2024 FSC-klagomål.docx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 33532-2024 FSC-klagomål mail.docx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 33532-2024 tillsynsbegäran.docx", "A 33532-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 33532-2024 tillsynsbegäran mail.docx", "A 33532-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 7564-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45705</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Solvända</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 7564-2025 artfynd.xlsx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 7564-2025 karta.png", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 7564-2025 georefererad karta.tif", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 7564-2025 FSC-klagomål.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 7564-2025 FSC-klagomål mail.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 7564-2025 tillsynsbegäran.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 7564-2025 tillsynsbegäran mail.docx", "A 7564-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 41274-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45898</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 41274-2025 artfynd.xlsx", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 41274-2025 karta.png", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 41274-2025 georefererad karta.tif", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 41274-2025 FSC-klagomål.docx", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 41274-2025 FSC-klagomål mail.docx", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 41274-2025 tillsynsbegäran.docx", "A 41274-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 41274-2025 tillsynsbegäran mail.docx", "A 41274-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 46156-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45924</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46156-2025 artfynd.xlsx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46156-2025 karta.png", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46156-2025 georefererad karta.tif", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46156-2025 FSC-klagomål.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46156-2025 FSC-klagomål mail.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46156-2025 tillsynsbegäran.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46156-2025 tillsynsbegäran mail.docx", "A 46156-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 46123-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45924</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46123-2025 artfynd.xlsx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46123-2025 karta.png", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46123-2025 georefererad karta.tif", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/knärot/A 46123-2025 karta knärot.png", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46123-2025 FSC-klagomål.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46123-2025 FSC-klagomål mail.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46123-2025 tillsynsbegäran.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsynsmail/A 46123-2025 tillsynsbegäran mail.docx", "A 46123-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 46522-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45926</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MJÖLBY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/artfynd/A 46522-2025 artfynd.xlsx", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor/A 46522-2025 karta.png", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/kartor_geotiff/A 46522-2025 georefererad karta.tif", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomål/A 46522-2025 FSC-klagomål.docx", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/klagomålsmail/A 46522-2025 FSC-klagomål mail.docx", "A 46522-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0586/tillsyn/A 46522-2025 tillsynsbegäran.docx", "A 46522-2025")</f>
-   